--- a/data/mysaa_products.xlsx
+++ b/data/mysaa_products.xlsx
@@ -581,24 +581,27 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O12"/>
+  <dimension ref="A1:R26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="36" customWidth="1" min="2" max="2"/>
+    <col width="37" customWidth="1" min="1" max="1"/>
+    <col width="37" customWidth="1" min="2" max="2"/>
     <col width="19" customWidth="1" min="3" max="3"/>
     <col width="19" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
     <col width="13" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
     <col width="50" customWidth="1" min="8" max="8"/>
-    <col width="50" customWidth="1" min="9" max="9"/>
-    <col width="50" customWidth="1" min="10" max="10"/>
+    <col width="35" customWidth="1" min="9" max="9"/>
+    <col width="45" customWidth="1" min="10" max="10"/>
     <col width="50" customWidth="1" min="11" max="11"/>
     <col width="12" customWidth="1" min="12" max="12"/>
     <col width="12" customWidth="1" min="13" max="13"/>
     <col width="14" customWidth="1" min="14" max="14"/>
     <col width="12" customWidth="1" min="15" max="15"/>
+    <col width="50" customWidth="1" min="16" max="16"/>
+    <col width="50" customWidth="1" min="17" max="17"/>
+    <col width="50" customWidth="1" min="18" max="18"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -677,16 +680,31 @@
           <t>active</t>
         </is>
       </c>
+      <c r="P1" s="2" t="inlineStr">
+        <is>
+          <t>image1</t>
+        </is>
+      </c>
+      <c r="Q1" s="2" t="inlineStr">
+        <is>
+          <t>image2</t>
+        </is>
+      </c>
+      <c r="R1" s="2" t="inlineStr">
+        <is>
+          <t>image3</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>dhoop-chandan-hero-jar</t>
+          <t>gulab-ki-chitthi-hero-jar-candle</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Dhoop &amp; Chandan Hero Jar Candle</t>
+          <t>Gulab Ki Chitthi Hero Jar Candle</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -696,7 +714,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>dhoop-chandan</t>
+          <t>gulab-ki-chitthi</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -707,11 +725,7 @@
           <t>220 ml</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>220 g</t>
-        </is>
-      </c>
+      <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr">
         <is>
           <t>Natural soy wax, cotton wick, phthalate-free fragrance oils</t>
@@ -719,21 +733,21 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Amber glass jar with metal lid, kraft gift sleeve</t>
+          <t>Mysaa Rituals signature packaging</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Sandalwood and dhoop, poured slow into our largest jar.</t>
+          <t>Gulab Ki Chitthi in our hero jar candle.</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Poured in small batches into our signature amber apothecary jar, this candle opens with warm sandalwood and settles into a soft trail of dhoop. The cotton wick burns clean and even for a long, unhurried evening. Burn time of approximately 45 hours.</t>
+          <t>A Mysaa Rituals hero jar candle in the Gulab Ki Chitthi fragrance. Made for gifting, rituals and everyday moments.</t>
         </is>
       </c>
       <c r="L2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M2" t="b">
         <v>0</v>
@@ -743,42 +757,53 @@
       </c>
       <c r="O2" t="b">
         <v>1</v>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>assets/catalogue/gulab-ki-chitthi/hero-jar-candle/01-cover.jpg</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>assets/catalogue/gulab-ki-chitthi/hero-jar-candle/02-detail.jpg</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>assets/catalogue/gulab-ki-chitthi/hero-jar-candle/03-lifestyle.jpg</t>
+        </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>madhuban-hero-jar</t>
+          <t>gulab-ki-chitthi-wide-jar-candle</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Madhuban Hero Jar Candle</t>
+          <t>Gulab Ki Chitthi Wide Jar Candle</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>hero-jar-candle</t>
+          <t>wide-jar-candle</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>madhuban</t>
+          <t>gulab-ki-chitthi</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1050</v>
+        <v>650</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>220 ml</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>220 g</t>
-        </is>
-      </c>
+          <t>120 ml</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr">
         <is>
           <t>Natural soy wax, cotton wick, phthalate-free fragrance oils</t>
@@ -786,21 +811,21 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Amber glass jar with metal lid, kraft gift sleeve</t>
+          <t>Mysaa Rituals signature packaging</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Raat ki Rani and rose, for the hour after sunset.</t>
+          <t>Gulab Ki Chitthi in our wide jar candle.</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>A deep floral pour built around Raat ki Rani and rose, designed for evenings that want to slow down. Sits beautifully on a bedside table or dinner table alike. Burn time of approximately 45 hours.</t>
+          <t>A Mysaa Rituals wide jar candle in the Gulab Ki Chitthi fragrance. Made for gifting, rituals and everyday moments.</t>
         </is>
       </c>
       <c r="L3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M3" t="b">
         <v>0</v>
@@ -810,22 +835,37 @@
       </c>
       <c r="O3" t="b">
         <v>1</v>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>assets/catalogue/gulab-ki-chitthi/wide-jar-candle/01-cover.jpg</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>assets/catalogue/gulab-ki-chitthi/wide-jar-candle/02-detail.jpg</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>assets/catalogue/gulab-ki-chitthi/wide-jar-candle/03-lifestyle.jpg</t>
+        </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>gulab-ki-chitthi-hero-jar</t>
+          <t>gulab-ki-chitthi-shot-glass-candle</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Gulab Ki Chitthi Hero Jar Candle</t>
+          <t>Gulab Ki Chitthi Shot Glass Candle</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>hero-jar-candle</t>
+          <t>shot-glass-candle</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -834,18 +874,14 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>950</v>
+        <v>350</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>220 ml</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>220 g</t>
-        </is>
-      </c>
+          <t>60 ml</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr">
         <is>
           <t>Natural soy wax, cotton wick, phthalate-free fragrance oils</t>
@@ -853,17 +889,17 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Amber glass jar with metal lid, kraft gift sleeve</t>
+          <t>Mysaa Rituals signature packaging</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Rose, folded like an old letter, in our biggest jar.</t>
+          <t>Gulab Ki Chitthi in our shot glass candle.</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>Soft rose layered with delicate florals, reminiscent of a handwritten letter tucked away for years. A quietly nostalgic candle that fills a room without overwhelming it. Burn time of approximately 45 hours.</t>
+          <t>A Mysaa Rituals shot glass candle in the Gulab Ki Chitthi fragrance. Made for gifting, rituals and everyday moments.</t>
         </is>
       </c>
       <c r="L4" t="b">
@@ -877,42 +913,53 @@
       </c>
       <c r="O4" t="b">
         <v>1</v>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>assets/catalogue/gulab-ki-chitthi/shot-glass-candle/01-cover.jpg</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>assets/catalogue/gulab-ki-chitthi/shot-glass-candle/02-detail.jpg</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>assets/catalogue/gulab-ki-chitthi/shot-glass-candle/03-lifestyle.jpg</t>
+        </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>gajre-ka-shringar-wide-jar</t>
+          <t>gulab-ki-chitthi-wax-melts</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Gajre Ka Shringar Wide Jar Candle</t>
+          <t>Gulab Ki Chitthi Wax Sachet Combo</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>wide-jar-candle</t>
+          <t>wax-melts</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>gajre-ka-shringar</t>
+          <t>gulab-ki-chitthi</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>650</v>
+        <v>350</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>120 ml</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>120 g</t>
-        </is>
-      </c>
+          <t>Combo</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr">
         <is>
           <t>Natural soy wax, cotton wick, phthalate-free fragrance oils</t>
@@ -920,84 +967,95 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Wide glass jar with wooden lid, kraft gift sleeve</t>
+          <t>Mysaa Rituals signature packaging</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Fresh jasmine and mogra, in a shorter, wider pour.</t>
+          <t>Gulab Ki Chitthi in our wax sachet combo.</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>Jasmine and mogra layered into a fresh white floral, poured into our wide jar for a broader melt pool and faster fragrance throw. A lovely everyday size for smaller rooms. Burn time of approximately 28 hours.</t>
+          <t>A Mysaa Rituals wax sachet combo in the Gulab Ki Chitthi fragrance. Made for gifting, rituals and everyday moments.</t>
         </is>
       </c>
       <c r="L5" t="b">
         <v>0</v>
       </c>
       <c r="M5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N5" t="b">
         <v>1</v>
       </c>
       <c r="O5" t="b">
         <v>1</v>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>assets/catalogue/gulab-ki-chitthi/wax-melts/01-cover.jpg</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>assets/catalogue/gulab-ki-chitthi/wax-melts/02-detail.jpg</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>assets/catalogue/gulab-ki-chitthi/wax-melts/03-lifestyle.jpg</t>
+        </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>saanjh-wide-jar</t>
+          <t>gulab-ki-chitthi-gift-hampers</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Saanjh Wide Jar Candle</t>
+          <t>Gulab Ki Chitthi Gift Hamper</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>wide-jar-candle</t>
+          <t>gift-hampers</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>saanjh</t>
+          <t>gulab-ki-chitthi</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>650</v>
+        <v>0</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>120 ml</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>120 g</t>
-        </is>
-      </c>
+          <t>Curated set</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Natural soy wax, cotton wick, phthalate-free fragrance oils</t>
+          <t>Curated Mysaa Rituals gifting selection</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Wide glass jar with wooden lid, kraft gift sleeve</t>
+          <t>Mysaa Rituals signature packaging</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Soft amber and quiet woods, for the slow hour.</t>
+          <t>Gulab Ki Chitthi in our gift hamper.</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>Amber and quiet woods designed for the hour when the day exhales — journaling, wind-downs, unhurried evenings. The wide jar gives an even burn and a generous scent throw. Burn time of approximately 28 hours.</t>
+          <t>A Mysaa Rituals gift hamper in the Gulab Ki Chitthi fragrance. Made for gifting, rituals and everyday moments.</t>
         </is>
       </c>
       <c r="L6" t="b">
@@ -1011,22 +1069,37 @@
       </c>
       <c r="O6" t="b">
         <v>1</v>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>assets/catalogue/gulab-ki-chitthi/gift-hampers/01-cover.jpg</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>assets/catalogue/gulab-ki-chitthi/gift-hampers/02-detail.jpg</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>assets/catalogue/gulab-ki-chitthi/gift-hampers/03-lifestyle.jpg</t>
+        </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>dhoop-chandan-shot-glass</t>
+          <t>dhoop-chandan-hero-jar-candle</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Dhoop &amp; Chandan Shot Glass Candle</t>
+          <t>Dhoop &amp; Chandan Hero Jar Candle</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>shot-glass-candle</t>
+          <t>hero-jar-candle</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1035,18 +1108,14 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>350</v>
+        <v>950</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>60 ml</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>60 g</t>
-        </is>
-      </c>
+          <t>220 ml</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr">
         <is>
           <t>Natural soy wax, cotton wick, phthalate-free fragrance oils</t>
@@ -1054,66 +1123,77 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Glass shot jar, kraft gift box</t>
+          <t>Mysaa Rituals signature packaging</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>A small, sandalwood-warm votive for trying us out.</t>
+          <t>Dhoop &amp; Chandan in our hero jar candle.</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>Our smallest pour — a compact shot-glass candle that's perfect as a sampler, a favour, or a first introduction to Mysaa. Burn time of approximately 12 hours.</t>
+          <t>A Mysaa Rituals hero jar candle in the Dhoop &amp; Chandan fragrance. Made for gifting, rituals and everyday moments.</t>
         </is>
       </c>
       <c r="L7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M7" t="b">
         <v>0</v>
       </c>
       <c r="N7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O7" t="b">
         <v>1</v>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>assets/catalogue/dhoop-chandan/hero-jar-candle/01-cover.jpg</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>assets/catalogue/dhoop-chandan/hero-jar-candle/02-detail.jpg</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>assets/catalogue/dhoop-chandan/hero-jar-candle/03-lifestyle.jpg</t>
+        </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>gulab-ki-chitthi-shot-glass</t>
+          <t>dhoop-chandan-wide-jar-candle</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Gulab Ki Chitthi Shot Glass Candle</t>
+          <t>Dhoop &amp; Chandan Wide Jar Candle</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>shot-glass-candle</t>
+          <t>wide-jar-candle</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>gulab-ki-chitthi</t>
+          <t>dhoop-chandan</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>350</v>
+        <v>650</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>60 ml</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>60 g</t>
-        </is>
-      </c>
+          <t>120 ml</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr">
         <is>
           <t>Natural soy wax, cotton wick, phthalate-free fragrance oils</t>
@@ -1121,84 +1201,95 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Glass shot jar, kraft gift box</t>
+          <t>Mysaa Rituals signature packaging</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Rose in miniature — a keepsake-sized pour.</t>
+          <t>Dhoop &amp; Chandan in our wide jar candle.</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>A small rose candle that makes a thoughtful add-on gift or wedding favour. Burn time of approximately 12 hours.</t>
+          <t>A Mysaa Rituals wide jar candle in the Dhoop &amp; Chandan fragrance. Made for gifting, rituals and everyday moments.</t>
         </is>
       </c>
       <c r="L8" t="b">
         <v>0</v>
       </c>
       <c r="M8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O8" t="b">
         <v>1</v>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>assets/catalogue/dhoop-chandan/wide-jar-candle/01-cover.jpg</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>assets/catalogue/dhoop-chandan/wide-jar-candle/02-detail.jpg</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>assets/catalogue/dhoop-chandan/wide-jar-candle/03-lifestyle.jpg</t>
+        </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>madhuban-wax-melts</t>
+          <t>dhoop-chandan-shot-glass-candle</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Madhuban Wax Melts</t>
+          <t>Dhoop &amp; Chandan Shot Glass Candle</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>wax-melts</t>
+          <t>shot-glass-candle</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>madhuban</t>
+          <t>dhoop-chandan</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>450</v>
+        <v>350</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Pack of 6</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>90 g</t>
-        </is>
-      </c>
+          <t>60 ml</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Natural soy wax, phthalate-free fragrance oils</t>
+          <t>Natural soy wax, cotton wick, phthalate-free fragrance oils</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Recyclable clamshell pack</t>
+          <t>Mysaa Rituals signature packaging</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Raat ki Rani and rose, flameless.</t>
+          <t>Dhoop &amp; Chandan in our shot glass candle.</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>For anyone who loves fragrance but prefers a flameless option — melt a cube in an oil burner for the same deep floral warmth as our Madhuban candle. Each pack holds 6 individually scored cubes.</t>
+          <t>A Mysaa Rituals shot glass candle in the Dhoop &amp; Chandan fragrance. Made for gifting, rituals and everyday moments.</t>
         </is>
       </c>
       <c r="L9" t="b">
@@ -1208,21 +1299,36 @@
         <v>0</v>
       </c>
       <c r="N9" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O9" t="b">
         <v>1</v>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>assets/catalogue/dhoop-chandan/shot-glass-candle/01-cover.jpg</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>assets/catalogue/dhoop-chandan/shot-glass-candle/02-detail.jpg</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>assets/catalogue/dhoop-chandan/shot-glass-candle/03-lifestyle.jpg</t>
+        </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>gajre-ka-shringar-wax-sachet</t>
+          <t>dhoop-chandan-wax-melts</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Gajre Ka Shringar Wax Sachet Set</t>
+          <t>Dhoop &amp; Chandan Wax Sachet Combo</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1232,7 +1338,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>gajre-ka-shringar</t>
+          <t>dhoop-chandan</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -1240,56 +1346,67 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Set of 3</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>45 g</t>
-        </is>
-      </c>
+          <t>Combo</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Scented wax beads, breathable muslin pouch</t>
+          <t>Natural soy wax, cotton wick, phthalate-free fragrance oils</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Cotton drawstring pouch</t>
+          <t>Mysaa Rituals signature packaging</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Jasmine and mogra, tucked into a wardrobe or bag.</t>
+          <t>Dhoop &amp; Chandan in our wax sachet combo.</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>Slip a sachet into a wardrobe, drawer or gym bag for a soft, lingering hit of jasmine and mogra — no flame or wax burner needed. Fragrance lasts 4–6 weeks per sachet.</t>
+          <t>A Mysaa Rituals wax sachet combo in the Dhoop &amp; Chandan fragrance. Made for gifting, rituals and everyday moments.</t>
         </is>
       </c>
       <c r="L10" t="b">
         <v>0</v>
       </c>
       <c r="M10" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N10" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O10" t="b">
         <v>1</v>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>assets/catalogue/dhoop-chandan/wax-melts/01-cover.jpg</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>assets/catalogue/dhoop-chandan/wax-melts/02-detail.jpg</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>assets/catalogue/dhoop-chandan/wax-melts/03-lifestyle.jpg</t>
+        </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>diwali-ritual-hamper</t>
+          <t>dhoop-chandan-gift-hampers</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Diwali Ritual Hamper</t>
+          <t>Dhoop &amp; Chandan Gift Hamper</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1303,40 +1420,36 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2499</v>
+        <v>0</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>3-piece set</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>560 g</t>
-        </is>
-      </c>
+          <t>Curated set</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Assorted candles, gift box, dried florals</t>
+          <t>Curated Mysaa Rituals gifting selection</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Signature Mysaa gift box</t>
+          <t>Mysaa Rituals signature packaging</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Three fragrances, one festive ritual.</t>
+          <t>Dhoop &amp; Chandan in our gift hamper.</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>A curated set spanning sandalwood warmth and rose nostalgia — one hero jar, one wide jar, and one shot glass candle, boxed together for festive gifting. Comes with a handwritten note card on request.</t>
+          <t>A Mysaa Rituals gift hamper in the Dhoop &amp; Chandan fragrance. Made for gifting, rituals and everyday moments.</t>
         </is>
       </c>
       <c r="L11" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M11" t="b">
         <v>0</v>
@@ -1346,73 +1459,1191 @@
       </c>
       <c r="O11" t="b">
         <v>1</v>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>assets/catalogue/dhoop-chandan/gift-hampers/01-cover.jpg</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>assets/catalogue/dhoop-chandan/gift-hampers/02-detail.jpg</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>assets/catalogue/dhoop-chandan/gift-hampers/03-lifestyle.jpg</t>
+        </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>rakhi-ritual-gift-set</t>
+          <t>gajre-ka-shringar-hero-jar-candle</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Rakhi Ritual Gift Set</t>
+          <t>Gajre Ka Shringar Hero Jar Candle</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
+          <t>hero-jar-candle</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>gajre-ka-shringar</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>950</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>220 ml</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Natural soy wax, cotton wick, phthalate-free fragrance oils</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Mysaa Rituals signature packaging</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Gajre Ka Shringar in our hero jar candle.</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>A Mysaa Rituals hero jar candle in the Gajre Ka Shringar fragrance. Made for gifting, rituals and everyday moments.</t>
+        </is>
+      </c>
+      <c r="L12" t="b">
+        <v>0</v>
+      </c>
+      <c r="M12" t="b">
+        <v>0</v>
+      </c>
+      <c r="N12" t="b">
+        <v>1</v>
+      </c>
+      <c r="O12" t="b">
+        <v>1</v>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>assets/catalogue/gajre-ka-shringar/hero-jar-candle/01-cover.jpg</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>assets/catalogue/gajre-ka-shringar/hero-jar-candle/02-detail.jpg</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>assets/catalogue/gajre-ka-shringar/hero-jar-candle/03-lifestyle.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>gajre-ka-shringar-wide-jar-candle</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Gajre Ka Shringar Wide Jar Candle</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>wide-jar-candle</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>gajre-ka-shringar</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>650</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>120 ml</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Natural soy wax, cotton wick, phthalate-free fragrance oils</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Mysaa Rituals signature packaging</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Gajre Ka Shringar in our wide jar candle.</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>A Mysaa Rituals wide jar candle in the Gajre Ka Shringar fragrance. Made for gifting, rituals and everyday moments.</t>
+        </is>
+      </c>
+      <c r="L13" t="b">
+        <v>0</v>
+      </c>
+      <c r="M13" t="b">
+        <v>0</v>
+      </c>
+      <c r="N13" t="b">
+        <v>1</v>
+      </c>
+      <c r="O13" t="b">
+        <v>1</v>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>assets/catalogue/gajre-ka-shringar/wide-jar-candle/01-cover.jpg</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>assets/catalogue/gajre-ka-shringar/wide-jar-candle/02-detail.jpg</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>assets/catalogue/gajre-ka-shringar/wide-jar-candle/03-lifestyle.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>gajre-ka-shringar-shot-glass-candle</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Gajre Ka Shringar Shot Glass Candle</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>shot-glass-candle</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>gajre-ka-shringar</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>350</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>60 ml</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Natural soy wax, cotton wick, phthalate-free fragrance oils</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Mysaa Rituals signature packaging</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Gajre Ka Shringar in our shot glass candle.</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>A Mysaa Rituals shot glass candle in the Gajre Ka Shringar fragrance. Made for gifting, rituals and everyday moments.</t>
+        </is>
+      </c>
+      <c r="L14" t="b">
+        <v>0</v>
+      </c>
+      <c r="M14" t="b">
+        <v>0</v>
+      </c>
+      <c r="N14" t="b">
+        <v>1</v>
+      </c>
+      <c r="O14" t="b">
+        <v>1</v>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>assets/catalogue/gajre-ka-shringar/shot-glass-candle/01-cover.jpg</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>assets/catalogue/gajre-ka-shringar/shot-glass-candle/02-detail.jpg</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>assets/catalogue/gajre-ka-shringar/shot-glass-candle/03-lifestyle.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>gajre-ka-shringar-wax-melts</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Gajre Ka Shringar Wax Sachet Combo</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>wax-melts</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>gajre-ka-shringar</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>350</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Combo</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Natural soy wax, cotton wick, phthalate-free fragrance oils</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Mysaa Rituals signature packaging</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>Gajre Ka Shringar in our wax sachet combo.</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>A Mysaa Rituals wax sachet combo in the Gajre Ka Shringar fragrance. Made for gifting, rituals and everyday moments.</t>
+        </is>
+      </c>
+      <c r="L15" t="b">
+        <v>0</v>
+      </c>
+      <c r="M15" t="b">
+        <v>0</v>
+      </c>
+      <c r="N15" t="b">
+        <v>1</v>
+      </c>
+      <c r="O15" t="b">
+        <v>1</v>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>assets/catalogue/gajre-ka-shringar/wax-melts/01-cover.jpg</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>assets/catalogue/gajre-ka-shringar/wax-melts/02-detail.jpg</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>assets/catalogue/gajre-ka-shringar/wax-melts/03-lifestyle.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>gajre-ka-shringar-gift-hampers</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Gajre Ka Shringar Gift Hamper</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
           <t>gift-hampers</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="D16" t="inlineStr">
         <is>
           <t>gajre-ka-shringar</t>
         </is>
       </c>
-      <c r="E12" t="n">
-        <v>1499</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>2-piece set</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>340 g</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>Wide jar candle, personalised card, dried florals</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>Signature Mysaa gift box</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>A small ritual to send along with a rakhi.</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>A wide jar candle in fresh jasmine and mogra, paired with a personalised card — a small, fragrant ritual to send between siblings. Add a name for the card at no extra cost.</t>
-        </is>
-      </c>
-      <c r="L12" t="b">
-        <v>0</v>
-      </c>
-      <c r="M12" t="b">
-        <v>0</v>
-      </c>
-      <c r="N12" t="b">
-        <v>1</v>
-      </c>
-      <c r="O12" t="b">
-        <v>1</v>
+      <c r="E16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Curated set</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Curated Mysaa Rituals gifting selection</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Mysaa Rituals signature packaging</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Gajre Ka Shringar in our gift hamper.</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>A Mysaa Rituals gift hamper in the Gajre Ka Shringar fragrance. Made for gifting, rituals and everyday moments.</t>
+        </is>
+      </c>
+      <c r="L16" t="b">
+        <v>0</v>
+      </c>
+      <c r="M16" t="b">
+        <v>0</v>
+      </c>
+      <c r="N16" t="b">
+        <v>1</v>
+      </c>
+      <c r="O16" t="b">
+        <v>1</v>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>assets/catalogue/gajre-ka-shringar/gift-hampers/01-cover.jpg</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>assets/catalogue/gajre-ka-shringar/gift-hampers/02-detail.jpg</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>assets/catalogue/gajre-ka-shringar/gift-hampers/03-lifestyle.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>madhuban-hero-jar-candle</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Madhuban Hero Jar Candle</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>hero-jar-candle</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>madhuban</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>1050</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>220 ml</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Natural soy wax, cotton wick, phthalate-free fragrance oils</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>Mysaa Rituals signature packaging</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>Madhuban in our hero jar candle.</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>A Mysaa Rituals hero jar candle in the Madhuban fragrance. Made for gifting, rituals and everyday moments.</t>
+        </is>
+      </c>
+      <c r="L17" t="b">
+        <v>0</v>
+      </c>
+      <c r="M17" t="b">
+        <v>0</v>
+      </c>
+      <c r="N17" t="b">
+        <v>1</v>
+      </c>
+      <c r="O17" t="b">
+        <v>1</v>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>assets/catalogue/madhuban/hero-jar-candle/01-cover.jpg</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>assets/catalogue/madhuban/hero-jar-candle/02-detail.jpg</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>assets/catalogue/madhuban/hero-jar-candle/03-lifestyle.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>madhuban-wide-jar-candle</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Madhuban Wide Jar Candle</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>wide-jar-candle</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>madhuban</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>650</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>120 ml</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Natural soy wax, cotton wick, phthalate-free fragrance oils</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>Mysaa Rituals signature packaging</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>Madhuban in our wide jar candle.</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>A Mysaa Rituals wide jar candle in the Madhuban fragrance. Made for gifting, rituals and everyday moments.</t>
+        </is>
+      </c>
+      <c r="L18" t="b">
+        <v>0</v>
+      </c>
+      <c r="M18" t="b">
+        <v>0</v>
+      </c>
+      <c r="N18" t="b">
+        <v>1</v>
+      </c>
+      <c r="O18" t="b">
+        <v>1</v>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>assets/catalogue/madhuban/wide-jar-candle/01-cover.jpg</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>assets/catalogue/madhuban/wide-jar-candle/02-detail.jpg</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>assets/catalogue/madhuban/wide-jar-candle/03-lifestyle.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>madhuban-shot-glass-candle</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Madhuban Shot Glass Candle</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>shot-glass-candle</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>madhuban</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>350</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>60 ml</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Natural soy wax, cotton wick, phthalate-free fragrance oils</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>Mysaa Rituals signature packaging</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>Madhuban in our shot glass candle.</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>A Mysaa Rituals shot glass candle in the Madhuban fragrance. Made for gifting, rituals and everyday moments.</t>
+        </is>
+      </c>
+      <c r="L19" t="b">
+        <v>0</v>
+      </c>
+      <c r="M19" t="b">
+        <v>0</v>
+      </c>
+      <c r="N19" t="b">
+        <v>1</v>
+      </c>
+      <c r="O19" t="b">
+        <v>1</v>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>assets/catalogue/madhuban/shot-glass-candle/01-cover.jpg</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>assets/catalogue/madhuban/shot-glass-candle/02-detail.jpg</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>assets/catalogue/madhuban/shot-glass-candle/03-lifestyle.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>madhuban-wax-melts</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Madhuban Wax Sachet Combo</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>wax-melts</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>madhuban</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>350</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Combo</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Natural soy wax, cotton wick, phthalate-free fragrance oils</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>Mysaa Rituals signature packaging</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>Madhuban in our wax sachet combo.</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>A Mysaa Rituals wax sachet combo in the Madhuban fragrance. Made for gifting, rituals and everyday moments.</t>
+        </is>
+      </c>
+      <c r="L20" t="b">
+        <v>0</v>
+      </c>
+      <c r="M20" t="b">
+        <v>0</v>
+      </c>
+      <c r="N20" t="b">
+        <v>1</v>
+      </c>
+      <c r="O20" t="b">
+        <v>1</v>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>assets/catalogue/madhuban/wax-melts/01-cover.jpg</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>assets/catalogue/madhuban/wax-melts/02-detail.jpg</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>assets/catalogue/madhuban/wax-melts/03-lifestyle.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>madhuban-gift-hampers</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Madhuban Gift Hamper</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>gift-hampers</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>madhuban</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Curated set</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Curated Mysaa Rituals gifting selection</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>Mysaa Rituals signature packaging</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>Madhuban in our gift hamper.</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>A Mysaa Rituals gift hamper in the Madhuban fragrance. Made for gifting, rituals and everyday moments.</t>
+        </is>
+      </c>
+      <c r="L21" t="b">
+        <v>0</v>
+      </c>
+      <c r="M21" t="b">
+        <v>0</v>
+      </c>
+      <c r="N21" t="b">
+        <v>1</v>
+      </c>
+      <c r="O21" t="b">
+        <v>1</v>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>assets/catalogue/madhuban/gift-hampers/01-cover.jpg</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>assets/catalogue/madhuban/gift-hampers/02-detail.jpg</t>
+        </is>
+      </c>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>assets/catalogue/madhuban/gift-hampers/03-lifestyle.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>raat-ki-rani-hero-jar-candle</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Raat Ki Rani Hero Jar Candle</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>hero-jar-candle</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>raat-ki-rani</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>950</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>220 ml</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Natural soy wax, cotton wick, phthalate-free fragrance oils</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>Mysaa Rituals signature packaging</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>Raat Ki Rani in our hero jar candle.</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>A Mysaa Rituals hero jar candle in the Raat Ki Rani fragrance. Made for gifting, rituals and everyday moments.</t>
+        </is>
+      </c>
+      <c r="L22" t="b">
+        <v>0</v>
+      </c>
+      <c r="M22" t="b">
+        <v>0</v>
+      </c>
+      <c r="N22" t="b">
+        <v>1</v>
+      </c>
+      <c r="O22" t="b">
+        <v>1</v>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>assets/catalogue/raat-ki-rani/hero-jar-candle/01-cover.jpg</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>assets/catalogue/raat-ki-rani/hero-jar-candle/02-detail.jpg</t>
+        </is>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>assets/catalogue/raat-ki-rani/hero-jar-candle/03-lifestyle.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>raat-ki-rani-wide-jar-candle</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Raat Ki Rani Wide Jar Candle</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>wide-jar-candle</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>raat-ki-rani</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>650</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>120 ml</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr"/>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Natural soy wax, cotton wick, phthalate-free fragrance oils</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>Mysaa Rituals signature packaging</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>Raat Ki Rani in our wide jar candle.</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>A Mysaa Rituals wide jar candle in the Raat Ki Rani fragrance. Made for gifting, rituals and everyday moments.</t>
+        </is>
+      </c>
+      <c r="L23" t="b">
+        <v>0</v>
+      </c>
+      <c r="M23" t="b">
+        <v>0</v>
+      </c>
+      <c r="N23" t="b">
+        <v>1</v>
+      </c>
+      <c r="O23" t="b">
+        <v>1</v>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>assets/catalogue/raat-ki-rani/wide-jar-candle/01-cover.jpg</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>assets/catalogue/raat-ki-rani/wide-jar-candle/02-detail.jpg</t>
+        </is>
+      </c>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>assets/catalogue/raat-ki-rani/wide-jar-candle/03-lifestyle.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>raat-ki-rani-shot-glass-candle</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Raat Ki Rani Shot Glass Candle</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>shot-glass-candle</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>raat-ki-rani</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>350</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>60 ml</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr"/>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Natural soy wax, cotton wick, phthalate-free fragrance oils</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>Mysaa Rituals signature packaging</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>Raat Ki Rani in our shot glass candle.</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>A Mysaa Rituals shot glass candle in the Raat Ki Rani fragrance. Made for gifting, rituals and everyday moments.</t>
+        </is>
+      </c>
+      <c r="L24" t="b">
+        <v>0</v>
+      </c>
+      <c r="M24" t="b">
+        <v>0</v>
+      </c>
+      <c r="N24" t="b">
+        <v>1</v>
+      </c>
+      <c r="O24" t="b">
+        <v>1</v>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>assets/catalogue/raat-ki-rani/shot-glass-candle/01-cover.jpg</t>
+        </is>
+      </c>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>assets/catalogue/raat-ki-rani/shot-glass-candle/02-detail.jpg</t>
+        </is>
+      </c>
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>assets/catalogue/raat-ki-rani/shot-glass-candle/03-lifestyle.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>raat-ki-rani-wax-melts</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Raat Ki Rani Wax Sachet Combo</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>wax-melts</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>raat-ki-rani</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>350</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Combo</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Natural soy wax, cotton wick, phthalate-free fragrance oils</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>Mysaa Rituals signature packaging</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>Raat Ki Rani in our wax sachet combo.</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>A Mysaa Rituals wax sachet combo in the Raat Ki Rani fragrance. Made for gifting, rituals and everyday moments.</t>
+        </is>
+      </c>
+      <c r="L25" t="b">
+        <v>0</v>
+      </c>
+      <c r="M25" t="b">
+        <v>0</v>
+      </c>
+      <c r="N25" t="b">
+        <v>1</v>
+      </c>
+      <c r="O25" t="b">
+        <v>1</v>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>assets/catalogue/raat-ki-rani/wax-melts/01-cover.jpg</t>
+        </is>
+      </c>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>assets/catalogue/raat-ki-rani/wax-melts/02-detail.jpg</t>
+        </is>
+      </c>
+      <c r="R25" t="inlineStr">
+        <is>
+          <t>assets/catalogue/raat-ki-rani/wax-melts/03-lifestyle.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>raat-ki-rani-gift-hampers</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Raat Ki Rani Gift Hamper</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>gift-hampers</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>raat-ki-rani</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>0</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Curated set</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr"/>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Curated Mysaa Rituals gifting selection</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>Mysaa Rituals signature packaging</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>Raat Ki Rani in our gift hamper.</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>A Mysaa Rituals gift hamper in the Raat Ki Rani fragrance. Made for gifting, rituals and everyday moments.</t>
+        </is>
+      </c>
+      <c r="L26" t="b">
+        <v>0</v>
+      </c>
+      <c r="M26" t="b">
+        <v>0</v>
+      </c>
+      <c r="N26" t="b">
+        <v>1</v>
+      </c>
+      <c r="O26" t="b">
+        <v>1</v>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>assets/catalogue/raat-ki-rani/gift-hampers/01-cover.jpg</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>assets/catalogue/raat-ki-rani/gift-hampers/02-detail.jpg</t>
+        </is>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>assets/catalogue/raat-ki-rani/gift-hampers/03-lifestyle.jpg</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -1431,9 +2662,9 @@
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
     <col width="19" customWidth="1" min="2" max="2"/>
-    <col width="41" customWidth="1" min="3" max="3"/>
+    <col width="43" customWidth="1" min="3" max="3"/>
     <col width="50" customWidth="1" min="4" max="4"/>
-    <col width="43" customWidth="1" min="5" max="5"/>
+    <col width="45" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
@@ -1472,27 +2703,27 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>dhoop-chandan</t>
+          <t>gulab-ki-chitthi</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Dhoop &amp; Chandan</t>
+          <t>Gulab Ki Chitthi</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Sandalwood, warm wood, incense, earth</t>
+          <t>Rose, soft florals, nostalgic sweetness</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>A warm, grounding fragrance inspired by the familiar aroma of sandalwood and dhoop.</t>
+          <t>A fragrance that feels like receiving an old handwritten letter carrying the scent of roses.</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Warm, Grounding, Meditative, Comforting</t>
+          <t>Romantic, Nostalgic, Delicate, Personal</t>
         </is>
       </c>
       <c r="F2" t="b">
@@ -1502,27 +2733,27 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>gajre-ka-shringar</t>
+          <t>dhoop-chandan</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Gajre Ka Shringar</t>
+          <t>Dhoop &amp; Chandan</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Jasmine, mogra, fresh white florals</t>
+          <t>Sandalwood, warm wood, incense, earth</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Inspired by the fragrance of fresh gajras and the timeless beauty of jasmine.</t>
+          <t>A warm, grounding fragrance inspired by the familiar aroma of sandalwood and dhoop.</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Floral, Romantic, Fresh, Nostalgic</t>
+          <t>Warm, Grounding, Meditative, Comforting</t>
         </is>
       </c>
       <c r="F3" t="b">
@@ -1532,27 +2763,27 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>madhuban</t>
+          <t>gajre-ka-shringar</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Madhuban</t>
+          <t>Gajre Ka Shringar</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Raat ki Rani, rose, deep florals</t>
+          <t>Jasmine, mogra, fresh white florals</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>A deep floral fragrance inspired by flowers that come alive after sunset.</t>
+          <t>Inspired by the fragrance of fresh gajras and the timeless beauty of jasmine.</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Dreamy, Sensual, Night-blooming, Romantic</t>
+          <t>Floral, Romantic, Fresh, Nostalgic</t>
         </is>
       </c>
       <c r="F4" t="b">
@@ -1562,27 +2793,27 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>saanjh</t>
+          <t>madhuban</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Saanjh</t>
+          <t>Madhuban</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Soft amber, quiet woods, evening air</t>
+          <t>Raat ki Rani, rose, deep florals</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>An evening-inspired sensory experience, made for the hour when the day exhales.</t>
+          <t>A deep floral fragrance inspired by flowers that come alive after sunset.</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Calm, Warm, Reflective, Evening ritual</t>
+          <t>Dreamy, Sensual, Night-blooming, Romantic</t>
         </is>
       </c>
       <c r="F5" t="b">
@@ -1592,27 +2823,27 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>gulab-ki-chitthi</t>
+          <t>raat-ki-rani</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Gulab Ki Chitthi</t>
+          <t>Raat Ki Rani</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Rose, soft florals, nostalgic sweetness</t>
+          <t>Raat ki Rani, soft florals, evening bloom</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>A fragrance that feels like receiving an old handwritten letter carrying the scent of roses.</t>
+          <t>An evocative night-blooming floral fragrance inspired by the queen of the night.</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Romantic, Nostalgic, Delicate, Personal</t>
+          <t>Night-blooming, Floral, Enveloping, Elegant</t>
         </is>
       </c>
       <c r="F6" t="b">
@@ -1634,7 +2865,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
-    <col width="21" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
     <col width="21" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
   </cols>
@@ -1729,7 +2960,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Wax Melts &amp; Sachets</t>
+          <t>Wax Sachet Combo</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">

--- a/data/mysaa_products.xlsx
+++ b/data/mysaa_products.xlsx
@@ -1088,9 +1088,7 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr"/>
-    </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
@@ -1112,9 +1110,7 @@
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr"/>
-    </row>
+    <row r="6"/>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
@@ -1199,9 +1195,7 @@
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" t="inlineStr"/>
-    </row>
+    <row r="19"/>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
@@ -1220,7 +1214,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R31"/>
+  <dimension ref="A1:R32"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14.5"/>
   <cols>
     <col width="37" customWidth="1" min="1" max="2"/>
@@ -1359,7 +1353,6 @@
           <t>220 ml</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr">
         <is>
           <t>Natural soy wax, cotton wick, phthalate-free fragrance oils</t>
@@ -1437,7 +1430,6 @@
           <t>120 ml</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr">
         <is>
           <t>Natural soy wax, cotton wick, phthalate-free fragrance oils</t>
@@ -1515,7 +1507,6 @@
           <t>60 ml</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr">
         <is>
           <t>Natural soy wax, cotton wick, phthalate-free fragrance oils</t>
@@ -1593,7 +1584,6 @@
           <t>Combo</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr">
         <is>
           <t>Natural soy wax, cotton wick, phthalate-free fragrance oils</t>
@@ -1671,7 +1661,6 @@
           <t>Curated set</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr">
         <is>
           <t>Curated Mysaa Rituals gifting selection</t>
@@ -1749,7 +1738,6 @@
           <t>220 ml</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr">
         <is>
           <t>Natural soy wax, cotton wick, phthalate-free fragrance oils</t>
@@ -1827,7 +1815,6 @@
           <t>120 ml</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr">
         <is>
           <t>Natural soy wax, cotton wick, phthalate-free fragrance oils</t>
@@ -1905,7 +1892,6 @@
           <t>60 ml</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr">
         <is>
           <t>Natural soy wax, cotton wick, phthalate-free fragrance oils</t>
@@ -1983,7 +1969,6 @@
           <t>Combo</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr">
         <is>
           <t>Natural soy wax, cotton wick, phthalate-free fragrance oils</t>
@@ -2061,7 +2046,6 @@
           <t>Curated set</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr">
         <is>
           <t>Curated Mysaa Rituals gifting selection</t>
@@ -2139,7 +2123,6 @@
           <t>220 ml</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr">
         <is>
           <t>Natural soy wax, cotton wick, phthalate-free fragrance oils</t>
@@ -2217,7 +2200,6 @@
           <t>120 ml</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr">
         <is>
           <t>Natural soy wax, cotton wick, phthalate-free fragrance oils</t>
@@ -2295,7 +2277,6 @@
           <t>60 ml</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr">
         <is>
           <t>Natural soy wax, cotton wick, phthalate-free fragrance oils</t>
@@ -2373,7 +2354,6 @@
           <t>Combo</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr">
         <is>
           <t>Natural soy wax, cotton wick, phthalate-free fragrance oils</t>
@@ -2451,7 +2431,6 @@
           <t>Curated set</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr">
         <is>
           <t>Curated Mysaa Rituals gifting selection</t>
@@ -2529,7 +2508,6 @@
           <t>220 ml</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr">
         <is>
           <t>Natural soy wax, cotton wick, phthalate-free fragrance oils</t>
@@ -2607,7 +2585,6 @@
           <t>120 ml</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr">
         <is>
           <t>Natural soy wax, cotton wick, phthalate-free fragrance oils</t>
@@ -2685,7 +2662,6 @@
           <t>60 ml</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr">
         <is>
           <t>Natural soy wax, cotton wick, phthalate-free fragrance oils</t>
@@ -2763,7 +2739,6 @@
           <t>Combo</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr">
         <is>
           <t>Natural soy wax, cotton wick, phthalate-free fragrance oils</t>
@@ -2841,7 +2816,6 @@
           <t>Curated set</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr"/>
       <c r="H21" t="inlineStr">
         <is>
           <t>Curated Mysaa Rituals gifting selection</t>
@@ -2919,7 +2893,6 @@
           <t>220 ml</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr"/>
       <c r="H22" t="inlineStr">
         <is>
           <t>Natural soy wax, cotton wick, phthalate-free fragrance oils</t>
@@ -2997,7 +2970,6 @@
           <t>120 ml</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr"/>
       <c r="H23" t="inlineStr">
         <is>
           <t>Natural soy wax, cotton wick, phthalate-free fragrance oils</t>
@@ -3075,7 +3047,6 @@
           <t>60 ml</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr"/>
       <c r="H24" t="inlineStr">
         <is>
           <t>Natural soy wax, cotton wick, phthalate-free fragrance oils</t>
@@ -3153,7 +3124,6 @@
           <t>Combo</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr"/>
       <c r="H25" t="inlineStr">
         <is>
           <t>Natural soy wax, cotton wick, phthalate-free fragrance oils</t>
@@ -3231,7 +3201,6 @@
           <t>Curated set</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr"/>
       <c r="H26" t="inlineStr">
         <is>
           <t>Curated Mysaa Rituals gifting selection</t>
@@ -3309,7 +3278,6 @@
           <t>220 ml</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr"/>
       <c r="H27" t="inlineStr">
         <is>
           <t>Natural soy wax, cotton wick, phthalate-free fragrance oils</t>
@@ -3387,7 +3355,6 @@
           <t>120 ml</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr"/>
       <c r="H28" t="inlineStr">
         <is>
           <t>Natural soy wax, cotton wick, phthalate-free fragrance oils</t>
@@ -3465,7 +3432,6 @@
           <t>60 ml</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr"/>
       <c r="H29" t="inlineStr">
         <is>
           <t>Natural soy wax, cotton wick, phthalate-free fragrance oils</t>
@@ -3538,8 +3504,6 @@
       <c r="E30" t="n">
         <v>350</v>
       </c>
-      <c r="F30" t="inlineStr"/>
-      <c r="G30" t="inlineStr"/>
       <c r="H30" t="inlineStr">
         <is>
           <t>Natural soy wax, cotton wick, phthalate-free fragrance oils</t>
@@ -3612,8 +3576,6 @@
       <c r="E31" t="n">
         <v>0</v>
       </c>
-      <c r="F31" t="inlineStr"/>
-      <c r="G31" t="inlineStr"/>
       <c r="H31" t="inlineStr">
         <is>
           <t>Natural soy wax, cotton wick, phthalate-free fragrance oils</t>
@@ -3659,6 +3621,84 @@
       <c r="R31" t="inlineStr">
         <is>
           <t>assets/catalogue/saanjh/gift-hampers/03-lifestyle.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>discover-set-6-shot-glass-candles</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Mysaa Rituals Discover Set</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>discovery-set</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>all-fragrances</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>2200</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>6 × 60 ml</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr"/>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Natural soy wax, cotton wick, phthalate-free fragrance oils</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>Discover Set presentation box</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>All six Mysaa Rituals fragrances in six 60 ml shot glass jar candles.</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>A discovery set featuring all six Mysaa Rituals fragrances — six 60 ml shot glass jar candles designed to let you experience the full fragrance collection in one beautiful set.</t>
+        </is>
+      </c>
+      <c r="L32" t="b">
+        <v>0</v>
+      </c>
+      <c r="M32" t="b">
+        <v>1</v>
+      </c>
+      <c r="N32" t="b">
+        <v>0</v>
+      </c>
+      <c r="O32" t="b">
+        <v>1</v>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>assets/catalogue/all-fragrances/discovery-set/01-discover-set.jpg</t>
+        </is>
+      </c>
+      <c r="Q32" t="inlineStr">
+        <is>
+          <t>assets/catalogue/all-fragrances/discovery-set/02-gulab-ki-chitthi.jpg</t>
+        </is>
+      </c>
+      <c r="R32" t="inlineStr">
+        <is>
+          <t>assets/catalogue/all-fragrances/discovery-set/03-dhoop-chandan.jpg</t>
         </is>
       </c>
     </row>
@@ -3906,7 +3946,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:D7"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14.5" outlineLevelRow="5"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="2"/>
@@ -4033,6 +4073,26 @@
         </is>
       </c>
       <c r="D6" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>discovery-set</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Discovery Set</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>6 × 60 ml shot glass candles</t>
+        </is>
+      </c>
+      <c r="D7" t="b">
         <v>1</v>
       </c>
     </row>

--- a/data/mysaa_products.xlsx
+++ b/data/mysaa_products.xlsx
@@ -1088,7 +1088,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
@@ -1110,7 +1109,6 @@
         </is>
       </c>
     </row>
-    <row r="6"/>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
@@ -1195,7 +1193,6 @@
         </is>
       </c>
     </row>
-    <row r="19"/>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
@@ -1214,7 +1211,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R32"/>
+  <dimension ref="A1:S32"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14.5"/>
   <cols>
     <col width="37" customWidth="1" min="1" max="2"/>
@@ -1253,72 +1250,77 @@
           <t>fragranceSlug</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>mrp</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>price</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>volume</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>weight</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>materials</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>packaging</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>shortDescription</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>about</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>bestseller</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>isNew</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>customizable</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>active</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>image1</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>image2</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>image3</t>
         </is>
@@ -1346,56 +1348,59 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>950</v>
-      </c>
-      <c r="F2" t="inlineStr">
+        <v>899</v>
+      </c>
+      <c r="F2" t="n">
+        <v>799</v>
+      </c>
+      <c r="G2" t="inlineStr">
         <is>
           <t>220 ml</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>Natural soy wax, cotton wick, phthalate-free fragrance oils</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="J2" t="inlineStr">
         <is>
           <t>Mysaa Rituals signature packaging</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>Gulab Ki Chitthi in our hero jar candle.</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>A Mysaa Rituals hero jar candle in the Gulab Ki Chitthi fragrance. Made for gifting, rituals and everyday moments.</t>
         </is>
       </c>
-      <c r="L2" t="b">
-        <v>0</v>
-      </c>
       <c r="M2" t="b">
         <v>0</v>
       </c>
       <c r="N2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O2" t="b">
         <v>1</v>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="P2" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q2" t="inlineStr">
         <is>
           <t>assets/catalogue/gulab-ki-chitthi/hero-jar-candle/01-cover.jpg</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="R2" t="inlineStr">
         <is>
           <t>assets/catalogue/gulab-ki-chitthi/hero-jar-candle/02-detail.jpg</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>assets/catalogue/gulab-ki-chitthi/hero-jar-candle/03-lifestyle.jpg</t>
         </is>
@@ -1423,56 +1428,59 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>650</v>
-      </c>
-      <c r="F3" t="inlineStr">
+        <v>699</v>
+      </c>
+      <c r="F3" t="n">
+        <v>549</v>
+      </c>
+      <c r="G3" t="inlineStr">
         <is>
           <t>120 ml</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>Natural soy wax, cotton wick, phthalate-free fragrance oils</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="J3" t="inlineStr">
         <is>
           <t>Mysaa Rituals signature packaging</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>Gulab Ki Chitthi in our wide jar candle.</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>A Mysaa Rituals wide jar candle in the Gulab Ki Chitthi fragrance. Made for gifting, rituals and everyday moments.</t>
         </is>
       </c>
-      <c r="L3" t="b">
-        <v>0</v>
-      </c>
       <c r="M3" t="b">
         <v>0</v>
       </c>
       <c r="N3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O3" t="b">
         <v>1</v>
       </c>
-      <c r="P3" t="inlineStr">
+      <c r="P3" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q3" t="inlineStr">
         <is>
           <t>assets/catalogue/gulab-ki-chitthi/wide-jar-candle/01-cover.jpg</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
+      <c r="R3" t="inlineStr">
         <is>
           <t>assets/catalogue/gulab-ki-chitthi/wide-jar-candle/02-detail.jpg</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr">
+      <c r="S3" t="inlineStr">
         <is>
           <t>assets/catalogue/gulab-ki-chitthi/wide-jar-candle/03-lifestyle.jpg</t>
         </is>
@@ -1500,56 +1508,59 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>350</v>
-      </c>
-      <c r="F4" t="inlineStr">
+        <v>399</v>
+      </c>
+      <c r="F4" t="n">
+        <v>299</v>
+      </c>
+      <c r="G4" t="inlineStr">
         <is>
           <t>60 ml</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="I4" t="inlineStr">
         <is>
           <t>Natural soy wax, cotton wick, phthalate-free fragrance oils</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="J4" t="inlineStr">
         <is>
           <t>Mysaa Rituals signature packaging</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>Gulab Ki Chitthi in our shot glass candle.</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>A Mysaa Rituals shot glass candle in the Gulab Ki Chitthi fragrance. Made for gifting, rituals and everyday moments.</t>
         </is>
       </c>
-      <c r="L4" t="b">
-        <v>0</v>
-      </c>
       <c r="M4" t="b">
         <v>0</v>
       </c>
       <c r="N4" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O4" t="b">
         <v>1</v>
       </c>
-      <c r="P4" t="inlineStr">
+      <c r="P4" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q4" t="inlineStr">
         <is>
           <t>assets/catalogue/gulab-ki-chitthi/shot-glass-candle/01-cover.jpg</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr">
+      <c r="R4" t="inlineStr">
         <is>
           <t>assets/catalogue/gulab-ki-chitthi/shot-glass-candle/02-detail.jpg</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr">
+      <c r="S4" t="inlineStr">
         <is>
           <t>assets/catalogue/gulab-ki-chitthi/shot-glass-candle/03-lifestyle.jpg</t>
         </is>
@@ -1576,57 +1587,57 @@
           <t>gulab-ki-chitthi</t>
         </is>
       </c>
-      <c r="E5" t="n">
+      <c r="F5" t="n">
         <v>350</v>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t>Combo</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="I5" t="inlineStr">
         <is>
           <t>Natural soy wax, cotton wick, phthalate-free fragrance oils</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="J5" t="inlineStr">
         <is>
           <t>Mysaa Rituals signature packaging</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>Gulab Ki Chitthi in our wax sachet combo.</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>A Mysaa Rituals wax sachet combo in the Gulab Ki Chitthi fragrance. Made for gifting, rituals and everyday moments.</t>
         </is>
       </c>
-      <c r="L5" t="b">
-        <v>0</v>
-      </c>
       <c r="M5" t="b">
         <v>0</v>
       </c>
       <c r="N5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O5" t="b">
         <v>1</v>
       </c>
-      <c r="P5" t="inlineStr">
+      <c r="P5" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q5" t="inlineStr">
         <is>
           <t>assets/catalogue/gulab-ki-chitthi/wax-melts/01-cover.jpg</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr">
+      <c r="R5" t="inlineStr">
         <is>
           <t>assets/catalogue/gulab-ki-chitthi/wax-melts/02-detail.jpg</t>
         </is>
       </c>
-      <c r="R5" t="inlineStr">
+      <c r="S5" t="inlineStr">
         <is>
           <t>assets/catalogue/gulab-ki-chitthi/wax-melts/03-lifestyle.jpg</t>
         </is>
@@ -1653,57 +1664,57 @@
           <t>gulab-ki-chitthi</t>
         </is>
       </c>
-      <c r="E6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F6" t="inlineStr">
+      <c r="F6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" t="inlineStr">
         <is>
           <t>Curated set</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="I6" t="inlineStr">
         <is>
           <t>Curated Mysaa Rituals gifting selection</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="J6" t="inlineStr">
         <is>
           <t>Mysaa Rituals signature packaging</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>Gulab Ki Chitthi in our gift hamper.</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>A Mysaa Rituals gift hamper in the Gulab Ki Chitthi fragrance. Made for gifting, rituals and everyday moments.</t>
         </is>
       </c>
-      <c r="L6" t="b">
-        <v>0</v>
-      </c>
       <c r="M6" t="b">
         <v>0</v>
       </c>
       <c r="N6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O6" t="b">
         <v>1</v>
       </c>
-      <c r="P6" t="inlineStr">
+      <c r="P6" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q6" t="inlineStr">
         <is>
           <t>assets/catalogue/gulab-ki-chitthi/gift-hampers/01-cover.jpg</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr">
+      <c r="R6" t="inlineStr">
         <is>
           <t>assets/catalogue/gulab-ki-chitthi/gift-hampers/02-detail.jpg</t>
         </is>
       </c>
-      <c r="R6" t="inlineStr">
+      <c r="S6" t="inlineStr">
         <is>
           <t>assets/catalogue/gulab-ki-chitthi/gift-hampers/03-lifestyle.jpg</t>
         </is>
@@ -1731,56 +1742,59 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>950</v>
-      </c>
-      <c r="F7" t="inlineStr">
+        <v>899</v>
+      </c>
+      <c r="F7" t="n">
+        <v>799</v>
+      </c>
+      <c r="G7" t="inlineStr">
         <is>
           <t>220 ml</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="I7" t="inlineStr">
         <is>
           <t>Natural soy wax, cotton wick, phthalate-free fragrance oils</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
+      <c r="J7" t="inlineStr">
         <is>
           <t>Mysaa Rituals signature packaging</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>Dhoop &amp; Chandan in our hero jar candle.</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>A Mysaa Rituals hero jar candle in the Dhoop &amp; Chandan fragrance. Made for gifting, rituals and everyday moments.</t>
         </is>
       </c>
-      <c r="L7" t="b">
-        <v>0</v>
-      </c>
       <c r="M7" t="b">
         <v>0</v>
       </c>
       <c r="N7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O7" t="b">
         <v>1</v>
       </c>
-      <c r="P7" t="inlineStr">
+      <c r="P7" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q7" t="inlineStr">
         <is>
           <t>assets/catalogue/dhoop-chandan/hero-jar-candle/01-cover.jpg</t>
         </is>
       </c>
-      <c r="Q7" t="inlineStr">
+      <c r="R7" t="inlineStr">
         <is>
           <t>assets/catalogue/dhoop-chandan/hero-jar-candle/02-detail.jpg</t>
         </is>
       </c>
-      <c r="R7" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>assets/catalogue/dhoop-chandan/hero-jar-candle/03-lifestyle.jpg</t>
         </is>
@@ -1808,56 +1822,59 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>650</v>
-      </c>
-      <c r="F8" t="inlineStr">
+        <v>699</v>
+      </c>
+      <c r="F8" t="n">
+        <v>549</v>
+      </c>
+      <c r="G8" t="inlineStr">
         <is>
           <t>120 ml</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="I8" t="inlineStr">
         <is>
           <t>Natural soy wax, cotton wick, phthalate-free fragrance oils</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
+      <c r="J8" t="inlineStr">
         <is>
           <t>Mysaa Rituals signature packaging</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>Dhoop &amp; Chandan in our wide jar candle.</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>A Mysaa Rituals wide jar candle in the Dhoop &amp; Chandan fragrance. Made for gifting, rituals and everyday moments.</t>
         </is>
       </c>
-      <c r="L8" t="b">
-        <v>0</v>
-      </c>
       <c r="M8" t="b">
         <v>0</v>
       </c>
       <c r="N8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O8" t="b">
         <v>1</v>
       </c>
-      <c r="P8" t="inlineStr">
+      <c r="P8" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q8" t="inlineStr">
         <is>
           <t>assets/catalogue/dhoop-chandan/wide-jar-candle/01-cover.jpg</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr">
+      <c r="R8" t="inlineStr">
         <is>
           <t>assets/catalogue/dhoop-chandan/wide-jar-candle/02-detail.jpg</t>
         </is>
       </c>
-      <c r="R8" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>assets/catalogue/dhoop-chandan/wide-jar-candle/03-lifestyle.jpg</t>
         </is>
@@ -1885,56 +1902,59 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>350</v>
-      </c>
-      <c r="F9" t="inlineStr">
+        <v>399</v>
+      </c>
+      <c r="F9" t="n">
+        <v>299</v>
+      </c>
+      <c r="G9" t="inlineStr">
         <is>
           <t>60 ml</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="I9" t="inlineStr">
         <is>
           <t>Natural soy wax, cotton wick, phthalate-free fragrance oils</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
+      <c r="J9" t="inlineStr">
         <is>
           <t>Mysaa Rituals signature packaging</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
+      <c r="K9" t="inlineStr">
         <is>
           <t>Dhoop &amp; Chandan in our shot glass candle.</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t>A Mysaa Rituals shot glass candle in the Dhoop &amp; Chandan fragrance. Made for gifting, rituals and everyday moments.</t>
         </is>
       </c>
-      <c r="L9" t="b">
-        <v>0</v>
-      </c>
       <c r="M9" t="b">
         <v>0</v>
       </c>
       <c r="N9" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O9" t="b">
         <v>1</v>
       </c>
-      <c r="P9" t="inlineStr">
+      <c r="P9" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q9" t="inlineStr">
         <is>
           <t>assets/catalogue/dhoop-chandan/shot-glass-candle/01-cover.jpg</t>
         </is>
       </c>
-      <c r="Q9" t="inlineStr">
+      <c r="R9" t="inlineStr">
         <is>
           <t>assets/catalogue/dhoop-chandan/shot-glass-candle/02-detail.jpg</t>
         </is>
       </c>
-      <c r="R9" t="inlineStr">
+      <c r="S9" t="inlineStr">
         <is>
           <t>assets/catalogue/dhoop-chandan/shot-glass-candle/03-lifestyle.jpg</t>
         </is>
@@ -1961,57 +1981,57 @@
           <t>dhoop-chandan</t>
         </is>
       </c>
-      <c r="E10" t="n">
+      <c r="F10" t="n">
         <v>350</v>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="G10" t="inlineStr">
         <is>
           <t>Combo</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
+      <c r="I10" t="inlineStr">
         <is>
           <t>Natural soy wax, cotton wick, phthalate-free fragrance oils</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
+      <c r="J10" t="inlineStr">
         <is>
           <t>Mysaa Rituals signature packaging</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
+      <c r="K10" t="inlineStr">
         <is>
           <t>Dhoop &amp; Chandan in our wax sachet combo.</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="L10" t="inlineStr">
         <is>
           <t>A Mysaa Rituals wax sachet combo in the Dhoop &amp; Chandan fragrance. Made for gifting, rituals and everyday moments.</t>
         </is>
       </c>
-      <c r="L10" t="b">
-        <v>0</v>
-      </c>
       <c r="M10" t="b">
         <v>0</v>
       </c>
       <c r="N10" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O10" t="b">
         <v>1</v>
       </c>
-      <c r="P10" t="inlineStr">
+      <c r="P10" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q10" t="inlineStr">
         <is>
           <t>assets/catalogue/dhoop-chandan/wax-melts/01-cover.jpg</t>
         </is>
       </c>
-      <c r="Q10" t="inlineStr">
+      <c r="R10" t="inlineStr">
         <is>
           <t>assets/catalogue/dhoop-chandan/wax-melts/02-detail.jpg</t>
         </is>
       </c>
-      <c r="R10" t="inlineStr">
+      <c r="S10" t="inlineStr">
         <is>
           <t>assets/catalogue/dhoop-chandan/wax-melts/03-lifestyle.jpg</t>
         </is>
@@ -2038,57 +2058,57 @@
           <t>dhoop-chandan</t>
         </is>
       </c>
-      <c r="E11" t="n">
-        <v>0</v>
-      </c>
-      <c r="F11" t="inlineStr">
+      <c r="F11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" t="inlineStr">
         <is>
           <t>Curated set</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="I11" t="inlineStr">
         <is>
           <t>Curated Mysaa Rituals gifting selection</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
+      <c r="J11" t="inlineStr">
         <is>
           <t>Mysaa Rituals signature packaging</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr">
+      <c r="K11" t="inlineStr">
         <is>
           <t>Dhoop &amp; Chandan in our gift hamper.</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr">
+      <c r="L11" t="inlineStr">
         <is>
           <t>A Mysaa Rituals gift hamper in the Dhoop &amp; Chandan fragrance. Made for gifting, rituals and everyday moments.</t>
         </is>
       </c>
-      <c r="L11" t="b">
-        <v>0</v>
-      </c>
       <c r="M11" t="b">
         <v>0</v>
       </c>
       <c r="N11" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O11" t="b">
         <v>1</v>
       </c>
-      <c r="P11" t="inlineStr">
+      <c r="P11" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q11" t="inlineStr">
         <is>
           <t>assets/catalogue/dhoop-chandan/gift-hampers/01-cover.jpg</t>
         </is>
       </c>
-      <c r="Q11" t="inlineStr">
+      <c r="R11" t="inlineStr">
         <is>
           <t>assets/catalogue/dhoop-chandan/gift-hampers/02-detail.jpg</t>
         </is>
       </c>
-      <c r="R11" t="inlineStr">
+      <c r="S11" t="inlineStr">
         <is>
           <t>assets/catalogue/dhoop-chandan/gift-hampers/03-lifestyle.jpg</t>
         </is>
@@ -2116,56 +2136,59 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>950</v>
-      </c>
-      <c r="F12" t="inlineStr">
+        <v>899</v>
+      </c>
+      <c r="F12" t="n">
+        <v>799</v>
+      </c>
+      <c r="G12" t="inlineStr">
         <is>
           <t>220 ml</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
+      <c r="I12" t="inlineStr">
         <is>
           <t>Natural soy wax, cotton wick, phthalate-free fragrance oils</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
+      <c r="J12" t="inlineStr">
         <is>
           <t>Mysaa Rituals signature packaging</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr">
+      <c r="K12" t="inlineStr">
         <is>
           <t>Gajre Ka Shringar in our hero jar candle.</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr">
+      <c r="L12" t="inlineStr">
         <is>
           <t>A Mysaa Rituals hero jar candle in the Gajre Ka Shringar fragrance. Made for gifting, rituals and everyday moments.</t>
         </is>
       </c>
-      <c r="L12" t="b">
-        <v>0</v>
-      </c>
       <c r="M12" t="b">
         <v>0</v>
       </c>
       <c r="N12" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O12" t="b">
         <v>1</v>
       </c>
-      <c r="P12" t="inlineStr">
+      <c r="P12" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q12" t="inlineStr">
         <is>
           <t>assets/catalogue/gajre-ka-shringar/hero-jar-candle/01-cover.jpg</t>
         </is>
       </c>
-      <c r="Q12" t="inlineStr">
+      <c r="R12" t="inlineStr">
         <is>
           <t>assets/catalogue/gajre-ka-shringar/hero-jar-candle/02-detail.jpg</t>
         </is>
       </c>
-      <c r="R12" t="inlineStr">
+      <c r="S12" t="inlineStr">
         <is>
           <t>assets/catalogue/gajre-ka-shringar/hero-jar-candle/03-lifestyle.jpg</t>
         </is>
@@ -2193,56 +2216,59 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>650</v>
-      </c>
-      <c r="F13" t="inlineStr">
+        <v>699</v>
+      </c>
+      <c r="F13" t="n">
+        <v>549</v>
+      </c>
+      <c r="G13" t="inlineStr">
         <is>
           <t>120 ml</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
+      <c r="I13" t="inlineStr">
         <is>
           <t>Natural soy wax, cotton wick, phthalate-free fragrance oils</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
+      <c r="J13" t="inlineStr">
         <is>
           <t>Mysaa Rituals signature packaging</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr">
+      <c r="K13" t="inlineStr">
         <is>
           <t>Gajre Ka Shringar in our wide jar candle.</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr">
+      <c r="L13" t="inlineStr">
         <is>
           <t>A Mysaa Rituals wide jar candle in the Gajre Ka Shringar fragrance. Made for gifting, rituals and everyday moments.</t>
         </is>
       </c>
-      <c r="L13" t="b">
-        <v>0</v>
-      </c>
       <c r="M13" t="b">
         <v>0</v>
       </c>
       <c r="N13" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O13" t="b">
         <v>1</v>
       </c>
-      <c r="P13" t="inlineStr">
+      <c r="P13" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q13" t="inlineStr">
         <is>
           <t>assets/catalogue/gajre-ka-shringar/wide-jar-candle/01-cover.jpg</t>
         </is>
       </c>
-      <c r="Q13" t="inlineStr">
+      <c r="R13" t="inlineStr">
         <is>
           <t>assets/catalogue/gajre-ka-shringar/wide-jar-candle/02-detail.jpg</t>
         </is>
       </c>
-      <c r="R13" t="inlineStr">
+      <c r="S13" t="inlineStr">
         <is>
           <t>assets/catalogue/gajre-ka-shringar/wide-jar-candle/03-lifestyle.jpg</t>
         </is>
@@ -2270,56 +2296,59 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>350</v>
-      </c>
-      <c r="F14" t="inlineStr">
+        <v>399</v>
+      </c>
+      <c r="F14" t="n">
+        <v>299</v>
+      </c>
+      <c r="G14" t="inlineStr">
         <is>
           <t>60 ml</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
+      <c r="I14" t="inlineStr">
         <is>
           <t>Natural soy wax, cotton wick, phthalate-free fragrance oils</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
+      <c r="J14" t="inlineStr">
         <is>
           <t>Mysaa Rituals signature packaging</t>
         </is>
       </c>
-      <c r="J14" t="inlineStr">
+      <c r="K14" t="inlineStr">
         <is>
           <t>Gajre Ka Shringar in our shot glass candle.</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr">
+      <c r="L14" t="inlineStr">
         <is>
           <t>A Mysaa Rituals shot glass candle in the Gajre Ka Shringar fragrance. Made for gifting, rituals and everyday moments.</t>
         </is>
       </c>
-      <c r="L14" t="b">
-        <v>0</v>
-      </c>
       <c r="M14" t="b">
         <v>0</v>
       </c>
       <c r="N14" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O14" t="b">
         <v>1</v>
       </c>
-      <c r="P14" t="inlineStr">
+      <c r="P14" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q14" t="inlineStr">
         <is>
           <t>assets/catalogue/gajre-ka-shringar/shot-glass-candle/01-cover.jpg</t>
         </is>
       </c>
-      <c r="Q14" t="inlineStr">
+      <c r="R14" t="inlineStr">
         <is>
           <t>assets/catalogue/gajre-ka-shringar/shot-glass-candle/02-detail.jpg</t>
         </is>
       </c>
-      <c r="R14" t="inlineStr">
+      <c r="S14" t="inlineStr">
         <is>
           <t>assets/catalogue/gajre-ka-shringar/shot-glass-candle/03-lifestyle.jpg</t>
         </is>
@@ -2346,57 +2375,57 @@
           <t>gajre-ka-shringar</t>
         </is>
       </c>
-      <c r="E15" t="n">
+      <c r="F15" t="n">
         <v>350</v>
       </c>
-      <c r="F15" t="inlineStr">
+      <c r="G15" t="inlineStr">
         <is>
           <t>Combo</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
+      <c r="I15" t="inlineStr">
         <is>
           <t>Natural soy wax, cotton wick, phthalate-free fragrance oils</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr">
+      <c r="J15" t="inlineStr">
         <is>
           <t>Mysaa Rituals signature packaging</t>
         </is>
       </c>
-      <c r="J15" t="inlineStr">
+      <c r="K15" t="inlineStr">
         <is>
           <t>Gajre Ka Shringar in our wax sachet combo.</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr">
+      <c r="L15" t="inlineStr">
         <is>
           <t>A Mysaa Rituals wax sachet combo in the Gajre Ka Shringar fragrance. Made for gifting, rituals and everyday moments.</t>
         </is>
       </c>
-      <c r="L15" t="b">
-        <v>0</v>
-      </c>
       <c r="M15" t="b">
         <v>0</v>
       </c>
       <c r="N15" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O15" t="b">
         <v>1</v>
       </c>
-      <c r="P15" t="inlineStr">
+      <c r="P15" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q15" t="inlineStr">
         <is>
           <t>assets/catalogue/gajre-ka-shringar/wax-melts/01-cover.jpg</t>
         </is>
       </c>
-      <c r="Q15" t="inlineStr">
+      <c r="R15" t="inlineStr">
         <is>
           <t>assets/catalogue/gajre-ka-shringar/wax-melts/02-detail.jpg</t>
         </is>
       </c>
-      <c r="R15" t="inlineStr">
+      <c r="S15" t="inlineStr">
         <is>
           <t>assets/catalogue/gajre-ka-shringar/wax-melts/03-lifestyle.jpg</t>
         </is>
@@ -2423,57 +2452,57 @@
           <t>gajre-ka-shringar</t>
         </is>
       </c>
-      <c r="E16" t="n">
-        <v>0</v>
-      </c>
-      <c r="F16" t="inlineStr">
+      <c r="F16" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" t="inlineStr">
         <is>
           <t>Curated set</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
+      <c r="I16" t="inlineStr">
         <is>
           <t>Curated Mysaa Rituals gifting selection</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr">
+      <c r="J16" t="inlineStr">
         <is>
           <t>Mysaa Rituals signature packaging</t>
         </is>
       </c>
-      <c r="J16" t="inlineStr">
+      <c r="K16" t="inlineStr">
         <is>
           <t>Gajre Ka Shringar in our gift hamper.</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr">
+      <c r="L16" t="inlineStr">
         <is>
           <t>A Mysaa Rituals gift hamper in the Gajre Ka Shringar fragrance. Made for gifting, rituals and everyday moments.</t>
         </is>
       </c>
-      <c r="L16" t="b">
-        <v>0</v>
-      </c>
       <c r="M16" t="b">
         <v>0</v>
       </c>
       <c r="N16" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O16" t="b">
         <v>1</v>
       </c>
-      <c r="P16" t="inlineStr">
+      <c r="P16" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q16" t="inlineStr">
         <is>
           <t>assets/catalogue/gajre-ka-shringar/gift-hampers/01-cover.jpg</t>
         </is>
       </c>
-      <c r="Q16" t="inlineStr">
+      <c r="R16" t="inlineStr">
         <is>
           <t>assets/catalogue/gajre-ka-shringar/gift-hampers/02-detail.jpg</t>
         </is>
       </c>
-      <c r="R16" t="inlineStr">
+      <c r="S16" t="inlineStr">
         <is>
           <t>assets/catalogue/gajre-ka-shringar/gift-hampers/03-lifestyle.jpg</t>
         </is>
@@ -2501,56 +2530,59 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1050</v>
-      </c>
-      <c r="F17" t="inlineStr">
+        <v>899</v>
+      </c>
+      <c r="F17" t="n">
+        <v>799</v>
+      </c>
+      <c r="G17" t="inlineStr">
         <is>
           <t>220 ml</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
+      <c r="I17" t="inlineStr">
         <is>
           <t>Natural soy wax, cotton wick, phthalate-free fragrance oils</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr">
+      <c r="J17" t="inlineStr">
         <is>
           <t>Mysaa Rituals signature packaging</t>
         </is>
       </c>
-      <c r="J17" t="inlineStr">
+      <c r="K17" t="inlineStr">
         <is>
           <t>Madhuban in our hero jar candle.</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr">
+      <c r="L17" t="inlineStr">
         <is>
           <t>A Mysaa Rituals hero jar candle in the Madhuban fragrance. Made for gifting, rituals and everyday moments.</t>
         </is>
       </c>
-      <c r="L17" t="b">
-        <v>0</v>
-      </c>
       <c r="M17" t="b">
         <v>0</v>
       </c>
       <c r="N17" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O17" t="b">
         <v>1</v>
       </c>
-      <c r="P17" t="inlineStr">
+      <c r="P17" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q17" t="inlineStr">
         <is>
           <t>assets/catalogue/madhuban/hero-jar-candle/01-cover.jpg</t>
         </is>
       </c>
-      <c r="Q17" t="inlineStr">
+      <c r="R17" t="inlineStr">
         <is>
           <t>assets/catalogue/madhuban/hero-jar-candle/02-detail.jpg</t>
         </is>
       </c>
-      <c r="R17" t="inlineStr">
+      <c r="S17" t="inlineStr">
         <is>
           <t>assets/catalogue/madhuban/hero-jar-candle/03-lifestyle.jpg</t>
         </is>
@@ -2578,56 +2610,59 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>650</v>
-      </c>
-      <c r="F18" t="inlineStr">
+        <v>699</v>
+      </c>
+      <c r="F18" t="n">
+        <v>549</v>
+      </c>
+      <c r="G18" t="inlineStr">
         <is>
           <t>120 ml</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
+      <c r="I18" t="inlineStr">
         <is>
           <t>Natural soy wax, cotton wick, phthalate-free fragrance oils</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr">
+      <c r="J18" t="inlineStr">
         <is>
           <t>Mysaa Rituals signature packaging</t>
         </is>
       </c>
-      <c r="J18" t="inlineStr">
+      <c r="K18" t="inlineStr">
         <is>
           <t>Madhuban in our wide jar candle.</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr">
+      <c r="L18" t="inlineStr">
         <is>
           <t>A Mysaa Rituals wide jar candle in the Madhuban fragrance. Made for gifting, rituals and everyday moments.</t>
         </is>
       </c>
-      <c r="L18" t="b">
-        <v>0</v>
-      </c>
       <c r="M18" t="b">
         <v>0</v>
       </c>
       <c r="N18" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O18" t="b">
         <v>1</v>
       </c>
-      <c r="P18" t="inlineStr">
+      <c r="P18" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q18" t="inlineStr">
         <is>
           <t>assets/catalogue/madhuban/wide-jar-candle/01-cover.jpg</t>
         </is>
       </c>
-      <c r="Q18" t="inlineStr">
+      <c r="R18" t="inlineStr">
         <is>
           <t>assets/catalogue/madhuban/wide-jar-candle/02-detail.jpg</t>
         </is>
       </c>
-      <c r="R18" t="inlineStr">
+      <c r="S18" t="inlineStr">
         <is>
           <t>assets/catalogue/madhuban/wide-jar-candle/03-lifestyle.jpg</t>
         </is>
@@ -2655,56 +2690,59 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>350</v>
-      </c>
-      <c r="F19" t="inlineStr">
+        <v>399</v>
+      </c>
+      <c r="F19" t="n">
+        <v>299</v>
+      </c>
+      <c r="G19" t="inlineStr">
         <is>
           <t>60 ml</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
+      <c r="I19" t="inlineStr">
         <is>
           <t>Natural soy wax, cotton wick, phthalate-free fragrance oils</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr">
+      <c r="J19" t="inlineStr">
         <is>
           <t>Mysaa Rituals signature packaging</t>
         </is>
       </c>
-      <c r="J19" t="inlineStr">
+      <c r="K19" t="inlineStr">
         <is>
           <t>Madhuban in our shot glass candle.</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr">
+      <c r="L19" t="inlineStr">
         <is>
           <t>A Mysaa Rituals shot glass candle in the Madhuban fragrance. Made for gifting, rituals and everyday moments.</t>
         </is>
       </c>
-      <c r="L19" t="b">
-        <v>0</v>
-      </c>
       <c r="M19" t="b">
         <v>0</v>
       </c>
       <c r="N19" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O19" t="b">
         <v>1</v>
       </c>
-      <c r="P19" t="inlineStr">
+      <c r="P19" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q19" t="inlineStr">
         <is>
           <t>assets/catalogue/madhuban/shot-glass-candle/01-cover.jpg</t>
         </is>
       </c>
-      <c r="Q19" t="inlineStr">
+      <c r="R19" t="inlineStr">
         <is>
           <t>assets/catalogue/madhuban/shot-glass-candle/02-detail.jpg</t>
         </is>
       </c>
-      <c r="R19" t="inlineStr">
+      <c r="S19" t="inlineStr">
         <is>
           <t>assets/catalogue/madhuban/shot-glass-candle/03-lifestyle.jpg</t>
         </is>
@@ -2731,57 +2769,57 @@
           <t>madhuban</t>
         </is>
       </c>
-      <c r="E20" t="n">
+      <c r="F20" t="n">
         <v>350</v>
       </c>
-      <c r="F20" t="inlineStr">
+      <c r="G20" t="inlineStr">
         <is>
           <t>Combo</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr">
+      <c r="I20" t="inlineStr">
         <is>
           <t>Natural soy wax, cotton wick, phthalate-free fragrance oils</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr">
+      <c r="J20" t="inlineStr">
         <is>
           <t>Mysaa Rituals signature packaging</t>
         </is>
       </c>
-      <c r="J20" t="inlineStr">
+      <c r="K20" t="inlineStr">
         <is>
           <t>Madhuban in our wax sachet combo.</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr">
+      <c r="L20" t="inlineStr">
         <is>
           <t>A Mysaa Rituals wax sachet combo in the Madhuban fragrance. Made for gifting, rituals and everyday moments.</t>
         </is>
       </c>
-      <c r="L20" t="b">
-        <v>0</v>
-      </c>
       <c r="M20" t="b">
         <v>0</v>
       </c>
       <c r="N20" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O20" t="b">
         <v>1</v>
       </c>
-      <c r="P20" t="inlineStr">
+      <c r="P20" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q20" t="inlineStr">
         <is>
           <t>assets/catalogue/madhuban/wax-melts/01-cover.jpg</t>
         </is>
       </c>
-      <c r="Q20" t="inlineStr">
+      <c r="R20" t="inlineStr">
         <is>
           <t>assets/catalogue/madhuban/wax-melts/02-detail.jpg</t>
         </is>
       </c>
-      <c r="R20" t="inlineStr">
+      <c r="S20" t="inlineStr">
         <is>
           <t>assets/catalogue/madhuban/wax-melts/03-lifestyle.jpg</t>
         </is>
@@ -2808,57 +2846,57 @@
           <t>madhuban</t>
         </is>
       </c>
-      <c r="E21" t="n">
-        <v>0</v>
-      </c>
-      <c r="F21" t="inlineStr">
+      <c r="F21" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" t="inlineStr">
         <is>
           <t>Curated set</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
+      <c r="I21" t="inlineStr">
         <is>
           <t>Curated Mysaa Rituals gifting selection</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr">
+      <c r="J21" t="inlineStr">
         <is>
           <t>Mysaa Rituals signature packaging</t>
         </is>
       </c>
-      <c r="J21" t="inlineStr">
+      <c r="K21" t="inlineStr">
         <is>
           <t>Madhuban in our gift hamper.</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr">
+      <c r="L21" t="inlineStr">
         <is>
           <t>A Mysaa Rituals gift hamper in the Madhuban fragrance. Made for gifting, rituals and everyday moments.</t>
         </is>
       </c>
-      <c r="L21" t="b">
-        <v>0</v>
-      </c>
       <c r="M21" t="b">
         <v>0</v>
       </c>
       <c r="N21" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O21" t="b">
         <v>1</v>
       </c>
-      <c r="P21" t="inlineStr">
+      <c r="P21" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q21" t="inlineStr">
         <is>
           <t>assets/catalogue/madhuban/gift-hampers/01-cover.jpg</t>
         </is>
       </c>
-      <c r="Q21" t="inlineStr">
+      <c r="R21" t="inlineStr">
         <is>
           <t>assets/catalogue/madhuban/gift-hampers/02-detail.jpg</t>
         </is>
       </c>
-      <c r="R21" t="inlineStr">
+      <c r="S21" t="inlineStr">
         <is>
           <t>assets/catalogue/madhuban/gift-hampers/03-lifestyle.jpg</t>
         </is>
@@ -2886,56 +2924,59 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>950</v>
-      </c>
-      <c r="F22" t="inlineStr">
+        <v>899</v>
+      </c>
+      <c r="F22" t="n">
+        <v>799</v>
+      </c>
+      <c r="G22" t="inlineStr">
         <is>
           <t>220 ml</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
+      <c r="I22" t="inlineStr">
         <is>
           <t>Natural soy wax, cotton wick, phthalate-free fragrance oils</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr">
+      <c r="J22" t="inlineStr">
         <is>
           <t>Mysaa Rituals signature packaging</t>
         </is>
       </c>
-      <c r="J22" t="inlineStr">
+      <c r="K22" t="inlineStr">
         <is>
           <t>Raat Ki Rani in our hero jar candle.</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr">
+      <c r="L22" t="inlineStr">
         <is>
           <t>A Mysaa Rituals hero jar candle in the Raat Ki Rani fragrance. Made for gifting, rituals and everyday moments.</t>
         </is>
       </c>
-      <c r="L22" t="b">
-        <v>0</v>
-      </c>
       <c r="M22" t="b">
         <v>0</v>
       </c>
       <c r="N22" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O22" t="b">
         <v>1</v>
       </c>
-      <c r="P22" t="inlineStr">
+      <c r="P22" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q22" t="inlineStr">
         <is>
           <t>assets/catalogue/raat-ki-rani/hero-jar-candle/01-cover.jpg</t>
         </is>
       </c>
-      <c r="Q22" t="inlineStr">
+      <c r="R22" t="inlineStr">
         <is>
           <t>assets/catalogue/raat-ki-rani/hero-jar-candle/02-detail.jpg</t>
         </is>
       </c>
-      <c r="R22" t="inlineStr">
+      <c r="S22" t="inlineStr">
         <is>
           <t>assets/catalogue/raat-ki-rani/hero-jar-candle/03-lifestyle.jpg</t>
         </is>
@@ -2963,56 +3004,59 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>650</v>
-      </c>
-      <c r="F23" t="inlineStr">
+        <v>699</v>
+      </c>
+      <c r="F23" t="n">
+        <v>549</v>
+      </c>
+      <c r="G23" t="inlineStr">
         <is>
           <t>120 ml</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr">
+      <c r="I23" t="inlineStr">
         <is>
           <t>Natural soy wax, cotton wick, phthalate-free fragrance oils</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr">
+      <c r="J23" t="inlineStr">
         <is>
           <t>Mysaa Rituals signature packaging</t>
         </is>
       </c>
-      <c r="J23" t="inlineStr">
+      <c r="K23" t="inlineStr">
         <is>
           <t>Raat Ki Rani in our wide jar candle.</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr">
+      <c r="L23" t="inlineStr">
         <is>
           <t>A Mysaa Rituals wide jar candle in the Raat Ki Rani fragrance. Made for gifting, rituals and everyday moments.</t>
         </is>
       </c>
-      <c r="L23" t="b">
-        <v>0</v>
-      </c>
       <c r="M23" t="b">
         <v>0</v>
       </c>
       <c r="N23" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O23" t="b">
         <v>1</v>
       </c>
-      <c r="P23" t="inlineStr">
+      <c r="P23" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q23" t="inlineStr">
         <is>
           <t>assets/catalogue/raat-ki-rani/wide-jar-candle/01-cover.jpg</t>
         </is>
       </c>
-      <c r="Q23" t="inlineStr">
+      <c r="R23" t="inlineStr">
         <is>
           <t>assets/catalogue/raat-ki-rani/wide-jar-candle/02-detail.jpg</t>
         </is>
       </c>
-      <c r="R23" t="inlineStr">
+      <c r="S23" t="inlineStr">
         <is>
           <t>assets/catalogue/raat-ki-rani/wide-jar-candle/03-lifestyle.jpg</t>
         </is>
@@ -3040,56 +3084,59 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>350</v>
-      </c>
-      <c r="F24" t="inlineStr">
+        <v>399</v>
+      </c>
+      <c r="F24" t="n">
+        <v>299</v>
+      </c>
+      <c r="G24" t="inlineStr">
         <is>
           <t>60 ml</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr">
+      <c r="I24" t="inlineStr">
         <is>
           <t>Natural soy wax, cotton wick, phthalate-free fragrance oils</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr">
+      <c r="J24" t="inlineStr">
         <is>
           <t>Mysaa Rituals signature packaging</t>
         </is>
       </c>
-      <c r="J24" t="inlineStr">
+      <c r="K24" t="inlineStr">
         <is>
           <t>Raat Ki Rani in our shot glass candle.</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr">
+      <c r="L24" t="inlineStr">
         <is>
           <t>A Mysaa Rituals shot glass candle in the Raat Ki Rani fragrance. Made for gifting, rituals and everyday moments.</t>
         </is>
       </c>
-      <c r="L24" t="b">
-        <v>0</v>
-      </c>
       <c r="M24" t="b">
         <v>0</v>
       </c>
       <c r="N24" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O24" t="b">
         <v>1</v>
       </c>
-      <c r="P24" t="inlineStr">
+      <c r="P24" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q24" t="inlineStr">
         <is>
           <t>assets/catalogue/raat-ki-rani/shot-glass-candle/01-cover.jpg</t>
         </is>
       </c>
-      <c r="Q24" t="inlineStr">
+      <c r="R24" t="inlineStr">
         <is>
           <t>assets/catalogue/raat-ki-rani/shot-glass-candle/02-detail.jpg</t>
         </is>
       </c>
-      <c r="R24" t="inlineStr">
+      <c r="S24" t="inlineStr">
         <is>
           <t>assets/catalogue/raat-ki-rani/shot-glass-candle/03-lifestyle.jpg</t>
         </is>
@@ -3116,57 +3163,57 @@
           <t>raat-ki-rani</t>
         </is>
       </c>
-      <c r="E25" t="n">
+      <c r="F25" t="n">
         <v>350</v>
       </c>
-      <c r="F25" t="inlineStr">
+      <c r="G25" t="inlineStr">
         <is>
           <t>Combo</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr">
+      <c r="I25" t="inlineStr">
         <is>
           <t>Natural soy wax, cotton wick, phthalate-free fragrance oils</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr">
+      <c r="J25" t="inlineStr">
         <is>
           <t>Mysaa Rituals signature packaging</t>
         </is>
       </c>
-      <c r="J25" t="inlineStr">
+      <c r="K25" t="inlineStr">
         <is>
           <t>Raat Ki Rani in our wax sachet combo.</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr">
+      <c r="L25" t="inlineStr">
         <is>
           <t>A Mysaa Rituals wax sachet combo in the Raat Ki Rani fragrance. Made for gifting, rituals and everyday moments.</t>
         </is>
       </c>
-      <c r="L25" t="b">
-        <v>0</v>
-      </c>
       <c r="M25" t="b">
         <v>0</v>
       </c>
       <c r="N25" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O25" t="b">
         <v>1</v>
       </c>
-      <c r="P25" t="inlineStr">
+      <c r="P25" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q25" t="inlineStr">
         <is>
           <t>assets/catalogue/raat-ki-rani/wax-melts/01-cover.jpg</t>
         </is>
       </c>
-      <c r="Q25" t="inlineStr">
+      <c r="R25" t="inlineStr">
         <is>
           <t>assets/catalogue/raat-ki-rani/wax-melts/02-detail.jpg</t>
         </is>
       </c>
-      <c r="R25" t="inlineStr">
+      <c r="S25" t="inlineStr">
         <is>
           <t>assets/catalogue/raat-ki-rani/wax-melts/03-lifestyle.jpg</t>
         </is>
@@ -3193,57 +3240,57 @@
           <t>raat-ki-rani</t>
         </is>
       </c>
-      <c r="E26" t="n">
-        <v>0</v>
-      </c>
-      <c r="F26" t="inlineStr">
+      <c r="F26" t="n">
+        <v>0</v>
+      </c>
+      <c r="G26" t="inlineStr">
         <is>
           <t>Curated set</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr">
+      <c r="I26" t="inlineStr">
         <is>
           <t>Curated Mysaa Rituals gifting selection</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr">
+      <c r="J26" t="inlineStr">
         <is>
           <t>Mysaa Rituals signature packaging</t>
         </is>
       </c>
-      <c r="J26" t="inlineStr">
+      <c r="K26" t="inlineStr">
         <is>
           <t>Raat Ki Rani in our gift hamper.</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr">
+      <c r="L26" t="inlineStr">
         <is>
           <t>A Mysaa Rituals gift hamper in the Raat Ki Rani fragrance. Made for gifting, rituals and everyday moments.</t>
         </is>
       </c>
-      <c r="L26" t="b">
-        <v>0</v>
-      </c>
       <c r="M26" t="b">
         <v>0</v>
       </c>
       <c r="N26" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O26" t="b">
         <v>1</v>
       </c>
-      <c r="P26" t="inlineStr">
+      <c r="P26" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q26" t="inlineStr">
         <is>
           <t>assets/catalogue/raat-ki-rani/gift-hampers/01-cover.jpg</t>
         </is>
       </c>
-      <c r="Q26" t="inlineStr">
+      <c r="R26" t="inlineStr">
         <is>
           <t>assets/catalogue/raat-ki-rani/gift-hampers/02-detail.jpg</t>
         </is>
       </c>
-      <c r="R26" t="inlineStr">
+      <c r="S26" t="inlineStr">
         <is>
           <t>assets/catalogue/raat-ki-rani/gift-hampers/03-lifestyle.jpg</t>
         </is>
@@ -3271,56 +3318,59 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>950</v>
-      </c>
-      <c r="F27" t="inlineStr">
+        <v>899</v>
+      </c>
+      <c r="F27" t="n">
+        <v>799</v>
+      </c>
+      <c r="G27" t="inlineStr">
         <is>
           <t>220 ml</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr">
+      <c r="I27" t="inlineStr">
         <is>
           <t>Natural soy wax, cotton wick, phthalate-free fragrance oils</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr">
+      <c r="J27" t="inlineStr">
         <is>
           <t>Mysaa Rituals signature packaging</t>
         </is>
       </c>
-      <c r="J27" t="inlineStr">
+      <c r="K27" t="inlineStr">
         <is>
           <t>Saanjh in our hero jar candle.</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr">
+      <c r="L27" t="inlineStr">
         <is>
           <t>A Mysaa Rituals hero jar candle in the Saanjh fragrance — creamy vanilla softened by deep sandalwood, made for gifting, rituals and everyday moments.</t>
         </is>
       </c>
-      <c r="L27" t="b">
-        <v>0</v>
-      </c>
       <c r="M27" t="b">
         <v>0</v>
       </c>
       <c r="N27" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O27" t="b">
         <v>1</v>
       </c>
-      <c r="P27" t="inlineStr">
+      <c r="P27" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q27" t="inlineStr">
         <is>
           <t>assets/catalogue/saanjh/hero-jar-candle/01-cover.jpg</t>
         </is>
       </c>
-      <c r="Q27" t="inlineStr">
+      <c r="R27" t="inlineStr">
         <is>
           <t>assets/catalogue/saanjh/hero-jar-candle/02-detail.jpg</t>
         </is>
       </c>
-      <c r="R27" t="inlineStr">
+      <c r="S27" t="inlineStr">
         <is>
           <t>assets/catalogue/saanjh/hero-jar-candle/03-lifestyle.jpg</t>
         </is>
@@ -3348,38 +3398,38 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>650</v>
-      </c>
-      <c r="F28" t="inlineStr">
+        <v>699</v>
+      </c>
+      <c r="F28" t="n">
+        <v>549</v>
+      </c>
+      <c r="G28" t="inlineStr">
         <is>
           <t>120 ml</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr">
+      <c r="I28" t="inlineStr">
         <is>
           <t>Natural soy wax, cotton wick, phthalate-free fragrance oils</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr">
+      <c r="J28" t="inlineStr">
         <is>
           <t>Mysaa Rituals signature packaging</t>
         </is>
       </c>
-      <c r="J28" t="inlineStr">
+      <c r="K28" t="inlineStr">
         <is>
           <t>Saanjh in our wide jar candle.</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr">
+      <c r="L28" t="inlineStr">
         <is>
           <t>A Mysaa Rituals wide jar candle in the Saanjh fragrance — creamy vanilla softened by deep sandalwood, made for gifting, rituals and everyday moments.</t>
         </is>
       </c>
-      <c r="L28" t="b">
-        <v>0</v>
-      </c>
       <c r="M28" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N28" t="b">
         <v>1</v>
@@ -3387,17 +3437,20 @@
       <c r="O28" t="b">
         <v>1</v>
       </c>
-      <c r="P28" t="inlineStr">
+      <c r="P28" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q28" t="inlineStr">
         <is>
           <t>assets/catalogue/saanjh/wide-jar-candle/01-cover.jpg</t>
         </is>
       </c>
-      <c r="Q28" t="inlineStr">
+      <c r="R28" t="inlineStr">
         <is>
           <t>assets/catalogue/saanjh/wide-jar-candle/02-detail.jpg</t>
         </is>
       </c>
-      <c r="R28" t="inlineStr">
+      <c r="S28" t="inlineStr">
         <is>
           <t>assets/catalogue/saanjh/wide-jar-candle/03-lifestyle.jpg</t>
         </is>
@@ -3425,56 +3478,59 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>350</v>
-      </c>
-      <c r="F29" t="inlineStr">
+        <v>399</v>
+      </c>
+      <c r="F29" t="n">
+        <v>299</v>
+      </c>
+      <c r="G29" t="inlineStr">
         <is>
           <t>60 ml</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr">
+      <c r="I29" t="inlineStr">
         <is>
           <t>Natural soy wax, cotton wick, phthalate-free fragrance oils</t>
         </is>
       </c>
-      <c r="I29" t="inlineStr">
+      <c r="J29" t="inlineStr">
         <is>
           <t>Mysaa Rituals signature packaging</t>
         </is>
       </c>
-      <c r="J29" t="inlineStr">
+      <c r="K29" t="inlineStr">
         <is>
           <t>Saanjh in our shot glass candle.</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr">
+      <c r="L29" t="inlineStr">
         <is>
           <t>A Mysaa Rituals shot glass candle in the Saanjh fragrance — creamy vanilla softened by deep sandalwood, made for gifting, rituals and everyday moments.</t>
         </is>
       </c>
-      <c r="L29" t="b">
-        <v>0</v>
-      </c>
       <c r="M29" t="b">
         <v>0</v>
       </c>
       <c r="N29" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O29" t="b">
         <v>1</v>
       </c>
-      <c r="P29" t="inlineStr">
+      <c r="P29" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q29" t="inlineStr">
         <is>
           <t>assets/catalogue/saanjh/shot-glass-candle/01-cover.jpg</t>
         </is>
       </c>
-      <c r="Q29" t="inlineStr">
+      <c r="R29" t="inlineStr">
         <is>
           <t>assets/catalogue/saanjh/shot-glass-candle/02-detail.jpg</t>
         </is>
       </c>
-      <c r="R29" t="inlineStr">
+      <c r="S29" t="inlineStr">
         <is>
           <t>assets/catalogue/saanjh/shot-glass-candle/03-lifestyle.jpg</t>
         </is>
@@ -3501,52 +3557,52 @@
           <t>saanjh</t>
         </is>
       </c>
-      <c r="E30" t="n">
+      <c r="F30" t="n">
         <v>350</v>
       </c>
-      <c r="H30" t="inlineStr">
+      <c r="I30" t="inlineStr">
         <is>
           <t>Natural soy wax, cotton wick, phthalate-free fragrance oils</t>
         </is>
       </c>
-      <c r="I30" t="inlineStr">
+      <c r="J30" t="inlineStr">
         <is>
           <t>Mysaa Rituals signature packaging</t>
         </is>
       </c>
-      <c r="J30" t="inlineStr">
+      <c r="K30" t="inlineStr">
         <is>
           <t>Saanjh in our wax sachet combo.</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr">
+      <c r="L30" t="inlineStr">
         <is>
           <t>A Mysaa Rituals wax sachet combo in the Saanjh fragrance — creamy vanilla softened by deep sandalwood, made for gifting, rituals and everyday moments.</t>
         </is>
       </c>
-      <c r="L30" t="b">
-        <v>0</v>
-      </c>
       <c r="M30" t="b">
         <v>0</v>
       </c>
       <c r="N30" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O30" t="b">
         <v>1</v>
       </c>
-      <c r="P30" t="inlineStr">
+      <c r="P30" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q30" t="inlineStr">
         <is>
           <t>assets/catalogue/saanjh/wax-melts/01-cover.jpg</t>
         </is>
       </c>
-      <c r="Q30" t="inlineStr">
+      <c r="R30" t="inlineStr">
         <is>
           <t>assets/catalogue/saanjh/wax-melts/02-detail.jpg</t>
         </is>
       </c>
-      <c r="R30" t="inlineStr">
+      <c r="S30" t="inlineStr">
         <is>
           <t>assets/catalogue/saanjh/wax-melts/03-lifestyle.jpg</t>
         </is>
@@ -3573,52 +3629,52 @@
           <t>saanjh</t>
         </is>
       </c>
-      <c r="E31" t="n">
-        <v>0</v>
-      </c>
-      <c r="H31" t="inlineStr">
+      <c r="F31" t="n">
+        <v>0</v>
+      </c>
+      <c r="I31" t="inlineStr">
         <is>
           <t>Natural soy wax, cotton wick, phthalate-free fragrance oils</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr">
+      <c r="J31" t="inlineStr">
         <is>
           <t>Mysaa Rituals signature packaging</t>
         </is>
       </c>
-      <c r="J31" t="inlineStr">
+      <c r="K31" t="inlineStr">
         <is>
           <t>Saanjh in our gift hamper.</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr">
+      <c r="L31" t="inlineStr">
         <is>
           <t>A Mysaa Rituals gift hamper in the Saanjh fragrance — creamy vanilla softened by deep sandalwood, made for gifting, rituals and everyday moments.</t>
         </is>
       </c>
-      <c r="L31" t="b">
-        <v>0</v>
-      </c>
       <c r="M31" t="b">
         <v>0</v>
       </c>
       <c r="N31" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O31" t="b">
         <v>1</v>
       </c>
-      <c r="P31" t="inlineStr">
+      <c r="P31" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q31" t="inlineStr">
         <is>
           <t>assets/catalogue/saanjh/gift-hampers/01-cover.jpg</t>
         </is>
       </c>
-      <c r="Q31" t="inlineStr">
+      <c r="R31" t="inlineStr">
         <is>
           <t>assets/catalogue/saanjh/gift-hampers/02-detail.jpg</t>
         </is>
       </c>
-      <c r="R31" t="inlineStr">
+      <c r="S31" t="inlineStr">
         <is>
           <t>assets/catalogue/saanjh/gift-hampers/03-lifestyle.jpg</t>
         </is>
@@ -3646,57 +3702,59 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>2200</v>
-      </c>
-      <c r="F32" t="inlineStr">
+        <v>1999</v>
+      </c>
+      <c r="F32" t="n">
+        <v>1699</v>
+      </c>
+      <c r="G32" t="inlineStr">
         <is>
           <t>6 × 60 ml</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr"/>
-      <c r="H32" t="inlineStr">
+      <c r="I32" t="inlineStr">
         <is>
           <t>Natural soy wax, cotton wick, phthalate-free fragrance oils</t>
         </is>
       </c>
-      <c r="I32" t="inlineStr">
+      <c r="J32" t="inlineStr">
         <is>
           <t>Discover Set presentation box</t>
         </is>
       </c>
-      <c r="J32" t="inlineStr">
+      <c r="K32" t="inlineStr">
         <is>
           <t>All six Mysaa Rituals fragrances in six 60 ml shot glass jar candles.</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr">
+      <c r="L32" t="inlineStr">
         <is>
           <t>A discovery set featuring all six Mysaa Rituals fragrances — six 60 ml shot glass jar candles designed to let you experience the full fragrance collection in one beautiful set.</t>
         </is>
       </c>
-      <c r="L32" t="b">
-        <v>0</v>
-      </c>
       <c r="M32" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N32" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O32" t="b">
-        <v>1</v>
-      </c>
-      <c r="P32" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="P32" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q32" t="inlineStr">
         <is>
           <t>assets/catalogue/all-fragrances/discovery-set/01-discover-set.jpg</t>
         </is>
       </c>
-      <c r="Q32" t="inlineStr">
+      <c r="R32" t="inlineStr">
         <is>
           <t>assets/catalogue/all-fragrances/discovery-set/02-gulab-ki-chitthi.jpg</t>
         </is>
       </c>
-      <c r="R32" t="inlineStr">
+      <c r="S32" t="inlineStr">
         <is>
           <t>assets/catalogue/all-fragrances/discovery-set/03-dhoop-chandan.jpg</t>
         </is>

--- a/data/mysaa_products.xlsx
+++ b/data/mysaa_products.xlsx
@@ -2,8 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="18600" windowHeight="6800" tabRatio="600" firstSheet="0" activeTab="4" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read Me" sheetId="1" state="visible" r:id="rId1"/>
@@ -13,195 +14,32 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Settings" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="191029" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="4">
-    <numFmt numFmtId="164" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="165" formatCode="_ &quot;₹&quot;* #,##0.00_ ;_ &quot;₹&quot;* \-#,##0.00_ ;_ &quot;₹&quot;* &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="166" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="167" formatCode="_ &quot;₹&quot;* #,##0_ ;_ &quot;₹&quot;* \-#,##0_ ;_ &quot;₹&quot;* &quot;-&quot;_ ;_ @_ "/>
-  </numFmts>
-  <fonts count="23">
+  <numFmts count="0"/>
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
-      <charset val="134"/>
+      <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <name val="Calibri"/>
-      <charset val="134"/>
       <b val="1"/>
-      <color rgb="FFFFFFFF"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
+      <color rgb="00FFFFFF"/>
     </font>
     <font>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <color rgb="FF0000FF"/>
-      <sz val="11"/>
-      <u val="single"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <charset val="134"/>
       <b val="1"/>
-      <color rgb="FF7A1420"/>
+      <color rgb="007A1420"/>
       <sz val="14"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <color theme="1"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <color rgb="FF800080"/>
-      <sz val="11"/>
-      <u val="single"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <color rgb="FFFF0000"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <b val="1"/>
-      <color theme="3"/>
-      <sz val="18"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <i val="1"/>
-      <color rgb="FF7F7F7F"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <b val="1"/>
-      <color theme="3"/>
-      <sz val="15"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <b val="1"/>
-      <color theme="3"/>
-      <sz val="13"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <b val="1"/>
-      <color theme="3"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <color rgb="FF3F3F76"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <b val="1"/>
-      <color rgb="FF3F3F3F"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <b val="1"/>
-      <color rgb="FFFA7D00"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <b val="1"/>
-      <color rgb="FFFFFFFF"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <color rgb="FFFA7D00"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <b val="1"/>
-      <color theme="1"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <color rgb="FF006100"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <color rgb="FF9C0006"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <color rgb="FF9C6500"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <color theme="0"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <color theme="1"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="34">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
@@ -210,198 +48,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF7A1420"/>
-        <bgColor rgb="FF7A1420"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
+        <fgColor rgb="007A1420"/>
+        <bgColor rgb="007A1420"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="9">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -409,311 +61,19 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="49">
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="4" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="5" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="4" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="6" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
+  <cellStyleXfs count="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="6"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="1" xfId="0"/>
   </cellXfs>
-  <cellStyles count="49">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Comma" xfId="1" builtinId="3"/>
-    <cellStyle name="Currency" xfId="2" builtinId="4"/>
-    <cellStyle name="Percent" xfId="3" builtinId="5"/>
-    <cellStyle name="Comma [0]" xfId="4" builtinId="6"/>
-    <cellStyle name="Currency [0]" xfId="5" builtinId="7"/>
-    <cellStyle name="Link" xfId="6" builtinId="8"/>
-    <cellStyle name="Followed Hyperlink" xfId="7" builtinId="9"/>
-    <cellStyle name="Note" xfId="8" builtinId="10"/>
-    <cellStyle name="Warning Text" xfId="9" builtinId="11"/>
-    <cellStyle name="Title" xfId="10" builtinId="15"/>
-    <cellStyle name="CExplanatory Text" xfId="11" builtinId="53"/>
-    <cellStyle name="Heading 1" xfId="12" builtinId="16"/>
-    <cellStyle name="Heading 2" xfId="13" builtinId="17"/>
-    <cellStyle name="Heading 3" xfId="14" builtinId="18"/>
-    <cellStyle name="Heading 4" xfId="15" builtinId="19"/>
-    <cellStyle name="Input" xfId="16" builtinId="20"/>
-    <cellStyle name="Output" xfId="17" builtinId="21"/>
-    <cellStyle name="Calculation" xfId="18" builtinId="22"/>
-    <cellStyle name="Check Cell" xfId="19" builtinId="23"/>
-    <cellStyle name="Linked Cell" xfId="20" builtinId="24"/>
-    <cellStyle name="Total" xfId="21" builtinId="25"/>
-    <cellStyle name="Good" xfId="22" builtinId="26"/>
-    <cellStyle name="Bad" xfId="23" builtinId="27"/>
-    <cellStyle name="Neutral" xfId="24" builtinId="28"/>
-    <cellStyle name="Accent1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - Accent1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - Accent1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - Accent1" xfId="28" builtinId="32"/>
-    <cellStyle name="Accent2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - Accent2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - Accent2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - Accent2" xfId="32" builtinId="36"/>
-    <cellStyle name="Accent3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - Accent3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - Accent3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - Accent3" xfId="36" builtinId="40"/>
-    <cellStyle name="Accent4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - Accent4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - Accent4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - Accent4" xfId="40" builtinId="44"/>
-    <cellStyle name="Accent5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - Accent5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - Accent5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - Accent5" xfId="44" builtinId="48"/>
-    <cellStyle name="Accent6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - Accent6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - Accent6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - Accent6" xfId="48" builtinId="52"/>
+  <cellStyles count="1">
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -1066,6 +426,7 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
@@ -1076,17 +437,20 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:A20"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14.5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="90" customWidth="1" min="1" max="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="18.5" customHeight="1">
-      <c r="A1" s="3" t="inlineStr">
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>MYSAA RITUALS — Product Data Workbook</t>
         </is>
       </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1109,6 +473,9 @@
         </is>
       </c>
     </row>
+    <row r="6">
+      <c r="A6" t="inlineStr"/>
+    </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
@@ -1140,7 +507,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t xml:space="preserve">   wax-melts, gift-hampers. A product's categorySlug must match one</t>
+          <t xml:space="preserve">   mold-candles, wax-melts, gift-hampers, discovery-set. A product's categorySlug must match one</t>
         </is>
       </c>
     </row>
@@ -1192,6 +559,9 @@
           <t xml:space="preserve">   will update the live site automatically within a minute or two.</t>
         </is>
       </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1211,116 +581,140 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S32"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14.5"/>
+  <dimension ref="A1:V39"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="37" customWidth="1" min="1" max="2"/>
-    <col width="19" customWidth="1" min="3" max="4"/>
+    <col width="37" customWidth="1" min="1" max="1"/>
+    <col width="36" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="13" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="50" customWidth="1" min="8" max="8"/>
-    <col width="35" customWidth="1" min="9" max="9"/>
-    <col width="45" customWidth="1" min="10" max="10"/>
-    <col width="50" customWidth="1" min="11" max="11"/>
-    <col width="12" customWidth="1" min="12" max="13"/>
-    <col width="14" customWidth="1" min="14" max="14"/>
-    <col width="12" customWidth="1" min="15" max="15"/>
-    <col width="50" customWidth="1" min="16" max="18"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="17" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="50" customWidth="1" min="9" max="9"/>
+    <col width="17" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="50" customWidth="1" min="12" max="12"/>
+    <col width="35" customWidth="1" min="13" max="13"/>
+    <col width="50" customWidth="1" min="14" max="14"/>
+    <col width="50" customWidth="1" min="15" max="15"/>
+    <col width="12" customWidth="1" min="16" max="16"/>
+    <col width="12" customWidth="1" min="17" max="17"/>
+    <col width="14" customWidth="1" min="18" max="18"/>
+    <col width="12" customWidth="1" min="19" max="19"/>
+    <col width="50" customWidth="1" min="20" max="20"/>
+    <col width="50" customWidth="1" min="21" max="21"/>
+    <col width="50" customWidth="1" min="22" max="22"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="2" t="inlineStr">
         <is>
           <t>slug</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="2" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="2" t="inlineStr">
         <is>
           <t>categorySlug</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" s="2" t="inlineStr">
         <is>
           <t>fragranceSlug</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="2" t="inlineStr">
         <is>
           <t>mrp</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" s="2" t="inlineStr">
         <is>
           <t>price</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" s="2" t="inlineStr">
+        <is>
+          <t>discountPercent</t>
+        </is>
+      </c>
+      <c r="H1" s="2" t="inlineStr">
+        <is>
+          <t>moq</t>
+        </is>
+      </c>
+      <c r="I1" s="2" t="inlineStr">
+        <is>
+          <t>optionValues</t>
+        </is>
+      </c>
+      <c r="J1" s="2" t="inlineStr">
         <is>
           <t>volume</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="K1" s="2" t="inlineStr">
         <is>
           <t>weight</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="L1" s="2" t="inlineStr">
         <is>
           <t>materials</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="M1" s="2" t="inlineStr">
         <is>
           <t>packaging</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="N1" s="2" t="inlineStr">
         <is>
           <t>shortDescription</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="O1" s="2" t="inlineStr">
         <is>
           <t>about</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="P1" s="2" t="inlineStr">
         <is>
           <t>bestseller</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="Q1" s="2" t="inlineStr">
         <is>
           <t>isNew</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="R1" s="2" t="inlineStr">
         <is>
           <t>customizable</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="S1" s="2" t="inlineStr">
         <is>
           <t>active</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="T1" s="2" t="inlineStr">
         <is>
           <t>image1</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="U1" s="2" t="inlineStr">
         <is>
           <t>image2</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="V1" s="2" t="inlineStr">
         <is>
           <t>image3</t>
         </is>
@@ -1334,7 +728,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Gulab Ki Chitthi Hero Jar Candle</t>
+          <t>Gulab Ki Chitthi Signature</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -1348,59 +742,67 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>899</v>
+        <v>998.75</v>
       </c>
       <c r="F2" t="n">
         <v>799</v>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="G2" t="n">
+        <v>20</v>
+      </c>
+      <c r="H2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr">
         <is>
           <t>220 ml</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr">
         <is>
           <t>Natural soy wax, cotton wick, phthalate-free fragrance oils</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>Mysaa Rituals signature packaging</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>Gulab Ki Chitthi in our hero jar candle.</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>A Mysaa Rituals hero jar candle in the Gulab Ki Chitthi fragrance. Made for gifting, rituals and everyday moments.</t>
-        </is>
-      </c>
-      <c r="M2" t="b">
-        <v>0</v>
-      </c>
-      <c r="N2" t="b">
-        <v>0</v>
-      </c>
-      <c r="O2" t="b">
-        <v>1</v>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>Gulab Ki Chitthi in our signature.</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>A Mysaa Rituals signature in the Gulab Ki Chitthi fragrance. Made for gifting, rituals and everyday moments.</t>
+        </is>
       </c>
       <c r="P2" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q2" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="Q2" t="b">
+        <v>0</v>
+      </c>
+      <c r="R2" t="b">
+        <v>1</v>
+      </c>
+      <c r="S2" t="b">
+        <v>1</v>
+      </c>
+      <c r="T2" t="inlineStr">
         <is>
           <t>assets/catalogue/gulab-ki-chitthi/hero-jar-candle/01-cover.jpg</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>assets/catalogue/gulab-ki-chitthi/hero-jar-candle/02-detail.jpg</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="V2" t="inlineStr">
         <is>
           <t>assets/catalogue/gulab-ki-chitthi/hero-jar-candle/03-lifestyle.jpg</t>
         </is>
@@ -1414,7 +816,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Gulab Ki Chitthi Wide Jar Candle</t>
+          <t>Gulab Ki Chitthi Everyday Ritual</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -1428,59 +830,67 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>699</v>
+        <v>645.88</v>
       </c>
       <c r="F3" t="n">
         <v>549</v>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="G3" t="n">
+        <v>15</v>
+      </c>
+      <c r="H3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr">
         <is>
           <t>120 ml</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr">
         <is>
           <t>Natural soy wax, cotton wick, phthalate-free fragrance oils</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>Mysaa Rituals signature packaging</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>Gulab Ki Chitthi in our wide jar candle.</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>A Mysaa Rituals wide jar candle in the Gulab Ki Chitthi fragrance. Made for gifting, rituals and everyday moments.</t>
-        </is>
-      </c>
-      <c r="M3" t="b">
-        <v>0</v>
-      </c>
-      <c r="N3" t="b">
-        <v>0</v>
-      </c>
-      <c r="O3" t="b">
-        <v>1</v>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>Gulab Ki Chitthi in our everyday ritual.</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>A Mysaa Rituals everyday ritual in the Gulab Ki Chitthi fragrance. Made for gifting, rituals and everyday moments.</t>
+        </is>
       </c>
       <c r="P3" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q3" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="Q3" t="b">
+        <v>0</v>
+      </c>
+      <c r="R3" t="b">
+        <v>1</v>
+      </c>
+      <c r="S3" t="b">
+        <v>1</v>
+      </c>
+      <c r="T3" t="inlineStr">
         <is>
           <t>assets/catalogue/gulab-ki-chitthi/wide-jar-candle/01-cover.jpg</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>assets/catalogue/gulab-ki-chitthi/wide-jar-candle/02-detail.jpg</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
+      <c r="V3" t="inlineStr">
         <is>
           <t>assets/catalogue/gulab-ki-chitthi/wide-jar-candle/03-lifestyle.jpg</t>
         </is>
@@ -1494,7 +904,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Gulab Ki Chitthi Shot Glass Candle</t>
+          <t>Gulab Ki Chitthi Mini Ritual</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1508,59 +918,67 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>399</v>
+        <v>332.22</v>
       </c>
       <c r="F4" t="n">
         <v>299</v>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="G4" t="n">
+        <v>10</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr">
         <is>
           <t>60 ml</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr">
         <is>
           <t>Natural soy wax, cotton wick, phthalate-free fragrance oils</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>Mysaa Rituals signature packaging</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>Gulab Ki Chitthi in our shot glass candle.</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>A Mysaa Rituals shot glass candle in the Gulab Ki Chitthi fragrance. Made for gifting, rituals and everyday moments.</t>
-        </is>
-      </c>
-      <c r="M4" t="b">
-        <v>0</v>
-      </c>
-      <c r="N4" t="b">
-        <v>0</v>
-      </c>
-      <c r="O4" t="b">
-        <v>1</v>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>Gulab Ki Chitthi in our mini ritual.</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>A Mysaa Rituals mini ritual in the Gulab Ki Chitthi fragrance. Made for gifting, rituals and everyday moments.</t>
+        </is>
       </c>
       <c r="P4" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q4" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="Q4" t="b">
+        <v>0</v>
+      </c>
+      <c r="R4" t="b">
+        <v>1</v>
+      </c>
+      <c r="S4" t="b">
+        <v>1</v>
+      </c>
+      <c r="T4" t="inlineStr">
         <is>
           <t>assets/catalogue/gulab-ki-chitthi/shot-glass-candle/01-cover.jpg</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>assets/catalogue/gulab-ki-chitthi/shot-glass-candle/02-detail.jpg</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
+      <c r="V4" t="inlineStr">
         <is>
           <t>assets/catalogue/gulab-ki-chitthi/shot-glass-candle/03-lifestyle.jpg</t>
         </is>
@@ -1587,57 +1005,68 @@
           <t>gulab-ki-chitthi</t>
         </is>
       </c>
+      <c r="E5" t="n">
+        <v>0</v>
+      </c>
       <c r="F5" t="n">
         <v>350</v>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="G5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr">
         <is>
           <t>Combo</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr">
         <is>
           <t>Natural soy wax, cotton wick, phthalate-free fragrance oils</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>Mysaa Rituals signature packaging</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="N5" t="inlineStr">
         <is>
           <t>Gulab Ki Chitthi in our wax sachet combo.</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="O5" t="inlineStr">
         <is>
           <t>A Mysaa Rituals wax sachet combo in the Gulab Ki Chitthi fragrance. Made for gifting, rituals and everyday moments.</t>
         </is>
       </c>
-      <c r="M5" t="b">
-        <v>0</v>
-      </c>
-      <c r="N5" t="b">
-        <v>0</v>
-      </c>
-      <c r="O5" t="b">
-        <v>1</v>
-      </c>
       <c r="P5" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q5" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="b">
+        <v>0</v>
+      </c>
+      <c r="R5" t="b">
+        <v>1</v>
+      </c>
+      <c r="S5" t="b">
+        <v>1</v>
+      </c>
+      <c r="T5" t="inlineStr">
         <is>
           <t>assets/catalogue/gulab-ki-chitthi/wax-melts/01-cover.jpg</t>
         </is>
       </c>
-      <c r="R5" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>assets/catalogue/gulab-ki-chitthi/wax-melts/02-detail.jpg</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr">
+      <c r="V5" t="inlineStr">
         <is>
           <t>assets/catalogue/gulab-ki-chitthi/wax-melts/03-lifestyle.jpg</t>
         </is>
@@ -1664,57 +1093,68 @@
           <t>gulab-ki-chitthi</t>
         </is>
       </c>
+      <c r="E6" t="n">
+        <v>0</v>
+      </c>
       <c r="F6" t="n">
         <v>0</v>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="G6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr">
         <is>
           <t>Curated set</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr">
         <is>
           <t>Curated Mysaa Rituals gifting selection</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>Mysaa Rituals signature packaging</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="N6" t="inlineStr">
         <is>
           <t>Gulab Ki Chitthi in our gift hamper.</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="O6" t="inlineStr">
         <is>
           <t>A Mysaa Rituals gift hamper in the Gulab Ki Chitthi fragrance. Made for gifting, rituals and everyday moments.</t>
         </is>
       </c>
-      <c r="M6" t="b">
-        <v>0</v>
-      </c>
-      <c r="N6" t="b">
-        <v>0</v>
-      </c>
-      <c r="O6" t="b">
-        <v>1</v>
-      </c>
       <c r="P6" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q6" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="b">
+        <v>0</v>
+      </c>
+      <c r="R6" t="b">
+        <v>1</v>
+      </c>
+      <c r="S6" t="b">
+        <v>1</v>
+      </c>
+      <c r="T6" t="inlineStr">
         <is>
           <t>assets/catalogue/gulab-ki-chitthi/gift-hampers/01-cover.jpg</t>
         </is>
       </c>
-      <c r="R6" t="inlineStr">
+      <c r="U6" t="inlineStr">
         <is>
           <t>assets/catalogue/gulab-ki-chitthi/gift-hampers/02-detail.jpg</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr">
+      <c r="V6" t="inlineStr">
         <is>
           <t>assets/catalogue/gulab-ki-chitthi/gift-hampers/03-lifestyle.jpg</t>
         </is>
@@ -1728,7 +1168,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Dhoop &amp; Chandan Hero Jar Candle</t>
+          <t>Dhoop &amp; Chandan Signature</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1742,59 +1182,67 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>899</v>
+        <v>998.75</v>
       </c>
       <c r="F7" t="n">
         <v>799</v>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="G7" t="n">
+        <v>20</v>
+      </c>
+      <c r="H7" t="n">
+        <v>1</v>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr">
         <is>
           <t>220 ml</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr">
         <is>
           <t>Natural soy wax, cotton wick, phthalate-free fragrance oils</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>Mysaa Rituals signature packaging</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>Dhoop &amp; Chandan in our hero jar candle.</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>A Mysaa Rituals hero jar candle in the Dhoop &amp; Chandan fragrance. Made for gifting, rituals and everyday moments.</t>
-        </is>
-      </c>
-      <c r="M7" t="b">
-        <v>0</v>
-      </c>
-      <c r="N7" t="b">
-        <v>0</v>
-      </c>
-      <c r="O7" t="b">
-        <v>1</v>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>Dhoop &amp; Chandan in our signature.</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>A Mysaa Rituals signature in the Dhoop &amp; Chandan fragrance. Made for gifting, rituals and everyday moments.</t>
+        </is>
       </c>
       <c r="P7" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q7" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="b">
+        <v>0</v>
+      </c>
+      <c r="R7" t="b">
+        <v>1</v>
+      </c>
+      <c r="S7" t="b">
+        <v>1</v>
+      </c>
+      <c r="T7" t="inlineStr">
         <is>
           <t>assets/catalogue/dhoop-chandan/hero-jar-candle/01-cover.jpg</t>
         </is>
       </c>
-      <c r="R7" t="inlineStr">
+      <c r="U7" t="inlineStr">
         <is>
           <t>assets/catalogue/dhoop-chandan/hero-jar-candle/02-detail.jpg</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
+      <c r="V7" t="inlineStr">
         <is>
           <t>assets/catalogue/dhoop-chandan/hero-jar-candle/03-lifestyle.jpg</t>
         </is>
@@ -1808,7 +1256,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Dhoop &amp; Chandan Wide Jar Candle</t>
+          <t>Dhoop &amp; Chandan Everyday Ritual</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1822,59 +1270,67 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>699</v>
+        <v>645.88</v>
       </c>
       <c r="F8" t="n">
         <v>549</v>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="G8" t="n">
+        <v>15</v>
+      </c>
+      <c r="H8" t="n">
+        <v>1</v>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr">
         <is>
           <t>120 ml</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr">
         <is>
           <t>Natural soy wax, cotton wick, phthalate-free fragrance oils</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>Mysaa Rituals signature packaging</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>Dhoop &amp; Chandan in our wide jar candle.</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>A Mysaa Rituals wide jar candle in the Dhoop &amp; Chandan fragrance. Made for gifting, rituals and everyday moments.</t>
-        </is>
-      </c>
-      <c r="M8" t="b">
-        <v>0</v>
-      </c>
-      <c r="N8" t="b">
-        <v>0</v>
-      </c>
-      <c r="O8" t="b">
-        <v>1</v>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>Dhoop &amp; Chandan in our everyday ritual.</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>A Mysaa Rituals everyday ritual in the Dhoop &amp; Chandan fragrance. Made for gifting, rituals and everyday moments.</t>
+        </is>
       </c>
       <c r="P8" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q8" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="b">
+        <v>0</v>
+      </c>
+      <c r="R8" t="b">
+        <v>1</v>
+      </c>
+      <c r="S8" t="b">
+        <v>1</v>
+      </c>
+      <c r="T8" t="inlineStr">
         <is>
           <t>assets/catalogue/dhoop-chandan/wide-jar-candle/01-cover.jpg</t>
         </is>
       </c>
-      <c r="R8" t="inlineStr">
+      <c r="U8" t="inlineStr">
         <is>
           <t>assets/catalogue/dhoop-chandan/wide-jar-candle/02-detail.jpg</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr">
+      <c r="V8" t="inlineStr">
         <is>
           <t>assets/catalogue/dhoop-chandan/wide-jar-candle/03-lifestyle.jpg</t>
         </is>
@@ -1888,7 +1344,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Dhoop &amp; Chandan Shot Glass Candle</t>
+          <t>Dhoop &amp; Chandan Mini Ritual</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1902,59 +1358,67 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>399</v>
+        <v>332.22</v>
       </c>
       <c r="F9" t="n">
         <v>299</v>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="G9" t="n">
+        <v>10</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1</v>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr">
         <is>
           <t>60 ml</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr">
         <is>
           <t>Natural soy wax, cotton wick, phthalate-free fragrance oils</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>Mysaa Rituals signature packaging</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>Dhoop &amp; Chandan in our shot glass candle.</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>A Mysaa Rituals shot glass candle in the Dhoop &amp; Chandan fragrance. Made for gifting, rituals and everyday moments.</t>
-        </is>
-      </c>
-      <c r="M9" t="b">
-        <v>0</v>
-      </c>
-      <c r="N9" t="b">
-        <v>0</v>
-      </c>
-      <c r="O9" t="b">
-        <v>1</v>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>Dhoop &amp; Chandan in our mini ritual.</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>A Mysaa Rituals mini ritual in the Dhoop &amp; Chandan fragrance. Made for gifting, rituals and everyday moments.</t>
+        </is>
       </c>
       <c r="P9" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q9" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="b">
+        <v>0</v>
+      </c>
+      <c r="R9" t="b">
+        <v>1</v>
+      </c>
+      <c r="S9" t="b">
+        <v>1</v>
+      </c>
+      <c r="T9" t="inlineStr">
         <is>
           <t>assets/catalogue/dhoop-chandan/shot-glass-candle/01-cover.jpg</t>
         </is>
       </c>
-      <c r="R9" t="inlineStr">
+      <c r="U9" t="inlineStr">
         <is>
           <t>assets/catalogue/dhoop-chandan/shot-glass-candle/02-detail.jpg</t>
         </is>
       </c>
-      <c r="S9" t="inlineStr">
+      <c r="V9" t="inlineStr">
         <is>
           <t>assets/catalogue/dhoop-chandan/shot-glass-candle/03-lifestyle.jpg</t>
         </is>
@@ -1981,57 +1445,68 @@
           <t>dhoop-chandan</t>
         </is>
       </c>
+      <c r="E10" t="n">
+        <v>0</v>
+      </c>
       <c r="F10" t="n">
         <v>350</v>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="G10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" t="n">
+        <v>1</v>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr">
         <is>
           <t>Combo</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr">
         <is>
           <t>Natural soy wax, cotton wick, phthalate-free fragrance oils</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t>Mysaa Rituals signature packaging</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="N10" t="inlineStr">
         <is>
           <t>Dhoop &amp; Chandan in our wax sachet combo.</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="O10" t="inlineStr">
         <is>
           <t>A Mysaa Rituals wax sachet combo in the Dhoop &amp; Chandan fragrance. Made for gifting, rituals and everyday moments.</t>
         </is>
       </c>
-      <c r="M10" t="b">
-        <v>0</v>
-      </c>
-      <c r="N10" t="b">
-        <v>0</v>
-      </c>
-      <c r="O10" t="b">
-        <v>1</v>
-      </c>
       <c r="P10" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q10" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="b">
+        <v>0</v>
+      </c>
+      <c r="R10" t="b">
+        <v>1</v>
+      </c>
+      <c r="S10" t="b">
+        <v>1</v>
+      </c>
+      <c r="T10" t="inlineStr">
         <is>
           <t>assets/catalogue/dhoop-chandan/wax-melts/01-cover.jpg</t>
         </is>
       </c>
-      <c r="R10" t="inlineStr">
+      <c r="U10" t="inlineStr">
         <is>
           <t>assets/catalogue/dhoop-chandan/wax-melts/02-detail.jpg</t>
         </is>
       </c>
-      <c r="S10" t="inlineStr">
+      <c r="V10" t="inlineStr">
         <is>
           <t>assets/catalogue/dhoop-chandan/wax-melts/03-lifestyle.jpg</t>
         </is>
@@ -2058,57 +1533,68 @@
           <t>dhoop-chandan</t>
         </is>
       </c>
+      <c r="E11" t="n">
+        <v>0</v>
+      </c>
       <c r="F11" t="n">
         <v>0</v>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="G11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" t="n">
+        <v>1</v>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr">
         <is>
           <t>Curated set</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr">
         <is>
           <t>Curated Mysaa Rituals gifting selection</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr">
+      <c r="M11" t="inlineStr">
         <is>
           <t>Mysaa Rituals signature packaging</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr">
+      <c r="N11" t="inlineStr">
         <is>
           <t>Dhoop &amp; Chandan in our gift hamper.</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr">
+      <c r="O11" t="inlineStr">
         <is>
           <t>A Mysaa Rituals gift hamper in the Dhoop &amp; Chandan fragrance. Made for gifting, rituals and everyday moments.</t>
         </is>
       </c>
-      <c r="M11" t="b">
-        <v>0</v>
-      </c>
-      <c r="N11" t="b">
-        <v>0</v>
-      </c>
-      <c r="O11" t="b">
-        <v>1</v>
-      </c>
       <c r="P11" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q11" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="b">
+        <v>0</v>
+      </c>
+      <c r="R11" t="b">
+        <v>1</v>
+      </c>
+      <c r="S11" t="b">
+        <v>1</v>
+      </c>
+      <c r="T11" t="inlineStr">
         <is>
           <t>assets/catalogue/dhoop-chandan/gift-hampers/01-cover.jpg</t>
         </is>
       </c>
-      <c r="R11" t="inlineStr">
+      <c r="U11" t="inlineStr">
         <is>
           <t>assets/catalogue/dhoop-chandan/gift-hampers/02-detail.jpg</t>
         </is>
       </c>
-      <c r="S11" t="inlineStr">
+      <c r="V11" t="inlineStr">
         <is>
           <t>assets/catalogue/dhoop-chandan/gift-hampers/03-lifestyle.jpg</t>
         </is>
@@ -2122,7 +1608,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Gajre Ka Shringar Hero Jar Candle</t>
+          <t>Gajre Ka Shringar Signature</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -2136,59 +1622,67 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>899</v>
+        <v>998.75</v>
       </c>
       <c r="F12" t="n">
         <v>799</v>
       </c>
-      <c r="G12" t="inlineStr">
+      <c r="G12" t="n">
+        <v>20</v>
+      </c>
+      <c r="H12" t="n">
+        <v>1</v>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr">
         <is>
           <t>220 ml</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr">
         <is>
           <t>Natural soy wax, cotton wick, phthalate-free fragrance oils</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr">
+      <c r="M12" t="inlineStr">
         <is>
           <t>Mysaa Rituals signature packaging</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>Gajre Ka Shringar in our hero jar candle.</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>A Mysaa Rituals hero jar candle in the Gajre Ka Shringar fragrance. Made for gifting, rituals and everyday moments.</t>
-        </is>
-      </c>
-      <c r="M12" t="b">
-        <v>0</v>
-      </c>
-      <c r="N12" t="b">
-        <v>0</v>
-      </c>
-      <c r="O12" t="b">
-        <v>1</v>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>Gajre Ka Shringar in our signature.</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>A Mysaa Rituals signature in the Gajre Ka Shringar fragrance. Made for gifting, rituals and everyday moments.</t>
+        </is>
       </c>
       <c r="P12" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q12" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="Q12" t="b">
+        <v>0</v>
+      </c>
+      <c r="R12" t="b">
+        <v>1</v>
+      </c>
+      <c r="S12" t="b">
+        <v>1</v>
+      </c>
+      <c r="T12" t="inlineStr">
         <is>
           <t>assets/catalogue/gajre-ka-shringar/hero-jar-candle/01-cover.jpg</t>
         </is>
       </c>
-      <c r="R12" t="inlineStr">
+      <c r="U12" t="inlineStr">
         <is>
           <t>assets/catalogue/gajre-ka-shringar/hero-jar-candle/02-detail.jpg</t>
         </is>
       </c>
-      <c r="S12" t="inlineStr">
+      <c r="V12" t="inlineStr">
         <is>
           <t>assets/catalogue/gajre-ka-shringar/hero-jar-candle/03-lifestyle.jpg</t>
         </is>
@@ -2202,7 +1696,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Gajre Ka Shringar Wide Jar Candle</t>
+          <t>Gajre Ka Shringar Everyday Ritual</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -2216,59 +1710,67 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>699</v>
+        <v>645.88</v>
       </c>
       <c r="F13" t="n">
         <v>549</v>
       </c>
-      <c r="G13" t="inlineStr">
+      <c r="G13" t="n">
+        <v>15</v>
+      </c>
+      <c r="H13" t="n">
+        <v>1</v>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr">
         <is>
           <t>120 ml</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr">
         <is>
           <t>Natural soy wax, cotton wick, phthalate-free fragrance oils</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr">
+      <c r="M13" t="inlineStr">
         <is>
           <t>Mysaa Rituals signature packaging</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>Gajre Ka Shringar in our wide jar candle.</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>A Mysaa Rituals wide jar candle in the Gajre Ka Shringar fragrance. Made for gifting, rituals and everyday moments.</t>
-        </is>
-      </c>
-      <c r="M13" t="b">
-        <v>0</v>
-      </c>
-      <c r="N13" t="b">
-        <v>0</v>
-      </c>
-      <c r="O13" t="b">
-        <v>1</v>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>Gajre Ka Shringar in our everyday ritual.</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>A Mysaa Rituals everyday ritual in the Gajre Ka Shringar fragrance. Made for gifting, rituals and everyday moments.</t>
+        </is>
       </c>
       <c r="P13" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q13" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="b">
+        <v>0</v>
+      </c>
+      <c r="R13" t="b">
+        <v>1</v>
+      </c>
+      <c r="S13" t="b">
+        <v>1</v>
+      </c>
+      <c r="T13" t="inlineStr">
         <is>
           <t>assets/catalogue/gajre-ka-shringar/wide-jar-candle/01-cover.jpg</t>
         </is>
       </c>
-      <c r="R13" t="inlineStr">
+      <c r="U13" t="inlineStr">
         <is>
           <t>assets/catalogue/gajre-ka-shringar/wide-jar-candle/02-detail.jpg</t>
         </is>
       </c>
-      <c r="S13" t="inlineStr">
+      <c r="V13" t="inlineStr">
         <is>
           <t>assets/catalogue/gajre-ka-shringar/wide-jar-candle/03-lifestyle.jpg</t>
         </is>
@@ -2282,7 +1784,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Gajre Ka Shringar Shot Glass Candle</t>
+          <t>Gajre Ka Shringar Mini Ritual</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -2296,59 +1798,67 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>399</v>
+        <v>332.22</v>
       </c>
       <c r="F14" t="n">
         <v>299</v>
       </c>
-      <c r="G14" t="inlineStr">
+      <c r="G14" t="n">
+        <v>10</v>
+      </c>
+      <c r="H14" t="n">
+        <v>1</v>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr">
         <is>
           <t>60 ml</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr">
         <is>
           <t>Natural soy wax, cotton wick, phthalate-free fragrance oils</t>
         </is>
       </c>
-      <c r="J14" t="inlineStr">
+      <c r="M14" t="inlineStr">
         <is>
           <t>Mysaa Rituals signature packaging</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>Gajre Ka Shringar in our shot glass candle.</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>A Mysaa Rituals shot glass candle in the Gajre Ka Shringar fragrance. Made for gifting, rituals and everyday moments.</t>
-        </is>
-      </c>
-      <c r="M14" t="b">
-        <v>0</v>
-      </c>
-      <c r="N14" t="b">
-        <v>0</v>
-      </c>
-      <c r="O14" t="b">
-        <v>1</v>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>Gajre Ka Shringar in our mini ritual.</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>A Mysaa Rituals mini ritual in the Gajre Ka Shringar fragrance. Made for gifting, rituals and everyday moments.</t>
+        </is>
       </c>
       <c r="P14" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q14" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="b">
+        <v>0</v>
+      </c>
+      <c r="R14" t="b">
+        <v>1</v>
+      </c>
+      <c r="S14" t="b">
+        <v>1</v>
+      </c>
+      <c r="T14" t="inlineStr">
         <is>
           <t>assets/catalogue/gajre-ka-shringar/shot-glass-candle/01-cover.jpg</t>
         </is>
       </c>
-      <c r="R14" t="inlineStr">
+      <c r="U14" t="inlineStr">
         <is>
           <t>assets/catalogue/gajre-ka-shringar/shot-glass-candle/02-detail.jpg</t>
         </is>
       </c>
-      <c r="S14" t="inlineStr">
+      <c r="V14" t="inlineStr">
         <is>
           <t>assets/catalogue/gajre-ka-shringar/shot-glass-candle/03-lifestyle.jpg</t>
         </is>
@@ -2375,57 +1885,68 @@
           <t>gajre-ka-shringar</t>
         </is>
       </c>
+      <c r="E15" t="n">
+        <v>0</v>
+      </c>
       <c r="F15" t="n">
         <v>350</v>
       </c>
-      <c r="G15" t="inlineStr">
+      <c r="G15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" t="n">
+        <v>1</v>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr">
         <is>
           <t>Combo</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr">
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr">
         <is>
           <t>Natural soy wax, cotton wick, phthalate-free fragrance oils</t>
         </is>
       </c>
-      <c r="J15" t="inlineStr">
+      <c r="M15" t="inlineStr">
         <is>
           <t>Mysaa Rituals signature packaging</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr">
+      <c r="N15" t="inlineStr">
         <is>
           <t>Gajre Ka Shringar in our wax sachet combo.</t>
         </is>
       </c>
-      <c r="L15" t="inlineStr">
+      <c r="O15" t="inlineStr">
         <is>
           <t>A Mysaa Rituals wax sachet combo in the Gajre Ka Shringar fragrance. Made for gifting, rituals and everyday moments.</t>
         </is>
       </c>
-      <c r="M15" t="b">
-        <v>0</v>
-      </c>
-      <c r="N15" t="b">
-        <v>0</v>
-      </c>
-      <c r="O15" t="b">
-        <v>1</v>
-      </c>
       <c r="P15" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q15" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="b">
+        <v>0</v>
+      </c>
+      <c r="R15" t="b">
+        <v>1</v>
+      </c>
+      <c r="S15" t="b">
+        <v>1</v>
+      </c>
+      <c r="T15" t="inlineStr">
         <is>
           <t>assets/catalogue/gajre-ka-shringar/wax-melts/01-cover.jpg</t>
         </is>
       </c>
-      <c r="R15" t="inlineStr">
+      <c r="U15" t="inlineStr">
         <is>
           <t>assets/catalogue/gajre-ka-shringar/wax-melts/02-detail.jpg</t>
         </is>
       </c>
-      <c r="S15" t="inlineStr">
+      <c r="V15" t="inlineStr">
         <is>
           <t>assets/catalogue/gajre-ka-shringar/wax-melts/03-lifestyle.jpg</t>
         </is>
@@ -2452,57 +1973,68 @@
           <t>gajre-ka-shringar</t>
         </is>
       </c>
+      <c r="E16" t="n">
+        <v>0</v>
+      </c>
       <c r="F16" t="n">
         <v>0</v>
       </c>
-      <c r="G16" t="inlineStr">
+      <c r="G16" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" t="n">
+        <v>1</v>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr">
         <is>
           <t>Curated set</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr">
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr">
         <is>
           <t>Curated Mysaa Rituals gifting selection</t>
         </is>
       </c>
-      <c r="J16" t="inlineStr">
+      <c r="M16" t="inlineStr">
         <is>
           <t>Mysaa Rituals signature packaging</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr">
+      <c r="N16" t="inlineStr">
         <is>
           <t>Gajre Ka Shringar in our gift hamper.</t>
         </is>
       </c>
-      <c r="L16" t="inlineStr">
+      <c r="O16" t="inlineStr">
         <is>
           <t>A Mysaa Rituals gift hamper in the Gajre Ka Shringar fragrance. Made for gifting, rituals and everyday moments.</t>
         </is>
       </c>
-      <c r="M16" t="b">
-        <v>0</v>
-      </c>
-      <c r="N16" t="b">
-        <v>0</v>
-      </c>
-      <c r="O16" t="b">
-        <v>1</v>
-      </c>
       <c r="P16" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q16" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="Q16" t="b">
+        <v>0</v>
+      </c>
+      <c r="R16" t="b">
+        <v>1</v>
+      </c>
+      <c r="S16" t="b">
+        <v>1</v>
+      </c>
+      <c r="T16" t="inlineStr">
         <is>
           <t>assets/catalogue/gajre-ka-shringar/gift-hampers/01-cover.jpg</t>
         </is>
       </c>
-      <c r="R16" t="inlineStr">
+      <c r="U16" t="inlineStr">
         <is>
           <t>assets/catalogue/gajre-ka-shringar/gift-hampers/02-detail.jpg</t>
         </is>
       </c>
-      <c r="S16" t="inlineStr">
+      <c r="V16" t="inlineStr">
         <is>
           <t>assets/catalogue/gajre-ka-shringar/gift-hampers/03-lifestyle.jpg</t>
         </is>
@@ -2516,7 +2048,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Madhuban Hero Jar Candle</t>
+          <t>Madhuban Signature</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -2530,59 +2062,67 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>899</v>
+        <v>998.75</v>
       </c>
       <c r="F17" t="n">
         <v>799</v>
       </c>
-      <c r="G17" t="inlineStr">
+      <c r="G17" t="n">
+        <v>20</v>
+      </c>
+      <c r="H17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr">
         <is>
           <t>220 ml</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr">
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr">
         <is>
           <t>Natural soy wax, cotton wick, phthalate-free fragrance oils</t>
         </is>
       </c>
-      <c r="J17" t="inlineStr">
+      <c r="M17" t="inlineStr">
         <is>
           <t>Mysaa Rituals signature packaging</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>Madhuban in our hero jar candle.</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>A Mysaa Rituals hero jar candle in the Madhuban fragrance. Made for gifting, rituals and everyday moments.</t>
-        </is>
-      </c>
-      <c r="M17" t="b">
-        <v>0</v>
-      </c>
-      <c r="N17" t="b">
-        <v>0</v>
-      </c>
-      <c r="O17" t="b">
-        <v>1</v>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>Madhuban in our signature.</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>A Mysaa Rituals signature in the Madhuban fragrance. Made for gifting, rituals and everyday moments.</t>
+        </is>
       </c>
       <c r="P17" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q17" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="b">
+        <v>0</v>
+      </c>
+      <c r="R17" t="b">
+        <v>1</v>
+      </c>
+      <c r="S17" t="b">
+        <v>1</v>
+      </c>
+      <c r="T17" t="inlineStr">
         <is>
           <t>assets/catalogue/madhuban/hero-jar-candle/01-cover.jpg</t>
         </is>
       </c>
-      <c r="R17" t="inlineStr">
+      <c r="U17" t="inlineStr">
         <is>
           <t>assets/catalogue/madhuban/hero-jar-candle/02-detail.jpg</t>
         </is>
       </c>
-      <c r="S17" t="inlineStr">
+      <c r="V17" t="inlineStr">
         <is>
           <t>assets/catalogue/madhuban/hero-jar-candle/03-lifestyle.jpg</t>
         </is>
@@ -2596,7 +2136,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Madhuban Wide Jar Candle</t>
+          <t>Madhuban Everyday Ritual</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -2610,59 +2150,67 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>699</v>
+        <v>645.88</v>
       </c>
       <c r="F18" t="n">
         <v>549</v>
       </c>
-      <c r="G18" t="inlineStr">
+      <c r="G18" t="n">
+        <v>15</v>
+      </c>
+      <c r="H18" t="n">
+        <v>1</v>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr">
         <is>
           <t>120 ml</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr">
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr">
         <is>
           <t>Natural soy wax, cotton wick, phthalate-free fragrance oils</t>
         </is>
       </c>
-      <c r="J18" t="inlineStr">
+      <c r="M18" t="inlineStr">
         <is>
           <t>Mysaa Rituals signature packaging</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>Madhuban in our wide jar candle.</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>A Mysaa Rituals wide jar candle in the Madhuban fragrance. Made for gifting, rituals and everyday moments.</t>
-        </is>
-      </c>
-      <c r="M18" t="b">
-        <v>0</v>
-      </c>
-      <c r="N18" t="b">
-        <v>0</v>
-      </c>
-      <c r="O18" t="b">
-        <v>1</v>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>Madhuban in our everyday ritual.</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>A Mysaa Rituals everyday ritual in the Madhuban fragrance. Made for gifting, rituals and everyday moments.</t>
+        </is>
       </c>
       <c r="P18" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q18" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="Q18" t="b">
+        <v>0</v>
+      </c>
+      <c r="R18" t="b">
+        <v>1</v>
+      </c>
+      <c r="S18" t="b">
+        <v>1</v>
+      </c>
+      <c r="T18" t="inlineStr">
         <is>
           <t>assets/catalogue/madhuban/wide-jar-candle/01-cover.jpg</t>
         </is>
       </c>
-      <c r="R18" t="inlineStr">
+      <c r="U18" t="inlineStr">
         <is>
           <t>assets/catalogue/madhuban/wide-jar-candle/02-detail.jpg</t>
         </is>
       </c>
-      <c r="S18" t="inlineStr">
+      <c r="V18" t="inlineStr">
         <is>
           <t>assets/catalogue/madhuban/wide-jar-candle/03-lifestyle.jpg</t>
         </is>
@@ -2676,7 +2224,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Madhuban Shot Glass Candle</t>
+          <t>Madhuban Mini Ritual</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -2690,59 +2238,67 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>399</v>
+        <v>332.22</v>
       </c>
       <c r="F19" t="n">
         <v>299</v>
       </c>
-      <c r="G19" t="inlineStr">
+      <c r="G19" t="n">
+        <v>10</v>
+      </c>
+      <c r="H19" t="n">
+        <v>1</v>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr">
         <is>
           <t>60 ml</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr">
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr">
         <is>
           <t>Natural soy wax, cotton wick, phthalate-free fragrance oils</t>
         </is>
       </c>
-      <c r="J19" t="inlineStr">
+      <c r="M19" t="inlineStr">
         <is>
           <t>Mysaa Rituals signature packaging</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>Madhuban in our shot glass candle.</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>A Mysaa Rituals shot glass candle in the Madhuban fragrance. Made for gifting, rituals and everyday moments.</t>
-        </is>
-      </c>
-      <c r="M19" t="b">
-        <v>0</v>
-      </c>
-      <c r="N19" t="b">
-        <v>0</v>
-      </c>
-      <c r="O19" t="b">
-        <v>1</v>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>Madhuban in our mini ritual.</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>A Mysaa Rituals mini ritual in the Madhuban fragrance. Made for gifting, rituals and everyday moments.</t>
+        </is>
       </c>
       <c r="P19" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q19" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="Q19" t="b">
+        <v>0</v>
+      </c>
+      <c r="R19" t="b">
+        <v>1</v>
+      </c>
+      <c r="S19" t="b">
+        <v>1</v>
+      </c>
+      <c r="T19" t="inlineStr">
         <is>
           <t>assets/catalogue/madhuban/shot-glass-candle/01-cover.jpg</t>
         </is>
       </c>
-      <c r="R19" t="inlineStr">
+      <c r="U19" t="inlineStr">
         <is>
           <t>assets/catalogue/madhuban/shot-glass-candle/02-detail.jpg</t>
         </is>
       </c>
-      <c r="S19" t="inlineStr">
+      <c r="V19" t="inlineStr">
         <is>
           <t>assets/catalogue/madhuban/shot-glass-candle/03-lifestyle.jpg</t>
         </is>
@@ -2769,57 +2325,68 @@
           <t>madhuban</t>
         </is>
       </c>
+      <c r="E20" t="n">
+        <v>0</v>
+      </c>
       <c r="F20" t="n">
         <v>350</v>
       </c>
-      <c r="G20" t="inlineStr">
+      <c r="G20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" t="n">
+        <v>1</v>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr">
         <is>
           <t>Combo</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr">
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr">
         <is>
           <t>Natural soy wax, cotton wick, phthalate-free fragrance oils</t>
         </is>
       </c>
-      <c r="J20" t="inlineStr">
+      <c r="M20" t="inlineStr">
         <is>
           <t>Mysaa Rituals signature packaging</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr">
+      <c r="N20" t="inlineStr">
         <is>
           <t>Madhuban in our wax sachet combo.</t>
         </is>
       </c>
-      <c r="L20" t="inlineStr">
+      <c r="O20" t="inlineStr">
         <is>
           <t>A Mysaa Rituals wax sachet combo in the Madhuban fragrance. Made for gifting, rituals and everyday moments.</t>
         </is>
       </c>
-      <c r="M20" t="b">
-        <v>0</v>
-      </c>
-      <c r="N20" t="b">
-        <v>0</v>
-      </c>
-      <c r="O20" t="b">
-        <v>1</v>
-      </c>
       <c r="P20" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q20" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="Q20" t="b">
+        <v>0</v>
+      </c>
+      <c r="R20" t="b">
+        <v>1</v>
+      </c>
+      <c r="S20" t="b">
+        <v>1</v>
+      </c>
+      <c r="T20" t="inlineStr">
         <is>
           <t>assets/catalogue/madhuban/wax-melts/01-cover.jpg</t>
         </is>
       </c>
-      <c r="R20" t="inlineStr">
+      <c r="U20" t="inlineStr">
         <is>
           <t>assets/catalogue/madhuban/wax-melts/02-detail.jpg</t>
         </is>
       </c>
-      <c r="S20" t="inlineStr">
+      <c r="V20" t="inlineStr">
         <is>
           <t>assets/catalogue/madhuban/wax-melts/03-lifestyle.jpg</t>
         </is>
@@ -2846,57 +2413,68 @@
           <t>madhuban</t>
         </is>
       </c>
+      <c r="E21" t="n">
+        <v>0</v>
+      </c>
       <c r="F21" t="n">
         <v>0</v>
       </c>
-      <c r="G21" t="inlineStr">
+      <c r="G21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H21" t="n">
+        <v>1</v>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr">
         <is>
           <t>Curated set</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr">
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr">
         <is>
           <t>Curated Mysaa Rituals gifting selection</t>
         </is>
       </c>
-      <c r="J21" t="inlineStr">
+      <c r="M21" t="inlineStr">
         <is>
           <t>Mysaa Rituals signature packaging</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr">
+      <c r="N21" t="inlineStr">
         <is>
           <t>Madhuban in our gift hamper.</t>
         </is>
       </c>
-      <c r="L21" t="inlineStr">
+      <c r="O21" t="inlineStr">
         <is>
           <t>A Mysaa Rituals gift hamper in the Madhuban fragrance. Made for gifting, rituals and everyday moments.</t>
         </is>
       </c>
-      <c r="M21" t="b">
-        <v>0</v>
-      </c>
-      <c r="N21" t="b">
-        <v>0</v>
-      </c>
-      <c r="O21" t="b">
-        <v>1</v>
-      </c>
       <c r="P21" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q21" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="Q21" t="b">
+        <v>0</v>
+      </c>
+      <c r="R21" t="b">
+        <v>1</v>
+      </c>
+      <c r="S21" t="b">
+        <v>1</v>
+      </c>
+      <c r="T21" t="inlineStr">
         <is>
           <t>assets/catalogue/madhuban/gift-hampers/01-cover.jpg</t>
         </is>
       </c>
-      <c r="R21" t="inlineStr">
+      <c r="U21" t="inlineStr">
         <is>
           <t>assets/catalogue/madhuban/gift-hampers/02-detail.jpg</t>
         </is>
       </c>
-      <c r="S21" t="inlineStr">
+      <c r="V21" t="inlineStr">
         <is>
           <t>assets/catalogue/madhuban/gift-hampers/03-lifestyle.jpg</t>
         </is>
@@ -2910,7 +2488,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Raat Ki Rani Hero Jar Candle</t>
+          <t>Raat Ki Rani Signature</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -2924,59 +2502,67 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>899</v>
+        <v>998.75</v>
       </c>
       <c r="F22" t="n">
         <v>799</v>
       </c>
-      <c r="G22" t="inlineStr">
+      <c r="G22" t="n">
+        <v>20</v>
+      </c>
+      <c r="H22" t="n">
+        <v>1</v>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr">
         <is>
           <t>220 ml</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr">
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr">
         <is>
           <t>Natural soy wax, cotton wick, phthalate-free fragrance oils</t>
         </is>
       </c>
-      <c r="J22" t="inlineStr">
+      <c r="M22" t="inlineStr">
         <is>
           <t>Mysaa Rituals signature packaging</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>Raat Ki Rani in our hero jar candle.</t>
-        </is>
-      </c>
-      <c r="L22" t="inlineStr">
-        <is>
-          <t>A Mysaa Rituals hero jar candle in the Raat Ki Rani fragrance. Made for gifting, rituals and everyday moments.</t>
-        </is>
-      </c>
-      <c r="M22" t="b">
-        <v>0</v>
-      </c>
-      <c r="N22" t="b">
-        <v>0</v>
-      </c>
-      <c r="O22" t="b">
-        <v>1</v>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>Raat Ki Rani in our signature.</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>A Mysaa Rituals signature in the Raat Ki Rani fragrance. Made for gifting, rituals and everyday moments.</t>
+        </is>
       </c>
       <c r="P22" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q22" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="Q22" t="b">
+        <v>0</v>
+      </c>
+      <c r="R22" t="b">
+        <v>1</v>
+      </c>
+      <c r="S22" t="b">
+        <v>1</v>
+      </c>
+      <c r="T22" t="inlineStr">
         <is>
           <t>assets/catalogue/raat-ki-rani/hero-jar-candle/01-cover.jpg</t>
         </is>
       </c>
-      <c r="R22" t="inlineStr">
+      <c r="U22" t="inlineStr">
         <is>
           <t>assets/catalogue/raat-ki-rani/hero-jar-candle/02-detail.jpg</t>
         </is>
       </c>
-      <c r="S22" t="inlineStr">
+      <c r="V22" t="inlineStr">
         <is>
           <t>assets/catalogue/raat-ki-rani/hero-jar-candle/03-lifestyle.jpg</t>
         </is>
@@ -2990,7 +2576,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Raat Ki Rani Wide Jar Candle</t>
+          <t>Raat Ki Rani Everyday Ritual</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -3004,59 +2590,67 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>699</v>
+        <v>645.88</v>
       </c>
       <c r="F23" t="n">
         <v>549</v>
       </c>
-      <c r="G23" t="inlineStr">
+      <c r="G23" t="n">
+        <v>15</v>
+      </c>
+      <c r="H23" t="n">
+        <v>1</v>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr">
         <is>
           <t>120 ml</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr">
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr">
         <is>
           <t>Natural soy wax, cotton wick, phthalate-free fragrance oils</t>
         </is>
       </c>
-      <c r="J23" t="inlineStr">
+      <c r="M23" t="inlineStr">
         <is>
           <t>Mysaa Rituals signature packaging</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>Raat Ki Rani in our wide jar candle.</t>
-        </is>
-      </c>
-      <c r="L23" t="inlineStr">
-        <is>
-          <t>A Mysaa Rituals wide jar candle in the Raat Ki Rani fragrance. Made for gifting, rituals and everyday moments.</t>
-        </is>
-      </c>
-      <c r="M23" t="b">
-        <v>0</v>
-      </c>
-      <c r="N23" t="b">
-        <v>0</v>
-      </c>
-      <c r="O23" t="b">
-        <v>1</v>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>Raat Ki Rani in our everyday ritual.</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>A Mysaa Rituals everyday ritual in the Raat Ki Rani fragrance. Made for gifting, rituals and everyday moments.</t>
+        </is>
       </c>
       <c r="P23" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q23" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="Q23" t="b">
+        <v>0</v>
+      </c>
+      <c r="R23" t="b">
+        <v>1</v>
+      </c>
+      <c r="S23" t="b">
+        <v>1</v>
+      </c>
+      <c r="T23" t="inlineStr">
         <is>
           <t>assets/catalogue/raat-ki-rani/wide-jar-candle/01-cover.jpg</t>
         </is>
       </c>
-      <c r="R23" t="inlineStr">
+      <c r="U23" t="inlineStr">
         <is>
           <t>assets/catalogue/raat-ki-rani/wide-jar-candle/02-detail.jpg</t>
         </is>
       </c>
-      <c r="S23" t="inlineStr">
+      <c r="V23" t="inlineStr">
         <is>
           <t>assets/catalogue/raat-ki-rani/wide-jar-candle/03-lifestyle.jpg</t>
         </is>
@@ -3070,7 +2664,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Raat Ki Rani Shot Glass Candle</t>
+          <t>Raat Ki Rani Mini Ritual</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -3084,59 +2678,67 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>399</v>
+        <v>332.22</v>
       </c>
       <c r="F24" t="n">
         <v>299</v>
       </c>
-      <c r="G24" t="inlineStr">
+      <c r="G24" t="n">
+        <v>10</v>
+      </c>
+      <c r="H24" t="n">
+        <v>1</v>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr">
         <is>
           <t>60 ml</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr">
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr">
         <is>
           <t>Natural soy wax, cotton wick, phthalate-free fragrance oils</t>
         </is>
       </c>
-      <c r="J24" t="inlineStr">
+      <c r="M24" t="inlineStr">
         <is>
           <t>Mysaa Rituals signature packaging</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>Raat Ki Rani in our shot glass candle.</t>
-        </is>
-      </c>
-      <c r="L24" t="inlineStr">
-        <is>
-          <t>A Mysaa Rituals shot glass candle in the Raat Ki Rani fragrance. Made for gifting, rituals and everyday moments.</t>
-        </is>
-      </c>
-      <c r="M24" t="b">
-        <v>0</v>
-      </c>
-      <c r="N24" t="b">
-        <v>0</v>
-      </c>
-      <c r="O24" t="b">
-        <v>1</v>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>Raat Ki Rani in our mini ritual.</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>A Mysaa Rituals mini ritual in the Raat Ki Rani fragrance. Made for gifting, rituals and everyday moments.</t>
+        </is>
       </c>
       <c r="P24" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q24" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="Q24" t="b">
+        <v>0</v>
+      </c>
+      <c r="R24" t="b">
+        <v>1</v>
+      </c>
+      <c r="S24" t="b">
+        <v>1</v>
+      </c>
+      <c r="T24" t="inlineStr">
         <is>
           <t>assets/catalogue/raat-ki-rani/shot-glass-candle/01-cover.jpg</t>
         </is>
       </c>
-      <c r="R24" t="inlineStr">
+      <c r="U24" t="inlineStr">
         <is>
           <t>assets/catalogue/raat-ki-rani/shot-glass-candle/02-detail.jpg</t>
         </is>
       </c>
-      <c r="S24" t="inlineStr">
+      <c r="V24" t="inlineStr">
         <is>
           <t>assets/catalogue/raat-ki-rani/shot-glass-candle/03-lifestyle.jpg</t>
         </is>
@@ -3163,57 +2765,68 @@
           <t>raat-ki-rani</t>
         </is>
       </c>
+      <c r="E25" t="n">
+        <v>0</v>
+      </c>
       <c r="F25" t="n">
         <v>350</v>
       </c>
-      <c r="G25" t="inlineStr">
+      <c r="G25" t="n">
+        <v>0</v>
+      </c>
+      <c r="H25" t="n">
+        <v>1</v>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr">
         <is>
           <t>Combo</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr">
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr">
         <is>
           <t>Natural soy wax, cotton wick, phthalate-free fragrance oils</t>
         </is>
       </c>
-      <c r="J25" t="inlineStr">
+      <c r="M25" t="inlineStr">
         <is>
           <t>Mysaa Rituals signature packaging</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr">
+      <c r="N25" t="inlineStr">
         <is>
           <t>Raat Ki Rani in our wax sachet combo.</t>
         </is>
       </c>
-      <c r="L25" t="inlineStr">
+      <c r="O25" t="inlineStr">
         <is>
           <t>A Mysaa Rituals wax sachet combo in the Raat Ki Rani fragrance. Made for gifting, rituals and everyday moments.</t>
         </is>
       </c>
-      <c r="M25" t="b">
-        <v>0</v>
-      </c>
-      <c r="N25" t="b">
-        <v>0</v>
-      </c>
-      <c r="O25" t="b">
-        <v>1</v>
-      </c>
       <c r="P25" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q25" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="Q25" t="b">
+        <v>0</v>
+      </c>
+      <c r="R25" t="b">
+        <v>1</v>
+      </c>
+      <c r="S25" t="b">
+        <v>1</v>
+      </c>
+      <c r="T25" t="inlineStr">
         <is>
           <t>assets/catalogue/raat-ki-rani/wax-melts/01-cover.jpg</t>
         </is>
       </c>
-      <c r="R25" t="inlineStr">
+      <c r="U25" t="inlineStr">
         <is>
           <t>assets/catalogue/raat-ki-rani/wax-melts/02-detail.jpg</t>
         </is>
       </c>
-      <c r="S25" t="inlineStr">
+      <c r="V25" t="inlineStr">
         <is>
           <t>assets/catalogue/raat-ki-rani/wax-melts/03-lifestyle.jpg</t>
         </is>
@@ -3240,57 +2853,68 @@
           <t>raat-ki-rani</t>
         </is>
       </c>
+      <c r="E26" t="n">
+        <v>0</v>
+      </c>
       <c r="F26" t="n">
         <v>0</v>
       </c>
-      <c r="G26" t="inlineStr">
+      <c r="G26" t="n">
+        <v>0</v>
+      </c>
+      <c r="H26" t="n">
+        <v>1</v>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr">
         <is>
           <t>Curated set</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr">
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr">
         <is>
           <t>Curated Mysaa Rituals gifting selection</t>
         </is>
       </c>
-      <c r="J26" t="inlineStr">
+      <c r="M26" t="inlineStr">
         <is>
           <t>Mysaa Rituals signature packaging</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr">
+      <c r="N26" t="inlineStr">
         <is>
           <t>Raat Ki Rani in our gift hamper.</t>
         </is>
       </c>
-      <c r="L26" t="inlineStr">
+      <c r="O26" t="inlineStr">
         <is>
           <t>A Mysaa Rituals gift hamper in the Raat Ki Rani fragrance. Made for gifting, rituals and everyday moments.</t>
         </is>
       </c>
-      <c r="M26" t="b">
-        <v>0</v>
-      </c>
-      <c r="N26" t="b">
-        <v>0</v>
-      </c>
-      <c r="O26" t="b">
-        <v>1</v>
-      </c>
       <c r="P26" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q26" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="Q26" t="b">
+        <v>0</v>
+      </c>
+      <c r="R26" t="b">
+        <v>1</v>
+      </c>
+      <c r="S26" t="b">
+        <v>1</v>
+      </c>
+      <c r="T26" t="inlineStr">
         <is>
           <t>assets/catalogue/raat-ki-rani/gift-hampers/01-cover.jpg</t>
         </is>
       </c>
-      <c r="R26" t="inlineStr">
+      <c r="U26" t="inlineStr">
         <is>
           <t>assets/catalogue/raat-ki-rani/gift-hampers/02-detail.jpg</t>
         </is>
       </c>
-      <c r="S26" t="inlineStr">
+      <c r="V26" t="inlineStr">
         <is>
           <t>assets/catalogue/raat-ki-rani/gift-hampers/03-lifestyle.jpg</t>
         </is>
@@ -3304,7 +2928,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Saanjh Hero Jar Candle</t>
+          <t>Saanjh Signature</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -3318,59 +2942,67 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>899</v>
+        <v>998.75</v>
       </c>
       <c r="F27" t="n">
         <v>799</v>
       </c>
-      <c r="G27" t="inlineStr">
+      <c r="G27" t="n">
+        <v>20</v>
+      </c>
+      <c r="H27" t="n">
+        <v>1</v>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr">
         <is>
           <t>220 ml</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr">
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr">
         <is>
           <t>Natural soy wax, cotton wick, phthalate-free fragrance oils</t>
         </is>
       </c>
-      <c r="J27" t="inlineStr">
+      <c r="M27" t="inlineStr">
         <is>
           <t>Mysaa Rituals signature packaging</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>Saanjh in our hero jar candle.</t>
-        </is>
-      </c>
-      <c r="L27" t="inlineStr">
-        <is>
-          <t>A Mysaa Rituals hero jar candle in the Saanjh fragrance — creamy vanilla softened by deep sandalwood, made for gifting, rituals and everyday moments.</t>
-        </is>
-      </c>
-      <c r="M27" t="b">
-        <v>0</v>
-      </c>
-      <c r="N27" t="b">
-        <v>0</v>
-      </c>
-      <c r="O27" t="b">
-        <v>1</v>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>Saanjh in our signature.</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>A Mysaa Rituals signature in the Saanjh fragrance — creamy vanilla softened by deep sandalwood, made for gifting, rituals and everyday moments.</t>
+        </is>
       </c>
       <c r="P27" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q27" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="Q27" t="b">
+        <v>0</v>
+      </c>
+      <c r="R27" t="b">
+        <v>1</v>
+      </c>
+      <c r="S27" t="b">
+        <v>1</v>
+      </c>
+      <c r="T27" t="inlineStr">
         <is>
           <t>assets/catalogue/saanjh/hero-jar-candle/01-cover.jpg</t>
         </is>
       </c>
-      <c r="R27" t="inlineStr">
+      <c r="U27" t="inlineStr">
         <is>
           <t>assets/catalogue/saanjh/hero-jar-candle/02-detail.jpg</t>
         </is>
       </c>
-      <c r="S27" t="inlineStr">
+      <c r="V27" t="inlineStr">
         <is>
           <t>assets/catalogue/saanjh/hero-jar-candle/03-lifestyle.jpg</t>
         </is>
@@ -3384,7 +3016,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Saanjh Wide Jar Candle</t>
+          <t>Saanjh Everyday Ritual</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -3398,59 +3030,67 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>699</v>
+        <v>645.88</v>
       </c>
       <c r="F28" t="n">
         <v>549</v>
       </c>
-      <c r="G28" t="inlineStr">
+      <c r="G28" t="n">
+        <v>15</v>
+      </c>
+      <c r="H28" t="n">
+        <v>1</v>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr">
         <is>
           <t>120 ml</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr">
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr">
         <is>
           <t>Natural soy wax, cotton wick, phthalate-free fragrance oils</t>
         </is>
       </c>
-      <c r="J28" t="inlineStr">
+      <c r="M28" t="inlineStr">
         <is>
           <t>Mysaa Rituals signature packaging</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>Saanjh in our wide jar candle.</t>
-        </is>
-      </c>
-      <c r="L28" t="inlineStr">
-        <is>
-          <t>A Mysaa Rituals wide jar candle in the Saanjh fragrance — creamy vanilla softened by deep sandalwood, made for gifting, rituals and everyday moments.</t>
-        </is>
-      </c>
-      <c r="M28" t="b">
-        <v>0</v>
-      </c>
-      <c r="N28" t="b">
-        <v>1</v>
-      </c>
-      <c r="O28" t="b">
-        <v>1</v>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>Saanjh in our everyday ritual.</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>A Mysaa Rituals everyday ritual in the Saanjh fragrance — creamy vanilla softened by deep sandalwood, made for gifting, rituals and everyday moments.</t>
+        </is>
       </c>
       <c r="P28" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q28" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="Q28" t="b">
+        <v>1</v>
+      </c>
+      <c r="R28" t="b">
+        <v>1</v>
+      </c>
+      <c r="S28" t="b">
+        <v>1</v>
+      </c>
+      <c r="T28" t="inlineStr">
         <is>
           <t>assets/catalogue/saanjh/wide-jar-candle/01-cover.jpg</t>
         </is>
       </c>
-      <c r="R28" t="inlineStr">
+      <c r="U28" t="inlineStr">
         <is>
           <t>assets/catalogue/saanjh/wide-jar-candle/02-detail.jpg</t>
         </is>
       </c>
-      <c r="S28" t="inlineStr">
+      <c r="V28" t="inlineStr">
         <is>
           <t>assets/catalogue/saanjh/wide-jar-candle/03-lifestyle.jpg</t>
         </is>
@@ -3464,7 +3104,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Saanjh Shot Glass Candle</t>
+          <t>Saanjh Mini Ritual</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -3478,59 +3118,67 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>399</v>
+        <v>332.22</v>
       </c>
       <c r="F29" t="n">
         <v>299</v>
       </c>
-      <c r="G29" t="inlineStr">
+      <c r="G29" t="n">
+        <v>10</v>
+      </c>
+      <c r="H29" t="n">
+        <v>1</v>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr">
         <is>
           <t>60 ml</t>
         </is>
       </c>
-      <c r="I29" t="inlineStr">
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr">
         <is>
           <t>Natural soy wax, cotton wick, phthalate-free fragrance oils</t>
         </is>
       </c>
-      <c r="J29" t="inlineStr">
+      <c r="M29" t="inlineStr">
         <is>
           <t>Mysaa Rituals signature packaging</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>Saanjh in our shot glass candle.</t>
-        </is>
-      </c>
-      <c r="L29" t="inlineStr">
-        <is>
-          <t>A Mysaa Rituals shot glass candle in the Saanjh fragrance — creamy vanilla softened by deep sandalwood, made for gifting, rituals and everyday moments.</t>
-        </is>
-      </c>
-      <c r="M29" t="b">
-        <v>0</v>
-      </c>
-      <c r="N29" t="b">
-        <v>0</v>
-      </c>
-      <c r="O29" t="b">
-        <v>1</v>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>Saanjh in our mini ritual.</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>A Mysaa Rituals mini ritual in the Saanjh fragrance — creamy vanilla softened by deep sandalwood, made for gifting, rituals and everyday moments.</t>
+        </is>
       </c>
       <c r="P29" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q29" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="Q29" t="b">
+        <v>0</v>
+      </c>
+      <c r="R29" t="b">
+        <v>1</v>
+      </c>
+      <c r="S29" t="b">
+        <v>1</v>
+      </c>
+      <c r="T29" t="inlineStr">
         <is>
           <t>assets/catalogue/saanjh/shot-glass-candle/01-cover.jpg</t>
         </is>
       </c>
-      <c r="R29" t="inlineStr">
+      <c r="U29" t="inlineStr">
         <is>
           <t>assets/catalogue/saanjh/shot-glass-candle/02-detail.jpg</t>
         </is>
       </c>
-      <c r="S29" t="inlineStr">
+      <c r="V29" t="inlineStr">
         <is>
           <t>assets/catalogue/saanjh/shot-glass-candle/03-lifestyle.jpg</t>
         </is>
@@ -3557,52 +3205,64 @@
           <t>saanjh</t>
         </is>
       </c>
+      <c r="E30" t="n">
+        <v>0</v>
+      </c>
       <c r="F30" t="n">
         <v>350</v>
       </c>
-      <c r="I30" t="inlineStr">
+      <c r="G30" t="n">
+        <v>0</v>
+      </c>
+      <c r="H30" t="n">
+        <v>1</v>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr">
         <is>
           <t>Natural soy wax, cotton wick, phthalate-free fragrance oils</t>
         </is>
       </c>
-      <c r="J30" t="inlineStr">
+      <c r="M30" t="inlineStr">
         <is>
           <t>Mysaa Rituals signature packaging</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr">
+      <c r="N30" t="inlineStr">
         <is>
           <t>Saanjh in our wax sachet combo.</t>
         </is>
       </c>
-      <c r="L30" t="inlineStr">
+      <c r="O30" t="inlineStr">
         <is>
           <t>A Mysaa Rituals wax sachet combo in the Saanjh fragrance — creamy vanilla softened by deep sandalwood, made for gifting, rituals and everyday moments.</t>
         </is>
       </c>
-      <c r="M30" t="b">
-        <v>0</v>
-      </c>
-      <c r="N30" t="b">
-        <v>0</v>
-      </c>
-      <c r="O30" t="b">
-        <v>1</v>
-      </c>
       <c r="P30" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q30" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="Q30" t="b">
+        <v>0</v>
+      </c>
+      <c r="R30" t="b">
+        <v>1</v>
+      </c>
+      <c r="S30" t="b">
+        <v>1</v>
+      </c>
+      <c r="T30" t="inlineStr">
         <is>
           <t>assets/catalogue/saanjh/wax-melts/01-cover.jpg</t>
         </is>
       </c>
-      <c r="R30" t="inlineStr">
+      <c r="U30" t="inlineStr">
         <is>
           <t>assets/catalogue/saanjh/wax-melts/02-detail.jpg</t>
         </is>
       </c>
-      <c r="S30" t="inlineStr">
+      <c r="V30" t="inlineStr">
         <is>
           <t>assets/catalogue/saanjh/wax-melts/03-lifestyle.jpg</t>
         </is>
@@ -3629,52 +3289,64 @@
           <t>saanjh</t>
         </is>
       </c>
+      <c r="E31" t="n">
+        <v>0</v>
+      </c>
       <c r="F31" t="n">
         <v>0</v>
       </c>
-      <c r="I31" t="inlineStr">
+      <c r="G31" t="n">
+        <v>0</v>
+      </c>
+      <c r="H31" t="n">
+        <v>1</v>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr">
         <is>
           <t>Natural soy wax, cotton wick, phthalate-free fragrance oils</t>
         </is>
       </c>
-      <c r="J31" t="inlineStr">
+      <c r="M31" t="inlineStr">
         <is>
           <t>Mysaa Rituals signature packaging</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr">
+      <c r="N31" t="inlineStr">
         <is>
           <t>Saanjh in our gift hamper.</t>
         </is>
       </c>
-      <c r="L31" t="inlineStr">
+      <c r="O31" t="inlineStr">
         <is>
           <t>A Mysaa Rituals gift hamper in the Saanjh fragrance — creamy vanilla softened by deep sandalwood, made for gifting, rituals and everyday moments.</t>
         </is>
       </c>
-      <c r="M31" t="b">
-        <v>0</v>
-      </c>
-      <c r="N31" t="b">
-        <v>0</v>
-      </c>
-      <c r="O31" t="b">
-        <v>1</v>
-      </c>
       <c r="P31" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q31" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="Q31" t="b">
+        <v>0</v>
+      </c>
+      <c r="R31" t="b">
+        <v>1</v>
+      </c>
+      <c r="S31" t="b">
+        <v>1</v>
+      </c>
+      <c r="T31" t="inlineStr">
         <is>
           <t>assets/catalogue/saanjh/gift-hampers/01-cover.jpg</t>
         </is>
       </c>
-      <c r="R31" t="inlineStr">
+      <c r="U31" t="inlineStr">
         <is>
           <t>assets/catalogue/saanjh/gift-hampers/02-detail.jpg</t>
         </is>
       </c>
-      <c r="S31" t="inlineStr">
+      <c r="V31" t="inlineStr">
         <is>
           <t>assets/catalogue/saanjh/gift-hampers/03-lifestyle.jpg</t>
         </is>
@@ -3688,7 +3360,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Mysaa Rituals Discover Set</t>
+          <t>Mysaa Rituals Discovery Set</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -3702,63 +3374,602 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1999</v>
+        <v>2123.75</v>
       </c>
       <c r="F32" t="n">
         <v>1699</v>
       </c>
-      <c r="G32" t="inlineStr">
+      <c r="G32" t="n">
+        <v>20</v>
+      </c>
+      <c r="H32" t="n">
+        <v>1</v>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr">
         <is>
           <t>6 × 60 ml</t>
         </is>
       </c>
-      <c r="I32" t="inlineStr">
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr">
         <is>
           <t>Natural soy wax, cotton wick, phthalate-free fragrance oils</t>
         </is>
       </c>
-      <c r="J32" t="inlineStr">
+      <c r="M32" t="inlineStr">
         <is>
           <t>Discover Set presentation box</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>All six Mysaa Rituals fragrances in six 60 ml shot glass jar candles.</t>
-        </is>
-      </c>
-      <c r="L32" t="inlineStr">
-        <is>
-          <t>A discovery set featuring all six Mysaa Rituals fragrances — six 60 ml shot glass jar candles designed to let you experience the full fragrance collection in one beautiful set.</t>
-        </is>
-      </c>
-      <c r="M32" t="b">
-        <v>0</v>
-      </c>
-      <c r="N32" t="b">
-        <v>1</v>
-      </c>
-      <c r="O32" t="b">
-        <v>0</v>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>All six Mysaa Rituals fragrances in six 60 ml Mini Ritual candles.</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>A complete discovery of all six Mysaa Rituals fragrances, presented as six 60 ml Mini Ritual candles.</t>
+        </is>
       </c>
       <c r="P32" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q32" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="Q32" t="b">
+        <v>1</v>
+      </c>
+      <c r="R32" t="b">
+        <v>0</v>
+      </c>
+      <c r="S32" t="b">
+        <v>1</v>
+      </c>
+      <c r="T32" t="inlineStr">
         <is>
           <t>assets/catalogue/all-fragrances/discovery-set/01-discover-set.jpg</t>
         </is>
       </c>
-      <c r="R32" t="inlineStr">
+      <c r="U32" t="inlineStr">
         <is>
           <t>assets/catalogue/all-fragrances/discovery-set/02-gulab-ki-chitthi.jpg</t>
         </is>
       </c>
-      <c r="S32" t="inlineStr">
+      <c r="V32" t="inlineStr">
         <is>
           <t>assets/catalogue/all-fragrances/discovery-set/03-dhoop-chandan.jpg</t>
         </is>
       </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>gulab-ki-chitthi-grand-ritual</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Gulab Ki Chitthi Grand Ritual</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>grand-ritual</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>gulab-ki-chitthi</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>0</v>
+      </c>
+      <c r="F33" t="n">
+        <v>0</v>
+      </c>
+      <c r="G33" t="n">
+        <v>0</v>
+      </c>
+      <c r="H33" t="n">
+        <v>1</v>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>450 ml · 3 wick</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>Natural soy wax, cotton wicks, phthalate-free fragrance oils</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>Mysaa Rituals signature packaging</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>Gulab Ki Chitthi in our Grand Ritual — a 450 ml, 3-wick luxury candle.</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>A luxurious 450 ml, 3-wick Mysaa Rituals Grand Ritual in the Gulab Ki Chitthi fragrance. Designed for statement gifting and elevated spaces.</t>
+        </is>
+      </c>
+      <c r="P33" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q33" t="b">
+        <v>1</v>
+      </c>
+      <c r="R33" t="b">
+        <v>1</v>
+      </c>
+      <c r="S33" t="b">
+        <v>1</v>
+      </c>
+      <c r="T33" t="inlineStr"/>
+      <c r="U33" t="inlineStr"/>
+      <c r="V33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>dhoop-chandan-grand-ritual</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Dhoop &amp; Chandan Grand Ritual</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>grand-ritual</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>dhoop-chandan</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>0</v>
+      </c>
+      <c r="F34" t="n">
+        <v>0</v>
+      </c>
+      <c r="G34" t="n">
+        <v>0</v>
+      </c>
+      <c r="H34" t="n">
+        <v>1</v>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>450 ml · 3 wick</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>Natural soy wax, cotton wicks, phthalate-free fragrance oils</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>Mysaa Rituals signature packaging</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>Dhoop &amp; Chandan in our Grand Ritual — a 450 ml, 3-wick luxury candle.</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>A luxurious 450 ml, 3-wick Mysaa Rituals Grand Ritual in the Dhoop &amp; Chandan fragrance. Designed for statement gifting and elevated spaces.</t>
+        </is>
+      </c>
+      <c r="P34" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q34" t="b">
+        <v>1</v>
+      </c>
+      <c r="R34" t="b">
+        <v>1</v>
+      </c>
+      <c r="S34" t="b">
+        <v>1</v>
+      </c>
+      <c r="T34" t="inlineStr"/>
+      <c r="U34" t="inlineStr"/>
+      <c r="V34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>gajre-ka-shringar-grand-ritual</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Gajre Ka Shringar Grand Ritual</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>grand-ritual</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>gajre-ka-shringar</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>0</v>
+      </c>
+      <c r="F35" t="n">
+        <v>0</v>
+      </c>
+      <c r="G35" t="n">
+        <v>0</v>
+      </c>
+      <c r="H35" t="n">
+        <v>1</v>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>450 ml · 3 wick</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>Natural soy wax, cotton wicks, phthalate-free fragrance oils</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>Mysaa Rituals signature packaging</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>Gajre Ka Shringar in our Grand Ritual — a 450 ml, 3-wick luxury candle.</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>A luxurious 450 ml, 3-wick Mysaa Rituals Grand Ritual in the Gajre Ka Shringar fragrance. Designed for statement gifting and elevated spaces.</t>
+        </is>
+      </c>
+      <c r="P35" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q35" t="b">
+        <v>1</v>
+      </c>
+      <c r="R35" t="b">
+        <v>1</v>
+      </c>
+      <c r="S35" t="b">
+        <v>1</v>
+      </c>
+      <c r="T35" t="inlineStr"/>
+      <c r="U35" t="inlineStr"/>
+      <c r="V35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>madhuban-grand-ritual</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Madhuban Grand Ritual</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>grand-ritual</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>madhuban</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>0</v>
+      </c>
+      <c r="F36" t="n">
+        <v>0</v>
+      </c>
+      <c r="G36" t="n">
+        <v>0</v>
+      </c>
+      <c r="H36" t="n">
+        <v>1</v>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>450 ml · 3 wick</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>Natural soy wax, cotton wicks, phthalate-free fragrance oils</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>Mysaa Rituals signature packaging</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>Madhuban in our Grand Ritual — a 450 ml, 3-wick luxury candle.</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>A luxurious 450 ml, 3-wick Mysaa Rituals Grand Ritual in the Madhuban fragrance. Designed for statement gifting and elevated spaces.</t>
+        </is>
+      </c>
+      <c r="P36" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q36" t="b">
+        <v>1</v>
+      </c>
+      <c r="R36" t="b">
+        <v>1</v>
+      </c>
+      <c r="S36" t="b">
+        <v>1</v>
+      </c>
+      <c r="T36" t="inlineStr"/>
+      <c r="U36" t="inlineStr"/>
+      <c r="V36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>raat-ki-rani-grand-ritual</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Raat Ki Rani Grand Ritual</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>grand-ritual</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>raat-ki-rani</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>0</v>
+      </c>
+      <c r="F37" t="n">
+        <v>0</v>
+      </c>
+      <c r="G37" t="n">
+        <v>0</v>
+      </c>
+      <c r="H37" t="n">
+        <v>1</v>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>450 ml · 3 wick</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>Natural soy wax, cotton wicks, phthalate-free fragrance oils</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>Mysaa Rituals signature packaging</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>Raat Ki Rani in our Grand Ritual — a 450 ml, 3-wick luxury candle.</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>A luxurious 450 ml, 3-wick Mysaa Rituals Grand Ritual in the Raat Ki Rani fragrance. Designed for statement gifting and elevated spaces.</t>
+        </is>
+      </c>
+      <c r="P37" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q37" t="b">
+        <v>1</v>
+      </c>
+      <c r="R37" t="b">
+        <v>1</v>
+      </c>
+      <c r="S37" t="b">
+        <v>1</v>
+      </c>
+      <c r="T37" t="inlineStr"/>
+      <c r="U37" t="inlineStr"/>
+      <c r="V37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>saanjh-grand-ritual</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Saanjh Grand Ritual</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>grand-ritual</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>saanjh</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>0</v>
+      </c>
+      <c r="F38" t="n">
+        <v>0</v>
+      </c>
+      <c r="G38" t="n">
+        <v>0</v>
+      </c>
+      <c r="H38" t="n">
+        <v>1</v>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>450 ml · 3 wick</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>Natural soy wax, cotton wicks, phthalate-free fragrance oils</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>Mysaa Rituals signature packaging</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>Saanjh in our Grand Ritual — a 450 ml, 3-wick luxury candle.</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>A luxurious 450 ml, 3-wick Mysaa Rituals Grand Ritual in the Saanjh fragrance. Designed for statement gifting and elevated spaces.</t>
+        </is>
+      </c>
+      <c r="P38" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q38" t="b">
+        <v>1</v>
+      </c>
+      <c r="R38" t="b">
+        <v>1</v>
+      </c>
+      <c r="S38" t="b">
+        <v>1</v>
+      </c>
+      <c r="T38" t="inlineStr"/>
+      <c r="U38" t="inlineStr"/>
+      <c r="V38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>mold-candles</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Mold Candles</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>mold-candles</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>0</v>
+      </c>
+      <c r="F39" t="n">
+        <v>0</v>
+      </c>
+      <c r="G39" t="n">
+        <v>0</v>
+      </c>
+      <c r="H39" t="n">
+        <v>6</v>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>Daisy|Rose|Carnation|Cactus|Tortoise|Laddu|Chakli</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>MOQ 6 pieces</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>Hand-poured wax candle</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>Mysaa Rituals signature packaging</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>Choose from Daisy, Rose, Carnation, Cactus, Tortoise, Laddu or Chakli moulds. Minimum order 6 pieces.</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>A playful collection of handcrafted mould candles. Select one mould style for a minimum batch of 6 pieces.</t>
+        </is>
+      </c>
+      <c r="P39" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q39" t="b">
+        <v>1</v>
+      </c>
+      <c r="R39" t="b">
+        <v>1</v>
+      </c>
+      <c r="S39" t="b">
+        <v>1</v>
+      </c>
+      <c r="T39" t="inlineStr"/>
+      <c r="U39" t="inlineStr"/>
+      <c r="V39" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3772,9 +3983,10 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:F7"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14.5" outlineLevelRow="5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="19" customWidth="1" min="1" max="2"/>
+    <col width="19" customWidth="1" min="1" max="1"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
     <col width="43" customWidth="1" min="3" max="3"/>
     <col width="50" customWidth="1" min="4" max="4"/>
     <col width="45" customWidth="1" min="5" max="5"/>
@@ -3782,32 +3994,32 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="2" t="inlineStr">
         <is>
           <t>slug</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="2" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="2" t="inlineStr">
         <is>
           <t>notes</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" s="2" t="inlineStr">
         <is>
           <t>description</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" s="2" t="inlineStr">
         <is>
           <t>mood</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" s="2" t="inlineStr">
         <is>
           <t>active</t>
         </is>
@@ -3916,7 +4128,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Raat ki Rani, rose, deep florals</t>
+          <t>Jasmine, rose</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -4004,31 +4216,32 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D7"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14.5" outlineLevelRow="5"/>
+  <dimension ref="A1:D9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="19" customWidth="1" min="1" max="2"/>
-    <col width="21" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="35" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="2" t="inlineStr">
         <is>
           <t>slug</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="2" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="2" t="inlineStr">
         <is>
           <t>subtitle</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" s="2" t="inlineStr">
         <is>
           <t>active</t>
         </is>
@@ -4042,7 +4255,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Hero Jar Candle</t>
+          <t>Signature</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -4062,7 +4275,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Wide Jar Candle</t>
+          <t>Everyday Ritual</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -4082,7 +4295,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Shot Glass Candle</t>
+          <t>Mini Ritual</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -4147,10 +4360,50 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>6 × 60 ml shot glass candles</t>
+          <t>6 × 60 ml Mini Ritual candles</t>
         </is>
       </c>
       <c r="D7" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>grand-ritual</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Grand Ritual</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>450 ml · 3-wick luxury appearance</t>
+        </is>
+      </c>
+      <c r="D8" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>mold-candles</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Mold Candles</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>MOQ 6 pieces · choose your shape</t>
+        </is>
+      </c>
+      <c r="D9" t="b">
         <v>1</v>
       </c>
     </row>
@@ -4165,20 +4418,20 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B11"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14.5"/>
+  <dimension ref="A1:B23"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="17" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="1" max="1"/>
     <col width="50" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="2" t="inlineStr">
         <is>
           <t>key</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="2" t="inlineStr">
         <is>
           <t>value</t>
         </is>
@@ -4214,7 +4467,7 @@
           <t>whatsapp</t>
         </is>
       </c>
-      <c r="B4" s="4" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>919919115120</t>
         </is>
@@ -4226,7 +4479,7 @@
           <t>phone</t>
         </is>
       </c>
-      <c r="B5" s="4" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>+91 9919115120</t>
         </is>
@@ -4238,7 +4491,7 @@
           <t>email</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>mysaarituals@gmail.com</t>
         </is>
@@ -4304,10 +4557,140 @@
         </is>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>feedbackUrl</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>https://forms.cloud.microsoft/r/6S4JFC1WaX?origin=QRCode</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>feedbackQr</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>./assets/feedback-qr.jpeg</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>connectQr</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>./assets/connect-qr.jpeg</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>giftWrapEnabled</t>
+        </is>
+      </c>
+      <c r="B15" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>giftWrapCharge</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>festivalBannerEnabled</t>
+        </is>
+      </c>
+      <c r="B17" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>festivalBannerEyebrow</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Upcoming · Navratri &amp; Dussehra</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>festivalBannerTitle</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Light up the season. Gift a little warmth.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>festivalBannerText</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Bring home thoughtful candles and gifts for Navratri, Dussehra and the festive celebrations ahead.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>festivalBannerButtonText</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Shop the Festive Collection</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>festivalBannerCategory</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>festivals-celebrations</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>festivalBannerImage</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B6" display="mysaarituals@gmail.com" r:id="rId1"/>
-  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/mysaa_products.xlsx
+++ b/data/mysaa_products.xlsx
@@ -507,7 +507,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t xml:space="preserve">   mold-candles, wax-melts, gift-hampers, discovery-set. A product's categorySlug must match one</t>
+          <t xml:space="preserve">   mold-candles, wax-melts, gift-hampers, discovery-set, grand-ritual. A product's categorySlug must match one</t>
         </is>
       </c>
     </row>
@@ -581,7 +581,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V39"/>
+  <dimension ref="A1:X39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="37" customWidth="1" min="1" max="1"/>
@@ -592,20 +592,22 @@
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="17" customWidth="1" min="7" max="7"/>
     <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="50" customWidth="1" min="9" max="9"/>
-    <col width="17" customWidth="1" min="10" max="10"/>
-    <col width="12" customWidth="1" min="11" max="11"/>
-    <col width="50" customWidth="1" min="12" max="12"/>
-    <col width="35" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="24" customWidth="1" min="10" max="10"/>
+    <col width="50" customWidth="1" min="11" max="11"/>
+    <col width="18" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
     <col width="50" customWidth="1" min="14" max="14"/>
-    <col width="50" customWidth="1" min="15" max="15"/>
-    <col width="12" customWidth="1" min="16" max="16"/>
-    <col width="12" customWidth="1" min="17" max="17"/>
-    <col width="14" customWidth="1" min="18" max="18"/>
+    <col width="35" customWidth="1" min="15" max="15"/>
+    <col width="50" customWidth="1" min="16" max="16"/>
+    <col width="50" customWidth="1" min="17" max="17"/>
+    <col width="12" customWidth="1" min="18" max="18"/>
     <col width="12" customWidth="1" min="19" max="19"/>
-    <col width="50" customWidth="1" min="20" max="20"/>
-    <col width="50" customWidth="1" min="21" max="21"/>
+    <col width="14" customWidth="1" min="20" max="20"/>
+    <col width="12" customWidth="1" min="21" max="21"/>
     <col width="50" customWidth="1" min="22" max="22"/>
+    <col width="50" customWidth="1" min="23" max="23"/>
+    <col width="50" customWidth="1" min="24" max="24"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -651,70 +653,80 @@
       </c>
       <c r="I1" s="2" t="inlineStr">
         <is>
+          <t>availability</t>
+        </is>
+      </c>
+      <c r="J1" s="2" t="inlineStr">
+        <is>
+          <t>occasionSlugs</t>
+        </is>
+      </c>
+      <c r="K1" s="2" t="inlineStr">
+        <is>
           <t>optionValues</t>
         </is>
       </c>
-      <c r="J1" s="2" t="inlineStr">
+      <c r="L1" s="2" t="inlineStr">
         <is>
           <t>volume</t>
         </is>
       </c>
-      <c r="K1" s="2" t="inlineStr">
+      <c r="M1" s="2" t="inlineStr">
         <is>
           <t>weight</t>
         </is>
       </c>
-      <c r="L1" s="2" t="inlineStr">
+      <c r="N1" s="2" t="inlineStr">
         <is>
           <t>materials</t>
         </is>
       </c>
-      <c r="M1" s="2" t="inlineStr">
+      <c r="O1" s="2" t="inlineStr">
         <is>
           <t>packaging</t>
         </is>
       </c>
-      <c r="N1" s="2" t="inlineStr">
+      <c r="P1" s="2" t="inlineStr">
         <is>
           <t>shortDescription</t>
         </is>
       </c>
-      <c r="O1" s="2" t="inlineStr">
+      <c r="Q1" s="2" t="inlineStr">
         <is>
           <t>about</t>
         </is>
       </c>
-      <c r="P1" s="2" t="inlineStr">
+      <c r="R1" s="2" t="inlineStr">
         <is>
           <t>bestseller</t>
         </is>
       </c>
-      <c r="Q1" s="2" t="inlineStr">
+      <c r="S1" s="2" t="inlineStr">
         <is>
           <t>isNew</t>
         </is>
       </c>
-      <c r="R1" s="2" t="inlineStr">
+      <c r="T1" s="2" t="inlineStr">
         <is>
           <t>customizable</t>
         </is>
       </c>
-      <c r="S1" s="2" t="inlineStr">
+      <c r="U1" s="2" t="inlineStr">
         <is>
           <t>active</t>
         </is>
       </c>
-      <c r="T1" s="2" t="inlineStr">
+      <c r="V1" s="2" t="inlineStr">
         <is>
           <t>image1</t>
         </is>
       </c>
-      <c r="U1" s="2" t="inlineStr">
+      <c r="W1" s="2" t="inlineStr">
         <is>
           <t>image2</t>
         </is>
       </c>
-      <c r="V1" s="2" t="inlineStr">
+      <c r="X1" s="2" t="inlineStr">
         <is>
           <t>image3</t>
         </is>
@@ -728,7 +740,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Gulab Ki Chitthi Signature</t>
+          <t>Gulab Ki Chitthi Signature Ritual</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -742,7 +754,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>998.75</v>
+        <v>1000</v>
       </c>
       <c r="F2" t="n">
         <v>799</v>
@@ -754,55 +766,57 @@
         <v>1</v>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>220 ml</t>
-        </is>
-      </c>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr">
         <is>
+          <t>220 ml</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr">
+        <is>
           <t>Natural soy wax, cotton wick, phthalate-free fragrance oils</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t>Mysaa Rituals signature packaging</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>Gulab Ki Chitthi in our signature.</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>A Mysaa Rituals signature in the Gulab Ki Chitthi fragrance. Made for gifting, rituals and everyday moments.</t>
-        </is>
-      </c>
-      <c r="P2" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q2" t="b">
-        <v>0</v>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>Gulab Ki Chitthi in our signature ritual.</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>A Mysaa Rituals signature ritual in the Gulab Ki Chitthi fragrance. Made for gifting, rituals and everyday moments.</t>
+        </is>
       </c>
       <c r="R2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S2" t="b">
-        <v>1</v>
-      </c>
-      <c r="T2" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="T2" t="b">
+        <v>1</v>
+      </c>
+      <c r="U2" t="b">
+        <v>1</v>
+      </c>
+      <c r="V2" t="inlineStr">
         <is>
           <t>assets/catalogue/gulab-ki-chitthi/hero-jar-candle/01-cover.jpg</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>assets/catalogue/gulab-ki-chitthi/hero-jar-candle/02-detail.jpg</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
+      <c r="X2" t="inlineStr">
         <is>
           <t>assets/catalogue/gulab-ki-chitthi/hero-jar-candle/03-lifestyle.jpg</t>
         </is>
@@ -830,7 +844,7 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>645.88</v>
+        <v>650</v>
       </c>
       <c r="F3" t="n">
         <v>549</v>
@@ -842,55 +856,57 @@
         <v>1</v>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>120 ml</t>
-        </is>
-      </c>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr">
         <is>
+          <t>120 ml</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr">
+        <is>
           <t>Natural soy wax, cotton wick, phthalate-free fragrance oils</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="O3" t="inlineStr">
         <is>
           <t>Mysaa Rituals signature packaging</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="P3" t="inlineStr">
         <is>
           <t>Gulab Ki Chitthi in our everyday ritual.</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
         <is>
           <t>A Mysaa Rituals everyday ritual in the Gulab Ki Chitthi fragrance. Made for gifting, rituals and everyday moments.</t>
         </is>
       </c>
-      <c r="P3" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q3" t="b">
-        <v>0</v>
-      </c>
       <c r="R3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S3" t="b">
-        <v>1</v>
-      </c>
-      <c r="T3" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="T3" t="b">
+        <v>1</v>
+      </c>
+      <c r="U3" t="b">
+        <v>1</v>
+      </c>
+      <c r="V3" t="inlineStr">
         <is>
           <t>assets/catalogue/gulab-ki-chitthi/wide-jar-candle/01-cover.jpg</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>assets/catalogue/gulab-ki-chitthi/wide-jar-candle/02-detail.jpg</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
+      <c r="X3" t="inlineStr">
         <is>
           <t>assets/catalogue/gulab-ki-chitthi/wide-jar-candle/03-lifestyle.jpg</t>
         </is>
@@ -918,7 +934,7 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>332.22</v>
+        <v>350</v>
       </c>
       <c r="F4" t="n">
         <v>299</v>
@@ -930,55 +946,57 @@
         <v>1</v>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>60 ml</t>
-        </is>
-      </c>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr">
         <is>
+          <t>60 ml</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr">
+        <is>
           <t>Natural soy wax, cotton wick, phthalate-free fragrance oils</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="O4" t="inlineStr">
         <is>
           <t>Mysaa Rituals signature packaging</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="P4" t="inlineStr">
         <is>
           <t>Gulab Ki Chitthi in our mini ritual.</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr">
+      <c r="Q4" t="inlineStr">
         <is>
           <t>A Mysaa Rituals mini ritual in the Gulab Ki Chitthi fragrance. Made for gifting, rituals and everyday moments.</t>
         </is>
       </c>
-      <c r="P4" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q4" t="b">
-        <v>0</v>
-      </c>
       <c r="R4" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S4" t="b">
-        <v>1</v>
-      </c>
-      <c r="T4" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="T4" t="b">
+        <v>1</v>
+      </c>
+      <c r="U4" t="b">
+        <v>1</v>
+      </c>
+      <c r="V4" t="inlineStr">
         <is>
           <t>assets/catalogue/gulab-ki-chitthi/shot-glass-candle/01-cover.jpg</t>
         </is>
       </c>
-      <c r="U4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>assets/catalogue/gulab-ki-chitthi/shot-glass-candle/02-detail.jpg</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr">
+      <c r="X4" t="inlineStr">
         <is>
           <t>assets/catalogue/gulab-ki-chitthi/shot-glass-candle/03-lifestyle.jpg</t>
         </is>
@@ -1017,56 +1035,62 @@
       <c r="H5" t="n">
         <v>1</v>
       </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>Combo</t>
-        </is>
-      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>out-of-stock</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr">
         <is>
+          <t>Combo</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr">
+        <is>
           <t>Natural soy wax, cotton wick, phthalate-free fragrance oils</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="O5" t="inlineStr">
         <is>
           <t>Mysaa Rituals signature packaging</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
+      <c r="P5" t="inlineStr">
         <is>
           <t>Gulab Ki Chitthi in our wax sachet combo.</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr">
+      <c r="Q5" t="inlineStr">
         <is>
           <t>A Mysaa Rituals wax sachet combo in the Gulab Ki Chitthi fragrance. Made for gifting, rituals and everyday moments.</t>
         </is>
       </c>
-      <c r="P5" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q5" t="b">
-        <v>0</v>
-      </c>
       <c r="R5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S5" t="b">
-        <v>1</v>
-      </c>
-      <c r="T5" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="T5" t="b">
+        <v>1</v>
+      </c>
+      <c r="U5" t="b">
+        <v>1</v>
+      </c>
+      <c r="V5" t="inlineStr">
         <is>
           <t>assets/catalogue/gulab-ki-chitthi/wax-melts/01-cover.jpg</t>
         </is>
       </c>
-      <c r="U5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>assets/catalogue/gulab-ki-chitthi/wax-melts/02-detail.jpg</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
+      <c r="X5" t="inlineStr">
         <is>
           <t>assets/catalogue/gulab-ki-chitthi/wax-melts/03-lifestyle.jpg</t>
         </is>
@@ -1108,53 +1132,59 @@
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Curated set</t>
+          <t>weddings-return-gifts</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr">
         <is>
+          <t>Curated set</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr">
+        <is>
           <t>Curated Mysaa Rituals gifting selection</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="O6" t="inlineStr">
         <is>
           <t>Mysaa Rituals signature packaging</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
+      <c r="P6" t="inlineStr">
         <is>
           <t>Gulab Ki Chitthi in our gift hamper.</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr">
+      <c r="Q6" t="inlineStr">
         <is>
           <t>A Mysaa Rituals gift hamper in the Gulab Ki Chitthi fragrance. Made for gifting, rituals and everyday moments.</t>
         </is>
       </c>
-      <c r="P6" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q6" t="b">
-        <v>0</v>
-      </c>
       <c r="R6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S6" t="b">
-        <v>1</v>
-      </c>
-      <c r="T6" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="T6" t="b">
+        <v>1</v>
+      </c>
+      <c r="U6" t="b">
+        <v>1</v>
+      </c>
+      <c r="V6" t="inlineStr">
         <is>
           <t>assets/catalogue/gulab-ki-chitthi/gift-hampers/01-cover.jpg</t>
         </is>
       </c>
-      <c r="U6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>assets/catalogue/gulab-ki-chitthi/gift-hampers/02-detail.jpg</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr">
+      <c r="X6" t="inlineStr">
         <is>
           <t>assets/catalogue/gulab-ki-chitthi/gift-hampers/03-lifestyle.jpg</t>
         </is>
@@ -1168,7 +1198,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Dhoop &amp; Chandan Signature</t>
+          <t>Dhoop &amp; Chandan Signature Ritual</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1182,7 +1212,7 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>998.75</v>
+        <v>1000</v>
       </c>
       <c r="F7" t="n">
         <v>799</v>
@@ -1194,55 +1224,57 @@
         <v>1</v>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>220 ml</t>
-        </is>
-      </c>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr">
         <is>
+          <t>220 ml</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr">
+        <is>
           <t>Natural soy wax, cotton wick, phthalate-free fragrance oils</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="O7" t="inlineStr">
         <is>
           <t>Mysaa Rituals signature packaging</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>Dhoop &amp; Chandan in our signature.</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>A Mysaa Rituals signature in the Dhoop &amp; Chandan fragrance. Made for gifting, rituals and everyday moments.</t>
-        </is>
-      </c>
-      <c r="P7" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q7" t="b">
-        <v>0</v>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Dhoop &amp; Chandan in our signature ritual.</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>A Mysaa Rituals signature ritual in the Dhoop &amp; Chandan fragrance. Made for gifting, rituals and everyday moments.</t>
+        </is>
       </c>
       <c r="R7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S7" t="b">
-        <v>1</v>
-      </c>
-      <c r="T7" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="T7" t="b">
+        <v>1</v>
+      </c>
+      <c r="U7" t="b">
+        <v>1</v>
+      </c>
+      <c r="V7" t="inlineStr">
         <is>
           <t>assets/catalogue/dhoop-chandan/hero-jar-candle/01-cover.jpg</t>
         </is>
       </c>
-      <c r="U7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>assets/catalogue/dhoop-chandan/hero-jar-candle/02-detail.jpg</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr">
+      <c r="X7" t="inlineStr">
         <is>
           <t>assets/catalogue/dhoop-chandan/hero-jar-candle/03-lifestyle.jpg</t>
         </is>
@@ -1270,7 +1302,7 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>645.88</v>
+        <v>650</v>
       </c>
       <c r="F8" t="n">
         <v>549</v>
@@ -1282,55 +1314,57 @@
         <v>1</v>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>120 ml</t>
-        </is>
-      </c>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr">
         <is>
+          <t>120 ml</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr">
+        <is>
           <t>Natural soy wax, cotton wick, phthalate-free fragrance oils</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="O8" t="inlineStr">
         <is>
           <t>Mysaa Rituals signature packaging</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
+      <c r="P8" t="inlineStr">
         <is>
           <t>Dhoop &amp; Chandan in our everyday ritual.</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr">
+      <c r="Q8" t="inlineStr">
         <is>
           <t>A Mysaa Rituals everyday ritual in the Dhoop &amp; Chandan fragrance. Made for gifting, rituals and everyday moments.</t>
         </is>
       </c>
-      <c r="P8" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q8" t="b">
-        <v>0</v>
-      </c>
       <c r="R8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S8" t="b">
-        <v>1</v>
-      </c>
-      <c r="T8" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="T8" t="b">
+        <v>1</v>
+      </c>
+      <c r="U8" t="b">
+        <v>1</v>
+      </c>
+      <c r="V8" t="inlineStr">
         <is>
           <t>assets/catalogue/dhoop-chandan/wide-jar-candle/01-cover.jpg</t>
         </is>
       </c>
-      <c r="U8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>assets/catalogue/dhoop-chandan/wide-jar-candle/02-detail.jpg</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr">
+      <c r="X8" t="inlineStr">
         <is>
           <t>assets/catalogue/dhoop-chandan/wide-jar-candle/03-lifestyle.jpg</t>
         </is>
@@ -1358,7 +1392,7 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>332.22</v>
+        <v>350</v>
       </c>
       <c r="F9" t="n">
         <v>299</v>
@@ -1370,55 +1404,57 @@
         <v>1</v>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>60 ml</t>
-        </is>
-      </c>
+      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr">
         <is>
+          <t>60 ml</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr">
+        <is>
           <t>Natural soy wax, cotton wick, phthalate-free fragrance oils</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="O9" t="inlineStr">
         <is>
           <t>Mysaa Rituals signature packaging</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
+      <c r="P9" t="inlineStr">
         <is>
           <t>Dhoop &amp; Chandan in our mini ritual.</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr">
+      <c r="Q9" t="inlineStr">
         <is>
           <t>A Mysaa Rituals mini ritual in the Dhoop &amp; Chandan fragrance. Made for gifting, rituals and everyday moments.</t>
         </is>
       </c>
-      <c r="P9" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q9" t="b">
-        <v>0</v>
-      </c>
       <c r="R9" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S9" t="b">
-        <v>1</v>
-      </c>
-      <c r="T9" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="T9" t="b">
+        <v>1</v>
+      </c>
+      <c r="U9" t="b">
+        <v>1</v>
+      </c>
+      <c r="V9" t="inlineStr">
         <is>
           <t>assets/catalogue/dhoop-chandan/shot-glass-candle/01-cover.jpg</t>
         </is>
       </c>
-      <c r="U9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>assets/catalogue/dhoop-chandan/shot-glass-candle/02-detail.jpg</t>
         </is>
       </c>
-      <c r="V9" t="inlineStr">
+      <c r="X9" t="inlineStr">
         <is>
           <t>assets/catalogue/dhoop-chandan/shot-glass-candle/03-lifestyle.jpg</t>
         </is>
@@ -1457,56 +1493,62 @@
       <c r="H10" t="n">
         <v>1</v>
       </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>Combo</t>
-        </is>
-      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>out-of-stock</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr">
         <is>
+          <t>Combo</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr">
+        <is>
           <t>Natural soy wax, cotton wick, phthalate-free fragrance oils</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
+      <c r="O10" t="inlineStr">
         <is>
           <t>Mysaa Rituals signature packaging</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
+      <c r="P10" t="inlineStr">
         <is>
           <t>Dhoop &amp; Chandan in our wax sachet combo.</t>
         </is>
       </c>
-      <c r="O10" t="inlineStr">
+      <c r="Q10" t="inlineStr">
         <is>
           <t>A Mysaa Rituals wax sachet combo in the Dhoop &amp; Chandan fragrance. Made for gifting, rituals and everyday moments.</t>
         </is>
       </c>
-      <c r="P10" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q10" t="b">
-        <v>0</v>
-      </c>
       <c r="R10" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S10" t="b">
-        <v>1</v>
-      </c>
-      <c r="T10" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="T10" t="b">
+        <v>1</v>
+      </c>
+      <c r="U10" t="b">
+        <v>1</v>
+      </c>
+      <c r="V10" t="inlineStr">
         <is>
           <t>assets/catalogue/dhoop-chandan/wax-melts/01-cover.jpg</t>
         </is>
       </c>
-      <c r="U10" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>assets/catalogue/dhoop-chandan/wax-melts/02-detail.jpg</t>
         </is>
       </c>
-      <c r="V10" t="inlineStr">
+      <c r="X10" t="inlineStr">
         <is>
           <t>assets/catalogue/dhoop-chandan/wax-melts/03-lifestyle.jpg</t>
         </is>
@@ -1548,53 +1590,59 @@
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Curated set</t>
+          <t>festivals-celebrations</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr">
         <is>
+          <t>Curated set</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr">
+        <is>
           <t>Curated Mysaa Rituals gifting selection</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr">
+      <c r="O11" t="inlineStr">
         <is>
           <t>Mysaa Rituals signature packaging</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr">
+      <c r="P11" t="inlineStr">
         <is>
           <t>Dhoop &amp; Chandan in our gift hamper.</t>
         </is>
       </c>
-      <c r="O11" t="inlineStr">
+      <c r="Q11" t="inlineStr">
         <is>
           <t>A Mysaa Rituals gift hamper in the Dhoop &amp; Chandan fragrance. Made for gifting, rituals and everyday moments.</t>
         </is>
       </c>
-      <c r="P11" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q11" t="b">
-        <v>0</v>
-      </c>
       <c r="R11" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S11" t="b">
-        <v>1</v>
-      </c>
-      <c r="T11" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="T11" t="b">
+        <v>1</v>
+      </c>
+      <c r="U11" t="b">
+        <v>1</v>
+      </c>
+      <c r="V11" t="inlineStr">
         <is>
           <t>assets/catalogue/dhoop-chandan/gift-hampers/01-cover.jpg</t>
         </is>
       </c>
-      <c r="U11" t="inlineStr">
+      <c r="W11" t="inlineStr">
         <is>
           <t>assets/catalogue/dhoop-chandan/gift-hampers/02-detail.jpg</t>
         </is>
       </c>
-      <c r="V11" t="inlineStr">
+      <c r="X11" t="inlineStr">
         <is>
           <t>assets/catalogue/dhoop-chandan/gift-hampers/03-lifestyle.jpg</t>
         </is>
@@ -1608,7 +1656,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Gajre Ka Shringar Signature</t>
+          <t>Gajre Ka Shringar Signature Ritual</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1622,7 +1670,7 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>998.75</v>
+        <v>1000</v>
       </c>
       <c r="F12" t="n">
         <v>799</v>
@@ -1634,55 +1682,57 @@
         <v>1</v>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>220 ml</t>
-        </is>
-      </c>
+      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr">
         <is>
+          <t>220 ml</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr">
+        <is>
           <t>Natural soy wax, cotton wick, phthalate-free fragrance oils</t>
         </is>
       </c>
-      <c r="M12" t="inlineStr">
+      <c r="O12" t="inlineStr">
         <is>
           <t>Mysaa Rituals signature packaging</t>
         </is>
       </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>Gajre Ka Shringar in our signature.</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>A Mysaa Rituals signature in the Gajre Ka Shringar fragrance. Made for gifting, rituals and everyday moments.</t>
-        </is>
-      </c>
-      <c r="P12" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q12" t="b">
-        <v>0</v>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Gajre Ka Shringar in our signature ritual.</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>A Mysaa Rituals signature ritual in the Gajre Ka Shringar fragrance. Made for gifting, rituals and everyday moments.</t>
+        </is>
       </c>
       <c r="R12" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S12" t="b">
-        <v>1</v>
-      </c>
-      <c r="T12" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="T12" t="b">
+        <v>1</v>
+      </c>
+      <c r="U12" t="b">
+        <v>1</v>
+      </c>
+      <c r="V12" t="inlineStr">
         <is>
           <t>assets/catalogue/gajre-ka-shringar/hero-jar-candle/01-cover.jpg</t>
         </is>
       </c>
-      <c r="U12" t="inlineStr">
+      <c r="W12" t="inlineStr">
         <is>
           <t>assets/catalogue/gajre-ka-shringar/hero-jar-candle/02-detail.jpg</t>
         </is>
       </c>
-      <c r="V12" t="inlineStr">
+      <c r="X12" t="inlineStr">
         <is>
           <t>assets/catalogue/gajre-ka-shringar/hero-jar-candle/03-lifestyle.jpg</t>
         </is>
@@ -1710,7 +1760,7 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>645.88</v>
+        <v>650</v>
       </c>
       <c r="F13" t="n">
         <v>549</v>
@@ -1722,55 +1772,57 @@
         <v>1</v>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>120 ml</t>
-        </is>
-      </c>
+      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr">
         <is>
+          <t>120 ml</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr">
+        <is>
           <t>Natural soy wax, cotton wick, phthalate-free fragrance oils</t>
         </is>
       </c>
-      <c r="M13" t="inlineStr">
+      <c r="O13" t="inlineStr">
         <is>
           <t>Mysaa Rituals signature packaging</t>
         </is>
       </c>
-      <c r="N13" t="inlineStr">
+      <c r="P13" t="inlineStr">
         <is>
           <t>Gajre Ka Shringar in our everyday ritual.</t>
         </is>
       </c>
-      <c r="O13" t="inlineStr">
+      <c r="Q13" t="inlineStr">
         <is>
           <t>A Mysaa Rituals everyday ritual in the Gajre Ka Shringar fragrance. Made for gifting, rituals and everyday moments.</t>
         </is>
       </c>
-      <c r="P13" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q13" t="b">
-        <v>0</v>
-      </c>
       <c r="R13" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S13" t="b">
-        <v>1</v>
-      </c>
-      <c r="T13" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="T13" t="b">
+        <v>1</v>
+      </c>
+      <c r="U13" t="b">
+        <v>1</v>
+      </c>
+      <c r="V13" t="inlineStr">
         <is>
           <t>assets/catalogue/gajre-ka-shringar/wide-jar-candle/01-cover.jpg</t>
         </is>
       </c>
-      <c r="U13" t="inlineStr">
+      <c r="W13" t="inlineStr">
         <is>
           <t>assets/catalogue/gajre-ka-shringar/wide-jar-candle/02-detail.jpg</t>
         </is>
       </c>
-      <c r="V13" t="inlineStr">
+      <c r="X13" t="inlineStr">
         <is>
           <t>assets/catalogue/gajre-ka-shringar/wide-jar-candle/03-lifestyle.jpg</t>
         </is>
@@ -1798,7 +1850,7 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>332.22</v>
+        <v>350</v>
       </c>
       <c r="F14" t="n">
         <v>299</v>
@@ -1810,55 +1862,57 @@
         <v>1</v>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>60 ml</t>
-        </is>
-      </c>
+      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr">
         <is>
+          <t>60 ml</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr">
+        <is>
           <t>Natural soy wax, cotton wick, phthalate-free fragrance oils</t>
         </is>
       </c>
-      <c r="M14" t="inlineStr">
+      <c r="O14" t="inlineStr">
         <is>
           <t>Mysaa Rituals signature packaging</t>
         </is>
       </c>
-      <c r="N14" t="inlineStr">
+      <c r="P14" t="inlineStr">
         <is>
           <t>Gajre Ka Shringar in our mini ritual.</t>
         </is>
       </c>
-      <c r="O14" t="inlineStr">
+      <c r="Q14" t="inlineStr">
         <is>
           <t>A Mysaa Rituals mini ritual in the Gajre Ka Shringar fragrance. Made for gifting, rituals and everyday moments.</t>
         </is>
       </c>
-      <c r="P14" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q14" t="b">
-        <v>0</v>
-      </c>
       <c r="R14" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S14" t="b">
-        <v>1</v>
-      </c>
-      <c r="T14" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="T14" t="b">
+        <v>1</v>
+      </c>
+      <c r="U14" t="b">
+        <v>1</v>
+      </c>
+      <c r="V14" t="inlineStr">
         <is>
           <t>assets/catalogue/gajre-ka-shringar/shot-glass-candle/01-cover.jpg</t>
         </is>
       </c>
-      <c r="U14" t="inlineStr">
+      <c r="W14" t="inlineStr">
         <is>
           <t>assets/catalogue/gajre-ka-shringar/shot-glass-candle/02-detail.jpg</t>
         </is>
       </c>
-      <c r="V14" t="inlineStr">
+      <c r="X14" t="inlineStr">
         <is>
           <t>assets/catalogue/gajre-ka-shringar/shot-glass-candle/03-lifestyle.jpg</t>
         </is>
@@ -1897,56 +1951,62 @@
       <c r="H15" t="n">
         <v>1</v>
       </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>Combo</t>
-        </is>
-      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>out-of-stock</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr">
         <is>
+          <t>Combo</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr">
+        <is>
           <t>Natural soy wax, cotton wick, phthalate-free fragrance oils</t>
         </is>
       </c>
-      <c r="M15" t="inlineStr">
+      <c r="O15" t="inlineStr">
         <is>
           <t>Mysaa Rituals signature packaging</t>
         </is>
       </c>
-      <c r="N15" t="inlineStr">
+      <c r="P15" t="inlineStr">
         <is>
           <t>Gajre Ka Shringar in our wax sachet combo.</t>
         </is>
       </c>
-      <c r="O15" t="inlineStr">
+      <c r="Q15" t="inlineStr">
         <is>
           <t>A Mysaa Rituals wax sachet combo in the Gajre Ka Shringar fragrance. Made for gifting, rituals and everyday moments.</t>
         </is>
       </c>
-      <c r="P15" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q15" t="b">
-        <v>0</v>
-      </c>
       <c r="R15" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S15" t="b">
-        <v>1</v>
-      </c>
-      <c r="T15" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="T15" t="b">
+        <v>1</v>
+      </c>
+      <c r="U15" t="b">
+        <v>1</v>
+      </c>
+      <c r="V15" t="inlineStr">
         <is>
           <t>assets/catalogue/gajre-ka-shringar/wax-melts/01-cover.jpg</t>
         </is>
       </c>
-      <c r="U15" t="inlineStr">
+      <c r="W15" t="inlineStr">
         <is>
           <t>assets/catalogue/gajre-ka-shringar/wax-melts/02-detail.jpg</t>
         </is>
       </c>
-      <c r="V15" t="inlineStr">
+      <c r="X15" t="inlineStr">
         <is>
           <t>assets/catalogue/gajre-ka-shringar/wax-melts/03-lifestyle.jpg</t>
         </is>
@@ -1988,53 +2048,59 @@
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr">
         <is>
-          <t>Curated set</t>
+          <t>weddings-return-gifts</t>
         </is>
       </c>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr">
         <is>
+          <t>Curated set</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr">
+        <is>
           <t>Curated Mysaa Rituals gifting selection</t>
         </is>
       </c>
-      <c r="M16" t="inlineStr">
+      <c r="O16" t="inlineStr">
         <is>
           <t>Mysaa Rituals signature packaging</t>
         </is>
       </c>
-      <c r="N16" t="inlineStr">
+      <c r="P16" t="inlineStr">
         <is>
           <t>Gajre Ka Shringar in our gift hamper.</t>
         </is>
       </c>
-      <c r="O16" t="inlineStr">
+      <c r="Q16" t="inlineStr">
         <is>
           <t>A Mysaa Rituals gift hamper in the Gajre Ka Shringar fragrance. Made for gifting, rituals and everyday moments.</t>
         </is>
       </c>
-      <c r="P16" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q16" t="b">
-        <v>0</v>
-      </c>
       <c r="R16" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S16" t="b">
-        <v>1</v>
-      </c>
-      <c r="T16" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="T16" t="b">
+        <v>1</v>
+      </c>
+      <c r="U16" t="b">
+        <v>1</v>
+      </c>
+      <c r="V16" t="inlineStr">
         <is>
           <t>assets/catalogue/gajre-ka-shringar/gift-hampers/01-cover.jpg</t>
         </is>
       </c>
-      <c r="U16" t="inlineStr">
+      <c r="W16" t="inlineStr">
         <is>
           <t>assets/catalogue/gajre-ka-shringar/gift-hampers/02-detail.jpg</t>
         </is>
       </c>
-      <c r="V16" t="inlineStr">
+      <c r="X16" t="inlineStr">
         <is>
           <t>assets/catalogue/gajre-ka-shringar/gift-hampers/03-lifestyle.jpg</t>
         </is>
@@ -2048,7 +2114,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Madhuban Signature</t>
+          <t>Madhuban Signature Ritual</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -2062,7 +2128,7 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>998.75</v>
+        <v>1000</v>
       </c>
       <c r="F17" t="n">
         <v>799</v>
@@ -2074,55 +2140,57 @@
         <v>1</v>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>220 ml</t>
-        </is>
-      </c>
+      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr">
         <is>
+          <t>220 ml</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr">
+        <is>
           <t>Natural soy wax, cotton wick, phthalate-free fragrance oils</t>
         </is>
       </c>
-      <c r="M17" t="inlineStr">
+      <c r="O17" t="inlineStr">
         <is>
           <t>Mysaa Rituals signature packaging</t>
         </is>
       </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>Madhuban in our signature.</t>
-        </is>
-      </c>
-      <c r="O17" t="inlineStr">
-        <is>
-          <t>A Mysaa Rituals signature in the Madhuban fragrance. Made for gifting, rituals and everyday moments.</t>
-        </is>
-      </c>
-      <c r="P17" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q17" t="b">
-        <v>0</v>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Madhuban in our signature ritual.</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>A Mysaa Rituals signature ritual in the Madhuban fragrance. Made for gifting, rituals and everyday moments.</t>
+        </is>
       </c>
       <c r="R17" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S17" t="b">
-        <v>1</v>
-      </c>
-      <c r="T17" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="T17" t="b">
+        <v>1</v>
+      </c>
+      <c r="U17" t="b">
+        <v>1</v>
+      </c>
+      <c r="V17" t="inlineStr">
         <is>
           <t>assets/catalogue/madhuban/hero-jar-candle/01-cover.jpg</t>
         </is>
       </c>
-      <c r="U17" t="inlineStr">
+      <c r="W17" t="inlineStr">
         <is>
           <t>assets/catalogue/madhuban/hero-jar-candle/02-detail.jpg</t>
         </is>
       </c>
-      <c r="V17" t="inlineStr">
+      <c r="X17" t="inlineStr">
         <is>
           <t>assets/catalogue/madhuban/hero-jar-candle/03-lifestyle.jpg</t>
         </is>
@@ -2150,7 +2218,7 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>645.88</v>
+        <v>650</v>
       </c>
       <c r="F18" t="n">
         <v>549</v>
@@ -2162,55 +2230,57 @@
         <v>1</v>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>120 ml</t>
-        </is>
-      </c>
+      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr">
         <is>
+          <t>120 ml</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr">
+        <is>
           <t>Natural soy wax, cotton wick, phthalate-free fragrance oils</t>
         </is>
       </c>
-      <c r="M18" t="inlineStr">
+      <c r="O18" t="inlineStr">
         <is>
           <t>Mysaa Rituals signature packaging</t>
         </is>
       </c>
-      <c r="N18" t="inlineStr">
+      <c r="P18" t="inlineStr">
         <is>
           <t>Madhuban in our everyday ritual.</t>
         </is>
       </c>
-      <c r="O18" t="inlineStr">
+      <c r="Q18" t="inlineStr">
         <is>
           <t>A Mysaa Rituals everyday ritual in the Madhuban fragrance. Made for gifting, rituals and everyday moments.</t>
         </is>
       </c>
-      <c r="P18" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q18" t="b">
-        <v>0</v>
-      </c>
       <c r="R18" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S18" t="b">
-        <v>1</v>
-      </c>
-      <c r="T18" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="T18" t="b">
+        <v>1</v>
+      </c>
+      <c r="U18" t="b">
+        <v>1</v>
+      </c>
+      <c r="V18" t="inlineStr">
         <is>
           <t>assets/catalogue/madhuban/wide-jar-candle/01-cover.jpg</t>
         </is>
       </c>
-      <c r="U18" t="inlineStr">
+      <c r="W18" t="inlineStr">
         <is>
           <t>assets/catalogue/madhuban/wide-jar-candle/02-detail.jpg</t>
         </is>
       </c>
-      <c r="V18" t="inlineStr">
+      <c r="X18" t="inlineStr">
         <is>
           <t>assets/catalogue/madhuban/wide-jar-candle/03-lifestyle.jpg</t>
         </is>
@@ -2238,7 +2308,7 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>332.22</v>
+        <v>350</v>
       </c>
       <c r="F19" t="n">
         <v>299</v>
@@ -2250,55 +2320,57 @@
         <v>1</v>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>60 ml</t>
-        </is>
-      </c>
+      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr">
         <is>
+          <t>60 ml</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr">
+        <is>
           <t>Natural soy wax, cotton wick, phthalate-free fragrance oils</t>
         </is>
       </c>
-      <c r="M19" t="inlineStr">
+      <c r="O19" t="inlineStr">
         <is>
           <t>Mysaa Rituals signature packaging</t>
         </is>
       </c>
-      <c r="N19" t="inlineStr">
+      <c r="P19" t="inlineStr">
         <is>
           <t>Madhuban in our mini ritual.</t>
         </is>
       </c>
-      <c r="O19" t="inlineStr">
+      <c r="Q19" t="inlineStr">
         <is>
           <t>A Mysaa Rituals mini ritual in the Madhuban fragrance. Made for gifting, rituals and everyday moments.</t>
         </is>
       </c>
-      <c r="P19" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q19" t="b">
-        <v>0</v>
-      </c>
       <c r="R19" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S19" t="b">
-        <v>1</v>
-      </c>
-      <c r="T19" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="T19" t="b">
+        <v>1</v>
+      </c>
+      <c r="U19" t="b">
+        <v>1</v>
+      </c>
+      <c r="V19" t="inlineStr">
         <is>
           <t>assets/catalogue/madhuban/shot-glass-candle/01-cover.jpg</t>
         </is>
       </c>
-      <c r="U19" t="inlineStr">
+      <c r="W19" t="inlineStr">
         <is>
           <t>assets/catalogue/madhuban/shot-glass-candle/02-detail.jpg</t>
         </is>
       </c>
-      <c r="V19" t="inlineStr">
+      <c r="X19" t="inlineStr">
         <is>
           <t>assets/catalogue/madhuban/shot-glass-candle/03-lifestyle.jpg</t>
         </is>
@@ -2337,56 +2409,62 @@
       <c r="H20" t="n">
         <v>1</v>
       </c>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>Combo</t>
-        </is>
-      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>out-of-stock</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr">
         <is>
+          <t>Combo</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr">
+        <is>
           <t>Natural soy wax, cotton wick, phthalate-free fragrance oils</t>
         </is>
       </c>
-      <c r="M20" t="inlineStr">
+      <c r="O20" t="inlineStr">
         <is>
           <t>Mysaa Rituals signature packaging</t>
         </is>
       </c>
-      <c r="N20" t="inlineStr">
+      <c r="P20" t="inlineStr">
         <is>
           <t>Madhuban in our wax sachet combo.</t>
         </is>
       </c>
-      <c r="O20" t="inlineStr">
+      <c r="Q20" t="inlineStr">
         <is>
           <t>A Mysaa Rituals wax sachet combo in the Madhuban fragrance. Made for gifting, rituals and everyday moments.</t>
         </is>
       </c>
-      <c r="P20" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q20" t="b">
-        <v>0</v>
-      </c>
       <c r="R20" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S20" t="b">
-        <v>1</v>
-      </c>
-      <c r="T20" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="T20" t="b">
+        <v>1</v>
+      </c>
+      <c r="U20" t="b">
+        <v>1</v>
+      </c>
+      <c r="V20" t="inlineStr">
         <is>
           <t>assets/catalogue/madhuban/wax-melts/01-cover.jpg</t>
         </is>
       </c>
-      <c r="U20" t="inlineStr">
+      <c r="W20" t="inlineStr">
         <is>
           <t>assets/catalogue/madhuban/wax-melts/02-detail.jpg</t>
         </is>
       </c>
-      <c r="V20" t="inlineStr">
+      <c r="X20" t="inlineStr">
         <is>
           <t>assets/catalogue/madhuban/wax-melts/03-lifestyle.jpg</t>
         </is>
@@ -2428,53 +2506,59 @@
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Curated set</t>
+          <t>festivals-celebrations</t>
         </is>
       </c>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr">
         <is>
+          <t>Curated set</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr">
+        <is>
           <t>Curated Mysaa Rituals gifting selection</t>
         </is>
       </c>
-      <c r="M21" t="inlineStr">
+      <c r="O21" t="inlineStr">
         <is>
           <t>Mysaa Rituals signature packaging</t>
         </is>
       </c>
-      <c r="N21" t="inlineStr">
+      <c r="P21" t="inlineStr">
         <is>
           <t>Madhuban in our gift hamper.</t>
         </is>
       </c>
-      <c r="O21" t="inlineStr">
+      <c r="Q21" t="inlineStr">
         <is>
           <t>A Mysaa Rituals gift hamper in the Madhuban fragrance. Made for gifting, rituals and everyday moments.</t>
         </is>
       </c>
-      <c r="P21" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q21" t="b">
-        <v>0</v>
-      </c>
       <c r="R21" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S21" t="b">
-        <v>1</v>
-      </c>
-      <c r="T21" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="T21" t="b">
+        <v>1</v>
+      </c>
+      <c r="U21" t="b">
+        <v>1</v>
+      </c>
+      <c r="V21" t="inlineStr">
         <is>
           <t>assets/catalogue/madhuban/gift-hampers/01-cover.jpg</t>
         </is>
       </c>
-      <c r="U21" t="inlineStr">
+      <c r="W21" t="inlineStr">
         <is>
           <t>assets/catalogue/madhuban/gift-hampers/02-detail.jpg</t>
         </is>
       </c>
-      <c r="V21" t="inlineStr">
+      <c r="X21" t="inlineStr">
         <is>
           <t>assets/catalogue/madhuban/gift-hampers/03-lifestyle.jpg</t>
         </is>
@@ -2488,7 +2572,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Raat Ki Rani Signature</t>
+          <t>Raat Ki Rani Signature Ritual</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -2502,7 +2586,7 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>998.75</v>
+        <v>1000</v>
       </c>
       <c r="F22" t="n">
         <v>799</v>
@@ -2514,55 +2598,57 @@
         <v>1</v>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>220 ml</t>
-        </is>
-      </c>
+      <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr">
         <is>
+          <t>220 ml</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="inlineStr">
+        <is>
           <t>Natural soy wax, cotton wick, phthalate-free fragrance oils</t>
         </is>
       </c>
-      <c r="M22" t="inlineStr">
+      <c r="O22" t="inlineStr">
         <is>
           <t>Mysaa Rituals signature packaging</t>
         </is>
       </c>
-      <c r="N22" t="inlineStr">
-        <is>
-          <t>Raat Ki Rani in our signature.</t>
-        </is>
-      </c>
-      <c r="O22" t="inlineStr">
-        <is>
-          <t>A Mysaa Rituals signature in the Raat Ki Rani fragrance. Made for gifting, rituals and everyday moments.</t>
-        </is>
-      </c>
-      <c r="P22" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q22" t="b">
-        <v>0</v>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Raat Ki Rani in our signature ritual.</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>A Mysaa Rituals signature ritual in the Raat Ki Rani fragrance. Made for gifting, rituals and everyday moments.</t>
+        </is>
       </c>
       <c r="R22" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S22" t="b">
-        <v>1</v>
-      </c>
-      <c r="T22" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="T22" t="b">
+        <v>1</v>
+      </c>
+      <c r="U22" t="b">
+        <v>1</v>
+      </c>
+      <c r="V22" t="inlineStr">
         <is>
           <t>assets/catalogue/raat-ki-rani/hero-jar-candle/01-cover.jpg</t>
         </is>
       </c>
-      <c r="U22" t="inlineStr">
+      <c r="W22" t="inlineStr">
         <is>
           <t>assets/catalogue/raat-ki-rani/hero-jar-candle/02-detail.jpg</t>
         </is>
       </c>
-      <c r="V22" t="inlineStr">
+      <c r="X22" t="inlineStr">
         <is>
           <t>assets/catalogue/raat-ki-rani/hero-jar-candle/03-lifestyle.jpg</t>
         </is>
@@ -2590,7 +2676,7 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>645.88</v>
+        <v>650</v>
       </c>
       <c r="F23" t="n">
         <v>549</v>
@@ -2602,55 +2688,57 @@
         <v>1</v>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>120 ml</t>
-        </is>
-      </c>
+      <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr">
         <is>
+          <t>120 ml</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr">
+        <is>
           <t>Natural soy wax, cotton wick, phthalate-free fragrance oils</t>
         </is>
       </c>
-      <c r="M23" t="inlineStr">
+      <c r="O23" t="inlineStr">
         <is>
           <t>Mysaa Rituals signature packaging</t>
         </is>
       </c>
-      <c r="N23" t="inlineStr">
+      <c r="P23" t="inlineStr">
         <is>
           <t>Raat Ki Rani in our everyday ritual.</t>
         </is>
       </c>
-      <c r="O23" t="inlineStr">
+      <c r="Q23" t="inlineStr">
         <is>
           <t>A Mysaa Rituals everyday ritual in the Raat Ki Rani fragrance. Made for gifting, rituals and everyday moments.</t>
         </is>
       </c>
-      <c r="P23" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q23" t="b">
-        <v>0</v>
-      </c>
       <c r="R23" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S23" t="b">
-        <v>1</v>
-      </c>
-      <c r="T23" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="T23" t="b">
+        <v>1</v>
+      </c>
+      <c r="U23" t="b">
+        <v>1</v>
+      </c>
+      <c r="V23" t="inlineStr">
         <is>
           <t>assets/catalogue/raat-ki-rani/wide-jar-candle/01-cover.jpg</t>
         </is>
       </c>
-      <c r="U23" t="inlineStr">
+      <c r="W23" t="inlineStr">
         <is>
           <t>assets/catalogue/raat-ki-rani/wide-jar-candle/02-detail.jpg</t>
         </is>
       </c>
-      <c r="V23" t="inlineStr">
+      <c r="X23" t="inlineStr">
         <is>
           <t>assets/catalogue/raat-ki-rani/wide-jar-candle/03-lifestyle.jpg</t>
         </is>
@@ -2678,7 +2766,7 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>332.22</v>
+        <v>350</v>
       </c>
       <c r="F24" t="n">
         <v>299</v>
@@ -2690,55 +2778,57 @@
         <v>1</v>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>60 ml</t>
-        </is>
-      </c>
+      <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr">
         <is>
+          <t>60 ml</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" t="inlineStr">
+        <is>
           <t>Natural soy wax, cotton wick, phthalate-free fragrance oils</t>
         </is>
       </c>
-      <c r="M24" t="inlineStr">
+      <c r="O24" t="inlineStr">
         <is>
           <t>Mysaa Rituals signature packaging</t>
         </is>
       </c>
-      <c r="N24" t="inlineStr">
+      <c r="P24" t="inlineStr">
         <is>
           <t>Raat Ki Rani in our mini ritual.</t>
         </is>
       </c>
-      <c r="O24" t="inlineStr">
+      <c r="Q24" t="inlineStr">
         <is>
           <t>A Mysaa Rituals mini ritual in the Raat Ki Rani fragrance. Made for gifting, rituals and everyday moments.</t>
         </is>
       </c>
-      <c r="P24" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q24" t="b">
-        <v>0</v>
-      </c>
       <c r="R24" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S24" t="b">
-        <v>1</v>
-      </c>
-      <c r="T24" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="T24" t="b">
+        <v>1</v>
+      </c>
+      <c r="U24" t="b">
+        <v>1</v>
+      </c>
+      <c r="V24" t="inlineStr">
         <is>
           <t>assets/catalogue/raat-ki-rani/shot-glass-candle/01-cover.jpg</t>
         </is>
       </c>
-      <c r="U24" t="inlineStr">
+      <c r="W24" t="inlineStr">
         <is>
           <t>assets/catalogue/raat-ki-rani/shot-glass-candle/02-detail.jpg</t>
         </is>
       </c>
-      <c r="V24" t="inlineStr">
+      <c r="X24" t="inlineStr">
         <is>
           <t>assets/catalogue/raat-ki-rani/shot-glass-candle/03-lifestyle.jpg</t>
         </is>
@@ -2777,56 +2867,62 @@
       <c r="H25" t="n">
         <v>1</v>
       </c>
-      <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>Combo</t>
-        </is>
-      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>out-of-stock</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr">
         <is>
+          <t>Combo</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr"/>
+      <c r="N25" t="inlineStr">
+        <is>
           <t>Natural soy wax, cotton wick, phthalate-free fragrance oils</t>
         </is>
       </c>
-      <c r="M25" t="inlineStr">
+      <c r="O25" t="inlineStr">
         <is>
           <t>Mysaa Rituals signature packaging</t>
         </is>
       </c>
-      <c r="N25" t="inlineStr">
+      <c r="P25" t="inlineStr">
         <is>
           <t>Raat Ki Rani in our wax sachet combo.</t>
         </is>
       </c>
-      <c r="O25" t="inlineStr">
+      <c r="Q25" t="inlineStr">
         <is>
           <t>A Mysaa Rituals wax sachet combo in the Raat Ki Rani fragrance. Made for gifting, rituals and everyday moments.</t>
         </is>
       </c>
-      <c r="P25" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q25" t="b">
-        <v>0</v>
-      </c>
       <c r="R25" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S25" t="b">
-        <v>1</v>
-      </c>
-      <c r="T25" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="T25" t="b">
+        <v>1</v>
+      </c>
+      <c r="U25" t="b">
+        <v>1</v>
+      </c>
+      <c r="V25" t="inlineStr">
         <is>
           <t>assets/catalogue/raat-ki-rani/wax-melts/01-cover.jpg</t>
         </is>
       </c>
-      <c r="U25" t="inlineStr">
+      <c r="W25" t="inlineStr">
         <is>
           <t>assets/catalogue/raat-ki-rani/wax-melts/02-detail.jpg</t>
         </is>
       </c>
-      <c r="V25" t="inlineStr">
+      <c r="X25" t="inlineStr">
         <is>
           <t>assets/catalogue/raat-ki-rani/wax-melts/03-lifestyle.jpg</t>
         </is>
@@ -2868,53 +2964,59 @@
       <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr">
         <is>
-          <t>Curated set</t>
+          <t>birthdays-just-because</t>
         </is>
       </c>
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr">
         <is>
+          <t>Curated set</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr"/>
+      <c r="N26" t="inlineStr">
+        <is>
           <t>Curated Mysaa Rituals gifting selection</t>
         </is>
       </c>
-      <c r="M26" t="inlineStr">
+      <c r="O26" t="inlineStr">
         <is>
           <t>Mysaa Rituals signature packaging</t>
         </is>
       </c>
-      <c r="N26" t="inlineStr">
+      <c r="P26" t="inlineStr">
         <is>
           <t>Raat Ki Rani in our gift hamper.</t>
         </is>
       </c>
-      <c r="O26" t="inlineStr">
+      <c r="Q26" t="inlineStr">
         <is>
           <t>A Mysaa Rituals gift hamper in the Raat Ki Rani fragrance. Made for gifting, rituals and everyday moments.</t>
         </is>
       </c>
-      <c r="P26" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q26" t="b">
-        <v>0</v>
-      </c>
       <c r="R26" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S26" t="b">
-        <v>1</v>
-      </c>
-      <c r="T26" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="T26" t="b">
+        <v>1</v>
+      </c>
+      <c r="U26" t="b">
+        <v>1</v>
+      </c>
+      <c r="V26" t="inlineStr">
         <is>
           <t>assets/catalogue/raat-ki-rani/gift-hampers/01-cover.jpg</t>
         </is>
       </c>
-      <c r="U26" t="inlineStr">
+      <c r="W26" t="inlineStr">
         <is>
           <t>assets/catalogue/raat-ki-rani/gift-hampers/02-detail.jpg</t>
         </is>
       </c>
-      <c r="V26" t="inlineStr">
+      <c r="X26" t="inlineStr">
         <is>
           <t>assets/catalogue/raat-ki-rani/gift-hampers/03-lifestyle.jpg</t>
         </is>
@@ -2928,7 +3030,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Saanjh Signature</t>
+          <t>Saanjh Signature Ritual</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2942,7 +3044,7 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>998.75</v>
+        <v>1000</v>
       </c>
       <c r="F27" t="n">
         <v>799</v>
@@ -2954,55 +3056,57 @@
         <v>1</v>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>220 ml</t>
-        </is>
-      </c>
+      <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr">
         <is>
+          <t>220 ml</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr"/>
+      <c r="N27" t="inlineStr">
+        <is>
           <t>Natural soy wax, cotton wick, phthalate-free fragrance oils</t>
         </is>
       </c>
-      <c r="M27" t="inlineStr">
+      <c r="O27" t="inlineStr">
         <is>
           <t>Mysaa Rituals signature packaging</t>
         </is>
       </c>
-      <c r="N27" t="inlineStr">
-        <is>
-          <t>Saanjh in our signature.</t>
-        </is>
-      </c>
-      <c r="O27" t="inlineStr">
-        <is>
-          <t>A Mysaa Rituals signature in the Saanjh fragrance — creamy vanilla softened by deep sandalwood, made for gifting, rituals and everyday moments.</t>
-        </is>
-      </c>
-      <c r="P27" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q27" t="b">
-        <v>0</v>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Saanjh in our signature ritual.</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>A Mysaa Rituals signature ritual in the Saanjh fragrance — creamy vanilla softened by deep sandalwood, made for gifting, rituals and everyday moments.</t>
+        </is>
       </c>
       <c r="R27" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S27" t="b">
-        <v>1</v>
-      </c>
-      <c r="T27" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="T27" t="b">
+        <v>1</v>
+      </c>
+      <c r="U27" t="b">
+        <v>1</v>
+      </c>
+      <c r="V27" t="inlineStr">
         <is>
           <t>assets/catalogue/saanjh/hero-jar-candle/01-cover.jpg</t>
         </is>
       </c>
-      <c r="U27" t="inlineStr">
+      <c r="W27" t="inlineStr">
         <is>
           <t>assets/catalogue/saanjh/hero-jar-candle/02-detail.jpg</t>
         </is>
       </c>
-      <c r="V27" t="inlineStr">
+      <c r="X27" t="inlineStr">
         <is>
           <t>assets/catalogue/saanjh/hero-jar-candle/03-lifestyle.jpg</t>
         </is>
@@ -3030,7 +3134,7 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>645.88</v>
+        <v>650</v>
       </c>
       <c r="F28" t="n">
         <v>549</v>
@@ -3042,55 +3146,57 @@
         <v>1</v>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>120 ml</t>
-        </is>
-      </c>
+      <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr">
         <is>
+          <t>120 ml</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr"/>
+      <c r="N28" t="inlineStr">
+        <is>
           <t>Natural soy wax, cotton wick, phthalate-free fragrance oils</t>
         </is>
       </c>
-      <c r="M28" t="inlineStr">
+      <c r="O28" t="inlineStr">
         <is>
           <t>Mysaa Rituals signature packaging</t>
         </is>
       </c>
-      <c r="N28" t="inlineStr">
+      <c r="P28" t="inlineStr">
         <is>
           <t>Saanjh in our everyday ritual.</t>
         </is>
       </c>
-      <c r="O28" t="inlineStr">
+      <c r="Q28" t="inlineStr">
         <is>
           <t>A Mysaa Rituals everyday ritual in the Saanjh fragrance — creamy vanilla softened by deep sandalwood, made for gifting, rituals and everyday moments.</t>
         </is>
       </c>
-      <c r="P28" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q28" t="b">
-        <v>1</v>
-      </c>
       <c r="R28" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S28" t="b">
         <v>1</v>
       </c>
-      <c r="T28" t="inlineStr">
+      <c r="T28" t="b">
+        <v>1</v>
+      </c>
+      <c r="U28" t="b">
+        <v>1</v>
+      </c>
+      <c r="V28" t="inlineStr">
         <is>
           <t>assets/catalogue/saanjh/wide-jar-candle/01-cover.jpg</t>
         </is>
       </c>
-      <c r="U28" t="inlineStr">
+      <c r="W28" t="inlineStr">
         <is>
           <t>assets/catalogue/saanjh/wide-jar-candle/02-detail.jpg</t>
         </is>
       </c>
-      <c r="V28" t="inlineStr">
+      <c r="X28" t="inlineStr">
         <is>
           <t>assets/catalogue/saanjh/wide-jar-candle/03-lifestyle.jpg</t>
         </is>
@@ -3118,7 +3224,7 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>332.22</v>
+        <v>350</v>
       </c>
       <c r="F29" t="n">
         <v>299</v>
@@ -3130,55 +3236,57 @@
         <v>1</v>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>60 ml</t>
-        </is>
-      </c>
+      <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr">
         <is>
+          <t>60 ml</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr"/>
+      <c r="N29" t="inlineStr">
+        <is>
           <t>Natural soy wax, cotton wick, phthalate-free fragrance oils</t>
         </is>
       </c>
-      <c r="M29" t="inlineStr">
+      <c r="O29" t="inlineStr">
         <is>
           <t>Mysaa Rituals signature packaging</t>
         </is>
       </c>
-      <c r="N29" t="inlineStr">
+      <c r="P29" t="inlineStr">
         <is>
           <t>Saanjh in our mini ritual.</t>
         </is>
       </c>
-      <c r="O29" t="inlineStr">
+      <c r="Q29" t="inlineStr">
         <is>
           <t>A Mysaa Rituals mini ritual in the Saanjh fragrance — creamy vanilla softened by deep sandalwood, made for gifting, rituals and everyday moments.</t>
         </is>
       </c>
-      <c r="P29" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q29" t="b">
-        <v>0</v>
-      </c>
       <c r="R29" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S29" t="b">
-        <v>1</v>
-      </c>
-      <c r="T29" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="T29" t="b">
+        <v>1</v>
+      </c>
+      <c r="U29" t="b">
+        <v>1</v>
+      </c>
+      <c r="V29" t="inlineStr">
         <is>
           <t>assets/catalogue/saanjh/shot-glass-candle/01-cover.jpg</t>
         </is>
       </c>
-      <c r="U29" t="inlineStr">
+      <c r="W29" t="inlineStr">
         <is>
           <t>assets/catalogue/saanjh/shot-glass-candle/02-detail.jpg</t>
         </is>
       </c>
-      <c r="V29" t="inlineStr">
+      <c r="X29" t="inlineStr">
         <is>
           <t>assets/catalogue/saanjh/shot-glass-candle/03-lifestyle.jpg</t>
         </is>
@@ -3217,52 +3325,58 @@
       <c r="H30" t="n">
         <v>1</v>
       </c>
-      <c r="I30" t="inlineStr"/>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>out-of-stock</t>
+        </is>
+      </c>
       <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr">
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr"/>
+      <c r="N30" t="inlineStr">
         <is>
           <t>Natural soy wax, cotton wick, phthalate-free fragrance oils</t>
         </is>
       </c>
-      <c r="M30" t="inlineStr">
+      <c r="O30" t="inlineStr">
         <is>
           <t>Mysaa Rituals signature packaging</t>
         </is>
       </c>
-      <c r="N30" t="inlineStr">
+      <c r="P30" t="inlineStr">
         <is>
           <t>Saanjh in our wax sachet combo.</t>
         </is>
       </c>
-      <c r="O30" t="inlineStr">
+      <c r="Q30" t="inlineStr">
         <is>
           <t>A Mysaa Rituals wax sachet combo in the Saanjh fragrance — creamy vanilla softened by deep sandalwood, made for gifting, rituals and everyday moments.</t>
         </is>
       </c>
-      <c r="P30" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q30" t="b">
-        <v>0</v>
-      </c>
       <c r="R30" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S30" t="b">
-        <v>1</v>
-      </c>
-      <c r="T30" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="T30" t="b">
+        <v>1</v>
+      </c>
+      <c r="U30" t="b">
+        <v>1</v>
+      </c>
+      <c r="V30" t="inlineStr">
         <is>
           <t>assets/catalogue/saanjh/wax-melts/01-cover.jpg</t>
         </is>
       </c>
-      <c r="U30" t="inlineStr">
+      <c r="W30" t="inlineStr">
         <is>
           <t>assets/catalogue/saanjh/wax-melts/02-detail.jpg</t>
         </is>
       </c>
-      <c r="V30" t="inlineStr">
+      <c r="X30" t="inlineStr">
         <is>
           <t>assets/catalogue/saanjh/wax-melts/03-lifestyle.jpg</t>
         </is>
@@ -3302,51 +3416,57 @@
         <v>1</v>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>birthdays-just-because</t>
+        </is>
+      </c>
       <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr">
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr"/>
+      <c r="N31" t="inlineStr">
         <is>
           <t>Natural soy wax, cotton wick, phthalate-free fragrance oils</t>
         </is>
       </c>
-      <c r="M31" t="inlineStr">
+      <c r="O31" t="inlineStr">
         <is>
           <t>Mysaa Rituals signature packaging</t>
         </is>
       </c>
-      <c r="N31" t="inlineStr">
+      <c r="P31" t="inlineStr">
         <is>
           <t>Saanjh in our gift hamper.</t>
         </is>
       </c>
-      <c r="O31" t="inlineStr">
+      <c r="Q31" t="inlineStr">
         <is>
           <t>A Mysaa Rituals gift hamper in the Saanjh fragrance — creamy vanilla softened by deep sandalwood, made for gifting, rituals and everyday moments.</t>
         </is>
       </c>
-      <c r="P31" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q31" t="b">
-        <v>0</v>
-      </c>
       <c r="R31" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S31" t="b">
-        <v>1</v>
-      </c>
-      <c r="T31" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="T31" t="b">
+        <v>1</v>
+      </c>
+      <c r="U31" t="b">
+        <v>1</v>
+      </c>
+      <c r="V31" t="inlineStr">
         <is>
           <t>assets/catalogue/saanjh/gift-hampers/01-cover.jpg</t>
         </is>
       </c>
-      <c r="U31" t="inlineStr">
+      <c r="W31" t="inlineStr">
         <is>
           <t>assets/catalogue/saanjh/gift-hampers/02-detail.jpg</t>
         </is>
       </c>
-      <c r="V31" t="inlineStr">
+      <c r="X31" t="inlineStr">
         <is>
           <t>assets/catalogue/saanjh/gift-hampers/03-lifestyle.jpg</t>
         </is>
@@ -3374,7 +3494,7 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>2123.75</v>
+        <v>2100</v>
       </c>
       <c r="F32" t="n">
         <v>1699</v>
@@ -3386,55 +3506,57 @@
         <v>1</v>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>6 × 60 ml</t>
-        </is>
-      </c>
+      <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr">
         <is>
+          <t>6 × 60 ml</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr"/>
+      <c r="N32" t="inlineStr">
+        <is>
           <t>Natural soy wax, cotton wick, phthalate-free fragrance oils</t>
         </is>
       </c>
-      <c r="M32" t="inlineStr">
+      <c r="O32" t="inlineStr">
         <is>
           <t>Discover Set presentation box</t>
         </is>
       </c>
-      <c r="N32" t="inlineStr">
+      <c r="P32" t="inlineStr">
         <is>
           <t>All six Mysaa Rituals fragrances in six 60 ml Mini Ritual candles.</t>
         </is>
       </c>
-      <c r="O32" t="inlineStr">
+      <c r="Q32" t="inlineStr">
         <is>
           <t>A complete discovery of all six Mysaa Rituals fragrances, presented as six 60 ml Mini Ritual candles.</t>
         </is>
       </c>
-      <c r="P32" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q32" t="b">
-        <v>1</v>
-      </c>
       <c r="R32" t="b">
         <v>0</v>
       </c>
       <c r="S32" t="b">
         <v>1</v>
       </c>
-      <c r="T32" t="inlineStr">
+      <c r="T32" t="b">
+        <v>0</v>
+      </c>
+      <c r="U32" t="b">
+        <v>1</v>
+      </c>
+      <c r="V32" t="inlineStr">
         <is>
           <t>assets/catalogue/all-fragrances/discovery-set/01-discover-set.jpg</t>
         </is>
       </c>
-      <c r="U32" t="inlineStr">
+      <c r="W32" t="inlineStr">
         <is>
           <t>assets/catalogue/all-fragrances/discovery-set/02-gulab-ki-chitthi.jpg</t>
         </is>
       </c>
-      <c r="V32" t="inlineStr">
+      <c r="X32" t="inlineStr">
         <is>
           <t>assets/catalogue/all-fragrances/discovery-set/03-dhoop-chandan.jpg</t>
         </is>
@@ -3474,47 +3596,49 @@
         <v>1</v>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>450 ml · 3 wick</t>
-        </is>
-      </c>
+      <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr">
         <is>
+          <t>450 ml · 3 wick</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr"/>
+      <c r="N33" t="inlineStr">
+        <is>
           <t>Natural soy wax, cotton wicks, phthalate-free fragrance oils</t>
         </is>
       </c>
-      <c r="M33" t="inlineStr">
+      <c r="O33" t="inlineStr">
         <is>
           <t>Mysaa Rituals signature packaging</t>
         </is>
       </c>
-      <c r="N33" t="inlineStr">
+      <c r="P33" t="inlineStr">
         <is>
           <t>Gulab Ki Chitthi in our Grand Ritual — a 450 ml, 3-wick luxury candle.</t>
         </is>
       </c>
-      <c r="O33" t="inlineStr">
+      <c r="Q33" t="inlineStr">
         <is>
           <t>A luxurious 450 ml, 3-wick Mysaa Rituals Grand Ritual in the Gulab Ki Chitthi fragrance. Designed for statement gifting and elevated spaces.</t>
         </is>
       </c>
-      <c r="P33" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q33" t="b">
-        <v>1</v>
-      </c>
       <c r="R33" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S33" t="b">
         <v>1</v>
       </c>
-      <c r="T33" t="inlineStr"/>
-      <c r="U33" t="inlineStr"/>
+      <c r="T33" t="b">
+        <v>1</v>
+      </c>
+      <c r="U33" t="b">
+        <v>1</v>
+      </c>
       <c r="V33" t="inlineStr"/>
+      <c r="W33" t="inlineStr"/>
+      <c r="X33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -3550,47 +3674,49 @@
         <v>1</v>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>450 ml · 3 wick</t>
-        </is>
-      </c>
+      <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr">
         <is>
+          <t>450 ml · 3 wick</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr"/>
+      <c r="N34" t="inlineStr">
+        <is>
           <t>Natural soy wax, cotton wicks, phthalate-free fragrance oils</t>
         </is>
       </c>
-      <c r="M34" t="inlineStr">
+      <c r="O34" t="inlineStr">
         <is>
           <t>Mysaa Rituals signature packaging</t>
         </is>
       </c>
-      <c r="N34" t="inlineStr">
+      <c r="P34" t="inlineStr">
         <is>
           <t>Dhoop &amp; Chandan in our Grand Ritual — a 450 ml, 3-wick luxury candle.</t>
         </is>
       </c>
-      <c r="O34" t="inlineStr">
+      <c r="Q34" t="inlineStr">
         <is>
           <t>A luxurious 450 ml, 3-wick Mysaa Rituals Grand Ritual in the Dhoop &amp; Chandan fragrance. Designed for statement gifting and elevated spaces.</t>
         </is>
       </c>
-      <c r="P34" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q34" t="b">
-        <v>1</v>
-      </c>
       <c r="R34" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S34" t="b">
         <v>1</v>
       </c>
-      <c r="T34" t="inlineStr"/>
-      <c r="U34" t="inlineStr"/>
+      <c r="T34" t="b">
+        <v>1</v>
+      </c>
+      <c r="U34" t="b">
+        <v>1</v>
+      </c>
       <c r="V34" t="inlineStr"/>
+      <c r="W34" t="inlineStr"/>
+      <c r="X34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -3626,47 +3752,49 @@
         <v>1</v>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>450 ml · 3 wick</t>
-        </is>
-      </c>
+      <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr">
         <is>
+          <t>450 ml · 3 wick</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr"/>
+      <c r="N35" t="inlineStr">
+        <is>
           <t>Natural soy wax, cotton wicks, phthalate-free fragrance oils</t>
         </is>
       </c>
-      <c r="M35" t="inlineStr">
+      <c r="O35" t="inlineStr">
         <is>
           <t>Mysaa Rituals signature packaging</t>
         </is>
       </c>
-      <c r="N35" t="inlineStr">
+      <c r="P35" t="inlineStr">
         <is>
           <t>Gajre Ka Shringar in our Grand Ritual — a 450 ml, 3-wick luxury candle.</t>
         </is>
       </c>
-      <c r="O35" t="inlineStr">
+      <c r="Q35" t="inlineStr">
         <is>
           <t>A luxurious 450 ml, 3-wick Mysaa Rituals Grand Ritual in the Gajre Ka Shringar fragrance. Designed for statement gifting and elevated spaces.</t>
         </is>
       </c>
-      <c r="P35" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q35" t="b">
-        <v>1</v>
-      </c>
       <c r="R35" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S35" t="b">
         <v>1</v>
       </c>
-      <c r="T35" t="inlineStr"/>
-      <c r="U35" t="inlineStr"/>
+      <c r="T35" t="b">
+        <v>1</v>
+      </c>
+      <c r="U35" t="b">
+        <v>1</v>
+      </c>
       <c r="V35" t="inlineStr"/>
+      <c r="W35" t="inlineStr"/>
+      <c r="X35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -3702,47 +3830,49 @@
         <v>1</v>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>450 ml · 3 wick</t>
-        </is>
-      </c>
+      <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr">
         <is>
+          <t>450 ml · 3 wick</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr"/>
+      <c r="N36" t="inlineStr">
+        <is>
           <t>Natural soy wax, cotton wicks, phthalate-free fragrance oils</t>
         </is>
       </c>
-      <c r="M36" t="inlineStr">
+      <c r="O36" t="inlineStr">
         <is>
           <t>Mysaa Rituals signature packaging</t>
         </is>
       </c>
-      <c r="N36" t="inlineStr">
+      <c r="P36" t="inlineStr">
         <is>
           <t>Madhuban in our Grand Ritual — a 450 ml, 3-wick luxury candle.</t>
         </is>
       </c>
-      <c r="O36" t="inlineStr">
+      <c r="Q36" t="inlineStr">
         <is>
           <t>A luxurious 450 ml, 3-wick Mysaa Rituals Grand Ritual in the Madhuban fragrance. Designed for statement gifting and elevated spaces.</t>
         </is>
       </c>
-      <c r="P36" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q36" t="b">
-        <v>1</v>
-      </c>
       <c r="R36" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S36" t="b">
         <v>1</v>
       </c>
-      <c r="T36" t="inlineStr"/>
-      <c r="U36" t="inlineStr"/>
+      <c r="T36" t="b">
+        <v>1</v>
+      </c>
+      <c r="U36" t="b">
+        <v>1</v>
+      </c>
       <c r="V36" t="inlineStr"/>
+      <c r="W36" t="inlineStr"/>
+      <c r="X36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -3778,47 +3908,49 @@
         <v>1</v>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>450 ml · 3 wick</t>
-        </is>
-      </c>
+      <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr">
         <is>
+          <t>450 ml · 3 wick</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr"/>
+      <c r="N37" t="inlineStr">
+        <is>
           <t>Natural soy wax, cotton wicks, phthalate-free fragrance oils</t>
         </is>
       </c>
-      <c r="M37" t="inlineStr">
+      <c r="O37" t="inlineStr">
         <is>
           <t>Mysaa Rituals signature packaging</t>
         </is>
       </c>
-      <c r="N37" t="inlineStr">
+      <c r="P37" t="inlineStr">
         <is>
           <t>Raat Ki Rani in our Grand Ritual — a 450 ml, 3-wick luxury candle.</t>
         </is>
       </c>
-      <c r="O37" t="inlineStr">
+      <c r="Q37" t="inlineStr">
         <is>
           <t>A luxurious 450 ml, 3-wick Mysaa Rituals Grand Ritual in the Raat Ki Rani fragrance. Designed for statement gifting and elevated spaces.</t>
         </is>
       </c>
-      <c r="P37" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q37" t="b">
-        <v>1</v>
-      </c>
       <c r="R37" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S37" t="b">
         <v>1</v>
       </c>
-      <c r="T37" t="inlineStr"/>
-      <c r="U37" t="inlineStr"/>
+      <c r="T37" t="b">
+        <v>1</v>
+      </c>
+      <c r="U37" t="b">
+        <v>1</v>
+      </c>
       <c r="V37" t="inlineStr"/>
+      <c r="W37" t="inlineStr"/>
+      <c r="X37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -3854,47 +3986,49 @@
         <v>1</v>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>450 ml · 3 wick</t>
-        </is>
-      </c>
+      <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
       <c r="L38" t="inlineStr">
         <is>
+          <t>450 ml · 3 wick</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr"/>
+      <c r="N38" t="inlineStr">
+        <is>
           <t>Natural soy wax, cotton wicks, phthalate-free fragrance oils</t>
         </is>
       </c>
-      <c r="M38" t="inlineStr">
+      <c r="O38" t="inlineStr">
         <is>
           <t>Mysaa Rituals signature packaging</t>
         </is>
       </c>
-      <c r="N38" t="inlineStr">
+      <c r="P38" t="inlineStr">
         <is>
           <t>Saanjh in our Grand Ritual — a 450 ml, 3-wick luxury candle.</t>
         </is>
       </c>
-      <c r="O38" t="inlineStr">
+      <c r="Q38" t="inlineStr">
         <is>
           <t>A luxurious 450 ml, 3-wick Mysaa Rituals Grand Ritual in the Saanjh fragrance. Designed for statement gifting and elevated spaces.</t>
         </is>
       </c>
-      <c r="P38" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q38" t="b">
-        <v>1</v>
-      </c>
       <c r="R38" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S38" t="b">
         <v>1</v>
       </c>
-      <c r="T38" t="inlineStr"/>
-      <c r="U38" t="inlineStr"/>
+      <c r="T38" t="b">
+        <v>1</v>
+      </c>
+      <c r="U38" t="b">
+        <v>1</v>
+      </c>
       <c r="V38" t="inlineStr"/>
+      <c r="W38" t="inlineStr"/>
+      <c r="X38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -3913,10 +4047,10 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="F39" t="n">
-        <v>0</v>
+        <v>399</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
@@ -3926,50 +4060,56 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
+          <t>in-stock</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr">
+        <is>
           <t>Daisy|Rose|Carnation|Cactus|Tortoise|Laddu|Chakli</t>
         </is>
       </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>MOQ 6 pieces</t>
-        </is>
-      </c>
-      <c r="K39" t="inlineStr"/>
       <c r="L39" t="inlineStr">
         <is>
+          <t>6 pieces minimum</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr"/>
+      <c r="N39" t="inlineStr">
+        <is>
           <t>Hand-poured wax candle</t>
         </is>
       </c>
-      <c r="M39" t="inlineStr">
+      <c r="O39" t="inlineStr">
         <is>
           <t>Mysaa Rituals signature packaging</t>
         </is>
       </c>
-      <c r="N39" t="inlineStr">
-        <is>
-          <t>Choose from Daisy, Rose, Carnation, Cactus, Tortoise, Laddu or Chakli moulds. Minimum order 6 pieces.</t>
-        </is>
-      </c>
-      <c r="O39" t="inlineStr">
-        <is>
-          <t>A playful collection of handcrafted mould candles. Select one mould style for a minimum batch of 6 pieces.</t>
-        </is>
-      </c>
-      <c r="P39" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q39" t="b">
-        <v>1</v>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Create a custom batch of mould candles with your choice of shape, fragrance and primary colour.</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>Choose one mould shape, one Mysaa Rituals fragrance and one primary colour for your batch. Minimum order is 6 pieces. The current batch price is ₹399 for 6 pieces.</t>
+        </is>
       </c>
       <c r="R39" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S39" t="b">
         <v>1</v>
       </c>
-      <c r="T39" t="inlineStr"/>
-      <c r="U39" t="inlineStr"/>
+      <c r="T39" t="b">
+        <v>1</v>
+      </c>
+      <c r="U39" t="b">
+        <v>1</v>
+      </c>
       <c r="V39" t="inlineStr"/>
+      <c r="W39" t="inlineStr"/>
+      <c r="X39" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4255,7 +4395,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Signature</t>
+          <t>Signature Ritual</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -4400,7 +4540,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>MOQ 6 pieces · choose your shape</t>
+          <t>MOQ 6 pieces · ₹399 for 6 pieces</t>
         </is>
       </c>
       <c r="D9" t="b">

--- a/data/mysaa_products.xlsx
+++ b/data/mysaa_products.xlsx
@@ -449,9 +449,7 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr"/>
-    </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
@@ -473,9 +471,7 @@
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr"/>
-    </row>
+    <row r="6"/>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
@@ -560,9 +556,7 @@
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" t="inlineStr"/>
-    </row>
+    <row r="19"/>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
@@ -754,7 +748,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1000</v>
+        <v>999</v>
       </c>
       <c r="F2" t="n">
         <v>799</v>
@@ -765,15 +759,11 @@
       <c r="H2" t="n">
         <v>1</v>
       </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr">
         <is>
           <t>220 ml</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr">
         <is>
           <t>Natural soy wax, cotton wick, phthalate-free fragrance oils</t>
@@ -844,7 +834,7 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="F3" t="n">
         <v>549</v>
@@ -855,15 +845,11 @@
       <c r="H3" t="n">
         <v>1</v>
       </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr">
         <is>
           <t>120 ml</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
           <t>Natural soy wax, cotton wick, phthalate-free fragrance oils</t>
@@ -934,7 +920,7 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="F4" t="n">
         <v>299</v>
@@ -945,15 +931,11 @@
       <c r="H4" t="n">
         <v>1</v>
       </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr">
         <is>
           <t>60 ml</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr">
         <is>
           <t>Natural soy wax, cotton wick, phthalate-free fragrance oils</t>
@@ -1040,14 +1022,11 @@
           <t>out-of-stock</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr">
         <is>
           <t>Combo</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr">
         <is>
           <t>Natural soy wax, cotton wick, phthalate-free fragrance oils</t>
@@ -1129,19 +1108,16 @@
       <c r="H6" t="n">
         <v>1</v>
       </c>
-      <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr">
         <is>
           <t>weddings-return-gifts</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr">
         <is>
           <t>Curated set</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr">
         <is>
           <t>Curated Mysaa Rituals gifting selection</t>
@@ -1212,7 +1188,7 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1000</v>
+        <v>999</v>
       </c>
       <c r="F7" t="n">
         <v>799</v>
@@ -1223,15 +1199,11 @@
       <c r="H7" t="n">
         <v>1</v>
       </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr">
         <is>
           <t>220 ml</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr">
         <is>
           <t>Natural soy wax, cotton wick, phthalate-free fragrance oils</t>
@@ -1302,7 +1274,7 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="F8" t="n">
         <v>549</v>
@@ -1313,15 +1285,11 @@
       <c r="H8" t="n">
         <v>1</v>
       </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr">
         <is>
           <t>120 ml</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr">
         <is>
           <t>Natural soy wax, cotton wick, phthalate-free fragrance oils</t>
@@ -1392,7 +1360,7 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="F9" t="n">
         <v>299</v>
@@ -1403,15 +1371,11 @@
       <c r="H9" t="n">
         <v>1</v>
       </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr">
         <is>
           <t>60 ml</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr">
         <is>
           <t>Natural soy wax, cotton wick, phthalate-free fragrance oils</t>
@@ -1498,14 +1462,11 @@
           <t>out-of-stock</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr">
         <is>
           <t>Combo</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr">
         <is>
           <t>Natural soy wax, cotton wick, phthalate-free fragrance oils</t>
@@ -1587,19 +1548,16 @@
       <c r="H11" t="n">
         <v>1</v>
       </c>
-      <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr">
         <is>
           <t>festivals-celebrations</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr">
         <is>
           <t>Curated set</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr">
         <is>
           <t>Curated Mysaa Rituals gifting selection</t>
@@ -1670,7 +1628,7 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1000</v>
+        <v>999</v>
       </c>
       <c r="F12" t="n">
         <v>799</v>
@@ -1681,15 +1639,11 @@
       <c r="H12" t="n">
         <v>1</v>
       </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr">
         <is>
           <t>220 ml</t>
         </is>
       </c>
-      <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr">
         <is>
           <t>Natural soy wax, cotton wick, phthalate-free fragrance oils</t>
@@ -1760,7 +1714,7 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="F13" t="n">
         <v>549</v>
@@ -1771,15 +1725,11 @@
       <c r="H13" t="n">
         <v>1</v>
       </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr">
         <is>
           <t>120 ml</t>
         </is>
       </c>
-      <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr">
         <is>
           <t>Natural soy wax, cotton wick, phthalate-free fragrance oils</t>
@@ -1850,7 +1800,7 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="F14" t="n">
         <v>299</v>
@@ -1861,15 +1811,11 @@
       <c r="H14" t="n">
         <v>1</v>
       </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr">
         <is>
           <t>60 ml</t>
         </is>
       </c>
-      <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr">
         <is>
           <t>Natural soy wax, cotton wick, phthalate-free fragrance oils</t>
@@ -1956,14 +1902,11 @@
           <t>out-of-stock</t>
         </is>
       </c>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr">
         <is>
           <t>Combo</t>
         </is>
       </c>
-      <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr">
         <is>
           <t>Natural soy wax, cotton wick, phthalate-free fragrance oils</t>
@@ -2045,19 +1988,16 @@
       <c r="H16" t="n">
         <v>1</v>
       </c>
-      <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr">
         <is>
           <t>weddings-return-gifts</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr">
         <is>
           <t>Curated set</t>
         </is>
       </c>
-      <c r="M16" t="inlineStr"/>
       <c r="N16" t="inlineStr">
         <is>
           <t>Curated Mysaa Rituals gifting selection</t>
@@ -2128,7 +2068,7 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1000</v>
+        <v>999</v>
       </c>
       <c r="F17" t="n">
         <v>799</v>
@@ -2139,15 +2079,11 @@
       <c r="H17" t="n">
         <v>1</v>
       </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr">
         <is>
           <t>220 ml</t>
         </is>
       </c>
-      <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr">
         <is>
           <t>Natural soy wax, cotton wick, phthalate-free fragrance oils</t>
@@ -2218,7 +2154,7 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="F18" t="n">
         <v>549</v>
@@ -2229,15 +2165,11 @@
       <c r="H18" t="n">
         <v>1</v>
       </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr">
         <is>
           <t>120 ml</t>
         </is>
       </c>
-      <c r="M18" t="inlineStr"/>
       <c r="N18" t="inlineStr">
         <is>
           <t>Natural soy wax, cotton wick, phthalate-free fragrance oils</t>
@@ -2308,7 +2240,7 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="F19" t="n">
         <v>299</v>
@@ -2319,15 +2251,11 @@
       <c r="H19" t="n">
         <v>1</v>
       </c>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr">
         <is>
           <t>60 ml</t>
         </is>
       </c>
-      <c r="M19" t="inlineStr"/>
       <c r="N19" t="inlineStr">
         <is>
           <t>Natural soy wax, cotton wick, phthalate-free fragrance oils</t>
@@ -2414,14 +2342,11 @@
           <t>out-of-stock</t>
         </is>
       </c>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr">
         <is>
           <t>Combo</t>
         </is>
       </c>
-      <c r="M20" t="inlineStr"/>
       <c r="N20" t="inlineStr">
         <is>
           <t>Natural soy wax, cotton wick, phthalate-free fragrance oils</t>
@@ -2503,19 +2428,16 @@
       <c r="H21" t="n">
         <v>1</v>
       </c>
-      <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr">
         <is>
           <t>festivals-celebrations</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr">
         <is>
           <t>Curated set</t>
         </is>
       </c>
-      <c r="M21" t="inlineStr"/>
       <c r="N21" t="inlineStr">
         <is>
           <t>Curated Mysaa Rituals gifting selection</t>
@@ -2586,7 +2508,7 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1000</v>
+        <v>999</v>
       </c>
       <c r="F22" t="n">
         <v>799</v>
@@ -2597,15 +2519,11 @@
       <c r="H22" t="n">
         <v>1</v>
       </c>
-      <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr">
         <is>
           <t>220 ml</t>
         </is>
       </c>
-      <c r="M22" t="inlineStr"/>
       <c r="N22" t="inlineStr">
         <is>
           <t>Natural soy wax, cotton wick, phthalate-free fragrance oils</t>
@@ -2676,7 +2594,7 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="F23" t="n">
         <v>549</v>
@@ -2687,15 +2605,11 @@
       <c r="H23" t="n">
         <v>1</v>
       </c>
-      <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr">
         <is>
           <t>120 ml</t>
         </is>
       </c>
-      <c r="M23" t="inlineStr"/>
       <c r="N23" t="inlineStr">
         <is>
           <t>Natural soy wax, cotton wick, phthalate-free fragrance oils</t>
@@ -2766,7 +2680,7 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="F24" t="n">
         <v>299</v>
@@ -2777,15 +2691,11 @@
       <c r="H24" t="n">
         <v>1</v>
       </c>
-      <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr">
         <is>
           <t>60 ml</t>
         </is>
       </c>
-      <c r="M24" t="inlineStr"/>
       <c r="N24" t="inlineStr">
         <is>
           <t>Natural soy wax, cotton wick, phthalate-free fragrance oils</t>
@@ -2872,14 +2782,11 @@
           <t>out-of-stock</t>
         </is>
       </c>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr">
         <is>
           <t>Combo</t>
         </is>
       </c>
-      <c r="M25" t="inlineStr"/>
       <c r="N25" t="inlineStr">
         <is>
           <t>Natural soy wax, cotton wick, phthalate-free fragrance oils</t>
@@ -2961,19 +2868,16 @@
       <c r="H26" t="n">
         <v>1</v>
       </c>
-      <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr">
         <is>
           <t>birthdays-just-because</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr">
         <is>
           <t>Curated set</t>
         </is>
       </c>
-      <c r="M26" t="inlineStr"/>
       <c r="N26" t="inlineStr">
         <is>
           <t>Curated Mysaa Rituals gifting selection</t>
@@ -3044,7 +2948,7 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1000</v>
+        <v>999</v>
       </c>
       <c r="F27" t="n">
         <v>799</v>
@@ -3055,15 +2959,11 @@
       <c r="H27" t="n">
         <v>1</v>
       </c>
-      <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr">
         <is>
           <t>220 ml</t>
         </is>
       </c>
-      <c r="M27" t="inlineStr"/>
       <c r="N27" t="inlineStr">
         <is>
           <t>Natural soy wax, cotton wick, phthalate-free fragrance oils</t>
@@ -3134,7 +3034,7 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="F28" t="n">
         <v>549</v>
@@ -3145,15 +3045,11 @@
       <c r="H28" t="n">
         <v>1</v>
       </c>
-      <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr">
         <is>
           <t>120 ml</t>
         </is>
       </c>
-      <c r="M28" t="inlineStr"/>
       <c r="N28" t="inlineStr">
         <is>
           <t>Natural soy wax, cotton wick, phthalate-free fragrance oils</t>
@@ -3224,7 +3120,7 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="F29" t="n">
         <v>299</v>
@@ -3235,15 +3131,11 @@
       <c r="H29" t="n">
         <v>1</v>
       </c>
-      <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr">
         <is>
           <t>60 ml</t>
         </is>
       </c>
-      <c r="M29" t="inlineStr"/>
       <c r="N29" t="inlineStr">
         <is>
           <t>Natural soy wax, cotton wick, phthalate-free fragrance oils</t>
@@ -3330,10 +3222,6 @@
           <t>out-of-stock</t>
         </is>
       </c>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr"/>
       <c r="N30" t="inlineStr">
         <is>
           <t>Natural soy wax, cotton wick, phthalate-free fragrance oils</t>
@@ -3415,15 +3303,11 @@
       <c r="H31" t="n">
         <v>1</v>
       </c>
-      <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr">
         <is>
           <t>birthdays-just-because</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr"/>
       <c r="N31" t="inlineStr">
         <is>
           <t>Natural soy wax, cotton wick, phthalate-free fragrance oils</t>
@@ -3494,7 +3378,7 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>2100</v>
+        <v>2099</v>
       </c>
       <c r="F32" t="n">
         <v>1699</v>
@@ -3505,15 +3389,11 @@
       <c r="H32" t="n">
         <v>1</v>
       </c>
-      <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr">
         <is>
           <t>6 × 60 ml</t>
         </is>
       </c>
-      <c r="M32" t="inlineStr"/>
       <c r="N32" t="inlineStr">
         <is>
           <t>Natural soy wax, cotton wick, phthalate-free fragrance oils</t>
@@ -3595,15 +3475,11 @@
       <c r="H33" t="n">
         <v>1</v>
       </c>
-      <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr">
         <is>
           <t>450 ml · 3 wick</t>
         </is>
       </c>
-      <c r="M33" t="inlineStr"/>
       <c r="N33" t="inlineStr">
         <is>
           <t>Natural soy wax, cotton wicks, phthalate-free fragrance oils</t>
@@ -3636,9 +3512,6 @@
       <c r="U33" t="b">
         <v>1</v>
       </c>
-      <c r="V33" t="inlineStr"/>
-      <c r="W33" t="inlineStr"/>
-      <c r="X33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -3673,15 +3546,11 @@
       <c r="H34" t="n">
         <v>1</v>
       </c>
-      <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr">
         <is>
           <t>450 ml · 3 wick</t>
         </is>
       </c>
-      <c r="M34" t="inlineStr"/>
       <c r="N34" t="inlineStr">
         <is>
           <t>Natural soy wax, cotton wicks, phthalate-free fragrance oils</t>
@@ -3714,9 +3583,6 @@
       <c r="U34" t="b">
         <v>1</v>
       </c>
-      <c r="V34" t="inlineStr"/>
-      <c r="W34" t="inlineStr"/>
-      <c r="X34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -3751,15 +3617,11 @@
       <c r="H35" t="n">
         <v>1</v>
       </c>
-      <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr">
         <is>
           <t>450 ml · 3 wick</t>
         </is>
       </c>
-      <c r="M35" t="inlineStr"/>
       <c r="N35" t="inlineStr">
         <is>
           <t>Natural soy wax, cotton wicks, phthalate-free fragrance oils</t>
@@ -3792,9 +3654,6 @@
       <c r="U35" t="b">
         <v>1</v>
       </c>
-      <c r="V35" t="inlineStr"/>
-      <c r="W35" t="inlineStr"/>
-      <c r="X35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -3829,15 +3688,11 @@
       <c r="H36" t="n">
         <v>1</v>
       </c>
-      <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr">
         <is>
           <t>450 ml · 3 wick</t>
         </is>
       </c>
-      <c r="M36" t="inlineStr"/>
       <c r="N36" t="inlineStr">
         <is>
           <t>Natural soy wax, cotton wicks, phthalate-free fragrance oils</t>
@@ -3870,9 +3725,6 @@
       <c r="U36" t="b">
         <v>1</v>
       </c>
-      <c r="V36" t="inlineStr"/>
-      <c r="W36" t="inlineStr"/>
-      <c r="X36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -3907,15 +3759,11 @@
       <c r="H37" t="n">
         <v>1</v>
       </c>
-      <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr">
         <is>
           <t>450 ml · 3 wick</t>
         </is>
       </c>
-      <c r="M37" t="inlineStr"/>
       <c r="N37" t="inlineStr">
         <is>
           <t>Natural soy wax, cotton wicks, phthalate-free fragrance oils</t>
@@ -3948,9 +3796,6 @@
       <c r="U37" t="b">
         <v>1</v>
       </c>
-      <c r="V37" t="inlineStr"/>
-      <c r="W37" t="inlineStr"/>
-      <c r="X37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -3985,15 +3830,11 @@
       <c r="H38" t="n">
         <v>1</v>
       </c>
-      <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
       <c r="L38" t="inlineStr">
         <is>
           <t>450 ml · 3 wick</t>
         </is>
       </c>
-      <c r="M38" t="inlineStr"/>
       <c r="N38" t="inlineStr">
         <is>
           <t>Natural soy wax, cotton wicks, phthalate-free fragrance oils</t>
@@ -4026,9 +3867,6 @@
       <c r="U38" t="b">
         <v>1</v>
       </c>
-      <c r="V38" t="inlineStr"/>
-      <c r="W38" t="inlineStr"/>
-      <c r="X38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -4047,7 +3885,7 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="F39" t="n">
         <v>399</v>
@@ -4063,7 +3901,6 @@
           <t>in-stock</t>
         </is>
       </c>
-      <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr">
         <is>
           <t>Daisy|Rose|Carnation|Cactus|Tortoise|Laddu|Chakli</t>
@@ -4074,7 +3911,6 @@
           <t>6 pieces minimum</t>
         </is>
       </c>
-      <c r="M39" t="inlineStr"/>
       <c r="N39" t="inlineStr">
         <is>
           <t>Hand-poured wax candle</t>
@@ -4107,9 +3943,6 @@
       <c r="U39" t="b">
         <v>1</v>
       </c>
-      <c r="V39" t="inlineStr"/>
-      <c r="W39" t="inlineStr"/>
-      <c r="X39" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4558,7 +4391,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B23"/>
+  <dimension ref="A1:B24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -4830,6 +4663,18 @@
         </is>
       </c>
     </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>orderEmail</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>mysaarituals@gmail.com</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/mysaa_products.xlsx
+++ b/data/mysaa_products.xlsx
@@ -449,7 +449,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
@@ -471,7 +470,6 @@
         </is>
       </c>
     </row>
-    <row r="6"/>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
@@ -556,7 +554,6 @@
         </is>
       </c>
     </row>
-    <row r="19"/>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
@@ -759,6 +756,12 @@
       <c r="H2" t="n">
         <v>1</v>
       </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>weddings-return-gifts</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr">
         <is>
           <t>220 ml</t>
@@ -845,6 +848,12 @@
       <c r="H3" t="n">
         <v>1</v>
       </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>weddings-return-gifts</t>
+        </is>
+      </c>
       <c r="L3" t="inlineStr">
         <is>
           <t>120 ml</t>
@@ -931,6 +940,12 @@
       <c r="H4" t="n">
         <v>1</v>
       </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>weddings-return-gifts</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr">
         <is>
           <t>60 ml</t>
@@ -1022,6 +1037,11 @@
           <t>out-of-stock</t>
         </is>
       </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>weddings-return-gifts</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr">
         <is>
           <t>Combo</t>
@@ -1108,6 +1128,7 @@
       <c r="H6" t="n">
         <v>1</v>
       </c>
+      <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr">
         <is>
           <t>weddings-return-gifts</t>
@@ -1199,6 +1220,12 @@
       <c r="H7" t="n">
         <v>1</v>
       </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>festivals-celebrations</t>
+        </is>
+      </c>
       <c r="L7" t="inlineStr">
         <is>
           <t>220 ml</t>
@@ -1285,6 +1312,12 @@
       <c r="H8" t="n">
         <v>1</v>
       </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>festivals-celebrations</t>
+        </is>
+      </c>
       <c r="L8" t="inlineStr">
         <is>
           <t>120 ml</t>
@@ -1371,6 +1404,12 @@
       <c r="H9" t="n">
         <v>1</v>
       </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>festivals-celebrations</t>
+        </is>
+      </c>
       <c r="L9" t="inlineStr">
         <is>
           <t>60 ml</t>
@@ -1462,6 +1501,11 @@
           <t>out-of-stock</t>
         </is>
       </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>festivals-celebrations</t>
+        </is>
+      </c>
       <c r="L10" t="inlineStr">
         <is>
           <t>Combo</t>
@@ -1548,6 +1592,7 @@
       <c r="H11" t="n">
         <v>1</v>
       </c>
+      <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr">
         <is>
           <t>festivals-celebrations</t>
@@ -1639,6 +1684,12 @@
       <c r="H12" t="n">
         <v>1</v>
       </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>weddings-return-gifts</t>
+        </is>
+      </c>
       <c r="L12" t="inlineStr">
         <is>
           <t>220 ml</t>
@@ -1725,6 +1776,12 @@
       <c r="H13" t="n">
         <v>1</v>
       </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>weddings-return-gifts</t>
+        </is>
+      </c>
       <c r="L13" t="inlineStr">
         <is>
           <t>120 ml</t>
@@ -1811,6 +1868,12 @@
       <c r="H14" t="n">
         <v>1</v>
       </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>weddings-return-gifts</t>
+        </is>
+      </c>
       <c r="L14" t="inlineStr">
         <is>
           <t>60 ml</t>
@@ -1902,6 +1965,11 @@
           <t>out-of-stock</t>
         </is>
       </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>weddings-return-gifts</t>
+        </is>
+      </c>
       <c r="L15" t="inlineStr">
         <is>
           <t>Combo</t>
@@ -1988,6 +2056,7 @@
       <c r="H16" t="n">
         <v>1</v>
       </c>
+      <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr">
         <is>
           <t>weddings-return-gifts</t>
@@ -2079,6 +2148,12 @@
       <c r="H17" t="n">
         <v>1</v>
       </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>festivals-celebrations</t>
+        </is>
+      </c>
       <c r="L17" t="inlineStr">
         <is>
           <t>220 ml</t>
@@ -2165,6 +2240,12 @@
       <c r="H18" t="n">
         <v>1</v>
       </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>festivals-celebrations</t>
+        </is>
+      </c>
       <c r="L18" t="inlineStr">
         <is>
           <t>120 ml</t>
@@ -2251,6 +2332,12 @@
       <c r="H19" t="n">
         <v>1</v>
       </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>festivals-celebrations</t>
+        </is>
+      </c>
       <c r="L19" t="inlineStr">
         <is>
           <t>60 ml</t>
@@ -2342,6 +2429,11 @@
           <t>out-of-stock</t>
         </is>
       </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>festivals-celebrations</t>
+        </is>
+      </c>
       <c r="L20" t="inlineStr">
         <is>
           <t>Combo</t>
@@ -2428,6 +2520,7 @@
       <c r="H21" t="n">
         <v>1</v>
       </c>
+      <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr">
         <is>
           <t>festivals-celebrations</t>
@@ -2519,6 +2612,12 @@
       <c r="H22" t="n">
         <v>1</v>
       </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>birthdays-just-because</t>
+        </is>
+      </c>
       <c r="L22" t="inlineStr">
         <is>
           <t>220 ml</t>
@@ -2605,6 +2704,12 @@
       <c r="H23" t="n">
         <v>1</v>
       </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>birthdays-just-because</t>
+        </is>
+      </c>
       <c r="L23" t="inlineStr">
         <is>
           <t>120 ml</t>
@@ -2691,6 +2796,12 @@
       <c r="H24" t="n">
         <v>1</v>
       </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>birthdays-just-because</t>
+        </is>
+      </c>
       <c r="L24" t="inlineStr">
         <is>
           <t>60 ml</t>
@@ -2782,6 +2893,11 @@
           <t>out-of-stock</t>
         </is>
       </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>birthdays-just-because</t>
+        </is>
+      </c>
       <c r="L25" t="inlineStr">
         <is>
           <t>Combo</t>
@@ -2868,6 +2984,7 @@
       <c r="H26" t="n">
         <v>1</v>
       </c>
+      <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr">
         <is>
           <t>birthdays-just-because</t>
@@ -2959,6 +3076,12 @@
       <c r="H27" t="n">
         <v>1</v>
       </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>birthdays-just-because</t>
+        </is>
+      </c>
       <c r="L27" t="inlineStr">
         <is>
           <t>220 ml</t>
@@ -3045,6 +3168,12 @@
       <c r="H28" t="n">
         <v>1</v>
       </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>birthdays-just-because</t>
+        </is>
+      </c>
       <c r="L28" t="inlineStr">
         <is>
           <t>120 ml</t>
@@ -3131,6 +3260,12 @@
       <c r="H29" t="n">
         <v>1</v>
       </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>birthdays-just-because</t>
+        </is>
+      </c>
       <c r="L29" t="inlineStr">
         <is>
           <t>60 ml</t>
@@ -3222,6 +3357,11 @@
           <t>out-of-stock</t>
         </is>
       </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>birthdays-just-because</t>
+        </is>
+      </c>
       <c r="N30" t="inlineStr">
         <is>
           <t>Natural soy wax, cotton wick, phthalate-free fragrance oils</t>
@@ -3303,6 +3443,7 @@
       <c r="H31" t="n">
         <v>1</v>
       </c>
+      <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr">
         <is>
           <t>birthdays-just-because</t>
@@ -3389,6 +3530,12 @@
       <c r="H32" t="n">
         <v>1</v>
       </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>festivals-celebrations|weddings-return-gifts|birthdays-just-because</t>
+        </is>
+      </c>
       <c r="L32" t="inlineStr">
         <is>
           <t>6 × 60 ml</t>
@@ -3464,16 +3611,22 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>0</v>
+        <v>1999</v>
       </c>
       <c r="F33" t="n">
-        <v>0</v>
+        <v>1499</v>
       </c>
       <c r="G33" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="H33" t="n">
         <v>1</v>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>weddings-return-gifts</t>
+        </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
@@ -3535,16 +3688,22 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>0</v>
+        <v>1999</v>
       </c>
       <c r="F34" t="n">
-        <v>0</v>
+        <v>1499</v>
       </c>
       <c r="G34" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="H34" t="n">
         <v>1</v>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>festivals-celebrations</t>
+        </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
@@ -3606,16 +3765,22 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>0</v>
+        <v>1999</v>
       </c>
       <c r="F35" t="n">
-        <v>0</v>
+        <v>1499</v>
       </c>
       <c r="G35" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="H35" t="n">
         <v>1</v>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>weddings-return-gifts</t>
+        </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
@@ -3677,16 +3842,22 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>0</v>
+        <v>1999</v>
       </c>
       <c r="F36" t="n">
-        <v>0</v>
+        <v>1499</v>
       </c>
       <c r="G36" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="H36" t="n">
         <v>1</v>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>festivals-celebrations</t>
+        </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
@@ -3748,16 +3919,22 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>0</v>
+        <v>1999</v>
       </c>
       <c r="F37" t="n">
-        <v>0</v>
+        <v>1499</v>
       </c>
       <c r="G37" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="H37" t="n">
         <v>1</v>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>birthdays-just-because</t>
+        </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
@@ -3819,16 +3996,22 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>0</v>
+        <v>1999</v>
       </c>
       <c r="F38" t="n">
-        <v>0</v>
+        <v>1499</v>
       </c>
       <c r="G38" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="H38" t="n">
         <v>1</v>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>birthdays-just-because</t>
+        </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
@@ -3899,6 +4082,11 @@
       <c r="I39" t="inlineStr">
         <is>
           <t>in-stock</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>festivals-celebrations|weddings-return-gifts|birthdays-just-because</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">

--- a/data/mysaa_products.xlsx
+++ b/data/mysaa_products.xlsx
@@ -449,6 +449,9 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="inlineStr"/>
+    </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
@@ -470,6 +473,9 @@
         </is>
       </c>
     </row>
+    <row r="6">
+      <c r="A6" t="inlineStr"/>
+    </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
@@ -553,6 +559,9 @@
           <t xml:space="preserve">   will update the live site automatically within a minute or two.</t>
         </is>
       </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -572,7 +581,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X39"/>
+  <dimension ref="A1:AE39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="37" customWidth="1" min="1" max="1"/>
@@ -584,7 +593,7 @@
     <col width="17" customWidth="1" min="7" max="7"/>
     <col width="12" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="24" customWidth="1" min="10" max="10"/>
+    <col width="50" customWidth="1" min="10" max="10"/>
     <col width="50" customWidth="1" min="11" max="11"/>
     <col width="18" customWidth="1" min="12" max="12"/>
     <col width="12" customWidth="1" min="13" max="13"/>
@@ -592,13 +601,20 @@
     <col width="35" customWidth="1" min="15" max="15"/>
     <col width="50" customWidth="1" min="16" max="16"/>
     <col width="50" customWidth="1" min="17" max="17"/>
-    <col width="12" customWidth="1" min="18" max="18"/>
-    <col width="12" customWidth="1" min="19" max="19"/>
-    <col width="14" customWidth="1" min="20" max="20"/>
-    <col width="12" customWidth="1" min="21" max="21"/>
+    <col width="50" customWidth="1" min="18" max="18"/>
+    <col width="50" customWidth="1" min="19" max="19"/>
+    <col width="50" customWidth="1" min="20" max="20"/>
+    <col width="50" customWidth="1" min="21" max="21"/>
     <col width="50" customWidth="1" min="22" max="22"/>
     <col width="50" customWidth="1" min="23" max="23"/>
     <col width="50" customWidth="1" min="24" max="24"/>
+    <col width="12" customWidth="1" min="25" max="25"/>
+    <col width="12" customWidth="1" min="26" max="26"/>
+    <col width="14" customWidth="1" min="27" max="27"/>
+    <col width="12" customWidth="1" min="28" max="28"/>
+    <col width="50" customWidth="1" min="29" max="29"/>
+    <col width="50" customWidth="1" min="30" max="30"/>
+    <col width="50" customWidth="1" min="31" max="31"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -689,35 +705,70 @@
       </c>
       <c r="R1" s="2" t="inlineStr">
         <is>
+          <t>description</t>
+        </is>
+      </c>
+      <c r="S1" s="2" t="inlineStr">
+        <is>
+          <t>burnTime</t>
+        </is>
+      </c>
+      <c r="T1" s="2" t="inlineStr">
+        <is>
+          <t>careInstructions</t>
+        </is>
+      </c>
+      <c r="U1" s="2" t="inlineStr">
+        <is>
+          <t>deliveryTime</t>
+        </is>
+      </c>
+      <c r="V1" s="2" t="inlineStr">
+        <is>
+          <t>shippingNote</t>
+        </is>
+      </c>
+      <c r="W1" s="2" t="inlineStr">
+        <is>
+          <t>returnsPolicy</t>
+        </is>
+      </c>
+      <c r="X1" s="2" t="inlineStr">
+        <is>
+          <t>seoKeywords</t>
+        </is>
+      </c>
+      <c r="Y1" s="2" t="inlineStr">
+        <is>
           <t>bestseller</t>
         </is>
       </c>
-      <c r="S1" s="2" t="inlineStr">
+      <c r="Z1" s="2" t="inlineStr">
         <is>
           <t>isNew</t>
         </is>
       </c>
-      <c r="T1" s="2" t="inlineStr">
+      <c r="AA1" s="2" t="inlineStr">
         <is>
           <t>customizable</t>
         </is>
       </c>
-      <c r="U1" s="2" t="inlineStr">
+      <c r="AB1" s="2" t="inlineStr">
         <is>
           <t>active</t>
         </is>
       </c>
-      <c r="V1" s="2" t="inlineStr">
+      <c r="AC1" s="2" t="inlineStr">
         <is>
           <t>image1</t>
         </is>
       </c>
-      <c r="W1" s="2" t="inlineStr">
+      <c r="AD1" s="2" t="inlineStr">
         <is>
           <t>image2</t>
         </is>
       </c>
-      <c r="X1" s="2" t="inlineStr">
+      <c r="AE1" s="2" t="inlineStr">
         <is>
           <t>image3</t>
         </is>
@@ -762,11 +813,13 @@
           <t>weddings-return-gifts</t>
         </is>
       </c>
+      <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr">
         <is>
           <t>220 ml</t>
         </is>
       </c>
+      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr">
         <is>
           <t>Natural soy wax, cotton wick, phthalate-free fragrance oils</t>
@@ -779,7 +832,7 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Gulab Ki Chitthi in our signature ritual.</t>
+          <t>Gulab Ki Chitthi · Signature Ritual. A fragrance that feels like receiving an old handwritten letter carrying the scent of roses.</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
@@ -787,29 +840,64 @@
           <t>A Mysaa Rituals signature ritual in the Gulab Ki Chitthi fragrance. Made for gifting, rituals and everyday moments.</t>
         </is>
       </c>
-      <c r="R2" t="b">
-        <v>0</v>
-      </c>
-      <c r="S2" t="b">
-        <v>0</v>
-      </c>
-      <c r="T2" t="b">
-        <v>1</v>
-      </c>
-      <c r="U2" t="b">
-        <v>1</v>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>Gulab Ki Chitthi Signature Ritual is a handcrafted signature ritual scented with Gulab Ki Chitthi. A fragrance that feels like receiving an old handwritten letter carrying the scent of roses. Made with natural soy wax, cotton wick(s) and phthalate-free fragrance oils, it is designed for slow everyday rituals, meaningful gifting and fragrance-led spaces.</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>Approx. 35–45 hours</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>Trim the wick to about 5 mm before each burn. On the first burn, allow the wax pool to reach the edge. Burn for no more than 3–4 hours at a time. Keep away from drafts, children and pets.</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>Usually 3–7 business days; the final delivery estimate is shared with your order confirmation.</t>
+        </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
+          <t>Shipping cost is separate and is calculated and shared with you at payment.</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>This product cannot be returned unless the wrong product or a defective product is received.</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>Gulab Ki Chitthi Signature Ritual, Gulab Ki Chitthi, Gulab Ki Chitthi candle, handcrafted signature ritual, soy wax candle India, Indian fragrance candle, handmade candle India, Mysaa Rituals, gifting India</t>
+        </is>
+      </c>
+      <c r="Y2" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AB2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
           <t>assets/catalogue/gulab-ki-chitthi/hero-jar-candle/01-cover.jpg</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
+      <c r="AD2" t="inlineStr">
         <is>
           <t>assets/catalogue/gulab-ki-chitthi/hero-jar-candle/02-detail.jpg</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr">
+      <c r="AE2" t="inlineStr">
         <is>
           <t>assets/catalogue/gulab-ki-chitthi/hero-jar-candle/03-lifestyle.jpg</t>
         </is>
@@ -854,11 +942,13 @@
           <t>weddings-return-gifts</t>
         </is>
       </c>
+      <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr">
         <is>
           <t>120 ml</t>
         </is>
       </c>
+      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
           <t>Natural soy wax, cotton wick, phthalate-free fragrance oils</t>
@@ -871,7 +961,7 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Gulab Ki Chitthi in our everyday ritual.</t>
+          <t>Gulab Ki Chitthi · Everyday Ritual. A fragrance that feels like receiving an old handwritten letter carrying the scent of roses.</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
@@ -879,29 +969,64 @@
           <t>A Mysaa Rituals everyday ritual in the Gulab Ki Chitthi fragrance. Made for gifting, rituals and everyday moments.</t>
         </is>
       </c>
-      <c r="R3" t="b">
-        <v>0</v>
-      </c>
-      <c r="S3" t="b">
-        <v>0</v>
-      </c>
-      <c r="T3" t="b">
-        <v>1</v>
-      </c>
-      <c r="U3" t="b">
-        <v>1</v>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>Gulab Ki Chitthi Everyday Ritual is a handcrafted everyday ritual scented with Gulab Ki Chitthi. A fragrance that feels like receiving an old handwritten letter carrying the scent of roses. Made with natural soy wax, cotton wick(s) and phthalate-free fragrance oils, it is designed for slow everyday rituals, meaningful gifting and fragrance-led spaces.</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>Approx. 20–25 hours</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Trim the wick to about 5 mm before each burn. On the first burn, allow the wax pool to reach the edge. Burn for no more than 3–4 hours at a time. Keep away from drafts, children and pets.</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Usually 3–7 business days; the final delivery estimate is shared with your order confirmation.</t>
+        </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
+          <t>Shipping cost is separate and is calculated and shared with you at payment.</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>This product cannot be returned unless the wrong product or a defective product is received.</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>Gulab Ki Chitthi Everyday Ritual, Gulab Ki Chitthi, Gulab Ki Chitthi candle, handcrafted everyday ritual, soy wax candle India, Indian fragrance candle, handmade candle India, Mysaa Rituals, gifting India</t>
+        </is>
+      </c>
+      <c r="Y3" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA3" t="b">
+        <v>1</v>
+      </c>
+      <c r="AB3" t="b">
+        <v>1</v>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
           <t>assets/catalogue/gulab-ki-chitthi/wide-jar-candle/01-cover.jpg</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
+      <c r="AD3" t="inlineStr">
         <is>
           <t>assets/catalogue/gulab-ki-chitthi/wide-jar-candle/02-detail.jpg</t>
         </is>
       </c>
-      <c r="X3" t="inlineStr">
+      <c r="AE3" t="inlineStr">
         <is>
           <t>assets/catalogue/gulab-ki-chitthi/wide-jar-candle/03-lifestyle.jpg</t>
         </is>
@@ -946,11 +1071,13 @@
           <t>weddings-return-gifts</t>
         </is>
       </c>
+      <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr">
         <is>
           <t>60 ml</t>
         </is>
       </c>
+      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr">
         <is>
           <t>Natural soy wax, cotton wick, phthalate-free fragrance oils</t>
@@ -963,7 +1090,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Gulab Ki Chitthi in our mini ritual.</t>
+          <t>Gulab Ki Chitthi · Mini Ritual. A fragrance that feels like receiving an old handwritten letter carrying the scent of roses.</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -971,29 +1098,64 @@
           <t>A Mysaa Rituals mini ritual in the Gulab Ki Chitthi fragrance. Made for gifting, rituals and everyday moments.</t>
         </is>
       </c>
-      <c r="R4" t="b">
-        <v>0</v>
-      </c>
-      <c r="S4" t="b">
-        <v>0</v>
-      </c>
-      <c r="T4" t="b">
-        <v>1</v>
-      </c>
-      <c r="U4" t="b">
-        <v>1</v>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>Gulab Ki Chitthi Mini Ritual is a handcrafted mini ritual scented with Gulab Ki Chitthi. A fragrance that feels like receiving an old handwritten letter carrying the scent of roses. Made with natural soy wax, cotton wick(s) and phthalate-free fragrance oils, it is designed for slow everyday rituals, meaningful gifting and fragrance-led spaces.</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>Approx. 10–15 hours</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Trim the wick to about 5 mm before each burn. On the first burn, allow the wax pool to reach the edge. Burn for no more than 3–4 hours at a time. Keep away from drafts, children and pets.</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Usually 3–7 business days; the final delivery estimate is shared with your order confirmation.</t>
+        </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
+          <t>Shipping cost is separate and is calculated and shared with you at payment.</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>This product cannot be returned unless the wrong product or a defective product is received.</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>Gulab Ki Chitthi Mini Ritual, Gulab Ki Chitthi, Gulab Ki Chitthi candle, handcrafted mini ritual, soy wax candle India, Indian fragrance candle, handmade candle India, Mysaa Rituals, gifting India</t>
+        </is>
+      </c>
+      <c r="Y4" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA4" t="b">
+        <v>1</v>
+      </c>
+      <c r="AB4" t="b">
+        <v>1</v>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
           <t>assets/catalogue/gulab-ki-chitthi/shot-glass-candle/01-cover.jpg</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr">
+      <c r="AD4" t="inlineStr">
         <is>
           <t>assets/catalogue/gulab-ki-chitthi/shot-glass-candle/02-detail.jpg</t>
         </is>
       </c>
-      <c r="X4" t="inlineStr">
+      <c r="AE4" t="inlineStr">
         <is>
           <t>assets/catalogue/gulab-ki-chitthi/shot-glass-candle/03-lifestyle.jpg</t>
         </is>
@@ -1042,11 +1204,13 @@
           <t>weddings-return-gifts</t>
         </is>
       </c>
+      <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr">
         <is>
           <t>Combo</t>
         </is>
       </c>
+      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr">
         <is>
           <t>Natural soy wax, cotton wick, phthalate-free fragrance oils</t>
@@ -1059,7 +1223,7 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Gulab Ki Chitthi in our wax sachet combo.</t>
+          <t>Gulab Ki Chitthi · Wax Sachet Combo. A fragrance that feels like receiving an old handwritten letter carrying the scent of roses.</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
@@ -1067,29 +1231,64 @@
           <t>A Mysaa Rituals wax sachet combo in the Gulab Ki Chitthi fragrance. Made for gifting, rituals and everyday moments.</t>
         </is>
       </c>
-      <c r="R5" t="b">
-        <v>0</v>
-      </c>
-      <c r="S5" t="b">
-        <v>0</v>
-      </c>
-      <c r="T5" t="b">
-        <v>1</v>
-      </c>
-      <c r="U5" t="b">
-        <v>1</v>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>Gulab Ki Chitthi wax sachet combo from Mysaa Rituals, made with natural soy wax and fragrance oils. A fragrance that feels like receiving an old handwritten letter carrying the scent of roses. It is a flame-free way to bring the fragrance into your space and is suited to gifting, wardrobes, drawers or wax-warming rituals.</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>Not applicable — designed to be warmed, not burned</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Place a wax sachet in a suitable wax warmer and follow the warmer manufacturer's instructions. Never place wax melts directly on a flame.</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Usually 3–7 business days; the final delivery estimate is shared with your order confirmation.</t>
+        </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
+          <t>Shipping cost is separate and is calculated and shared with you at payment.</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>This product cannot be returned unless the wrong product or a defective product is received.</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>Gulab Ki Chitthi Wax Sachet Combo, Gulab Ki Chitthi, Gulab Ki Chitthi candle, handcrafted wax sachet combo, soy wax candle India, Indian fragrance candle, handmade candle India, Mysaa Rituals, gifting India</t>
+        </is>
+      </c>
+      <c r="Y5" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA5" t="b">
+        <v>1</v>
+      </c>
+      <c r="AB5" t="b">
+        <v>1</v>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
           <t>assets/catalogue/gulab-ki-chitthi/wax-melts/01-cover.jpg</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr">
+      <c r="AD5" t="inlineStr">
         <is>
           <t>assets/catalogue/gulab-ki-chitthi/wax-melts/02-detail.jpg</t>
         </is>
       </c>
-      <c r="X5" t="inlineStr">
+      <c r="AE5" t="inlineStr">
         <is>
           <t>assets/catalogue/gulab-ki-chitthi/wax-melts/03-lifestyle.jpg</t>
         </is>
@@ -1134,11 +1333,13 @@
           <t>weddings-return-gifts</t>
         </is>
       </c>
+      <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr">
         <is>
           <t>Curated set</t>
         </is>
       </c>
+      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr">
         <is>
           <t>Curated Mysaa Rituals gifting selection</t>
@@ -1151,7 +1352,7 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Gulab Ki Chitthi in our gift hamper.</t>
+          <t>Gulab Ki Chitthi · Gift Hampers. A fragrance that feels like receiving an old handwritten letter carrying the scent of roses.</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
@@ -1159,29 +1360,64 @@
           <t>A Mysaa Rituals gift hamper in the Gulab Ki Chitthi fragrance. Made for gifting, rituals and everyday moments.</t>
         </is>
       </c>
-      <c r="R6" t="b">
-        <v>0</v>
-      </c>
-      <c r="S6" t="b">
-        <v>0</v>
-      </c>
-      <c r="T6" t="b">
-        <v>1</v>
-      </c>
-      <c r="U6" t="b">
-        <v>1</v>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>Gulab Ki Chitthi gift hamper from Mysaa Rituals — a curated gifting selection built around the Gulab Ki Chitthi fragrance. A fragrance that feels like receiving an old handwritten letter carrying the scent of roses. Designed for birthdays, weddings, festivals, return gifts and thoughtful personal gifting.</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>Varies by candle included in the hamper</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Follow the care instructions for each candle included in your hamper.</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Usually 3–7 business days; the final delivery estimate is shared with your order confirmation.</t>
+        </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
+          <t>Shipping cost is separate and is calculated and shared with you at payment.</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>This product cannot be returned unless the wrong product or a defective product is received.</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>Gulab Ki Chitthi Gift Hamper, Gulab Ki Chitthi, Gulab Ki Chitthi candle, handcrafted gift hampers, soy wax candle India, Indian fragrance candle, handmade candle India, Mysaa Rituals, gifting India, gift hamper India, wedding return gifts, festive gifts</t>
+        </is>
+      </c>
+      <c r="Y6" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA6" t="b">
+        <v>1</v>
+      </c>
+      <c r="AB6" t="b">
+        <v>1</v>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
           <t>assets/catalogue/gulab-ki-chitthi/gift-hampers/01-cover.jpg</t>
         </is>
       </c>
-      <c r="W6" t="inlineStr">
+      <c r="AD6" t="inlineStr">
         <is>
           <t>assets/catalogue/gulab-ki-chitthi/gift-hampers/02-detail.jpg</t>
         </is>
       </c>
-      <c r="X6" t="inlineStr">
+      <c r="AE6" t="inlineStr">
         <is>
           <t>assets/catalogue/gulab-ki-chitthi/gift-hampers/03-lifestyle.jpg</t>
         </is>
@@ -1226,11 +1462,13 @@
           <t>festivals-celebrations</t>
         </is>
       </c>
+      <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr">
         <is>
           <t>220 ml</t>
         </is>
       </c>
+      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr">
         <is>
           <t>Natural soy wax, cotton wick, phthalate-free fragrance oils</t>
@@ -1243,7 +1481,7 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Dhoop &amp; Chandan in our signature ritual.</t>
+          <t>Dhoop &amp; Chandan · Signature Ritual. A warm, grounding fragrance inspired by the familiar aroma of sandalwood and dhoop.</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
@@ -1251,29 +1489,64 @@
           <t>A Mysaa Rituals signature ritual in the Dhoop &amp; Chandan fragrance. Made for gifting, rituals and everyday moments.</t>
         </is>
       </c>
-      <c r="R7" t="b">
-        <v>0</v>
-      </c>
-      <c r="S7" t="b">
-        <v>0</v>
-      </c>
-      <c r="T7" t="b">
-        <v>1</v>
-      </c>
-      <c r="U7" t="b">
-        <v>1</v>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>Dhoop &amp; Chandan Signature Ritual is a handcrafted signature ritual scented with Dhoop &amp; Chandan. A warm, grounding fragrance inspired by the familiar aroma of sandalwood and dhoop. Made with natural soy wax, cotton wick(s) and phthalate-free fragrance oils, it is designed for slow everyday rituals, meaningful gifting and fragrance-led spaces.</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>Approx. 35–45 hours</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Trim the wick to about 5 mm before each burn. On the first burn, allow the wax pool to reach the edge. Burn for no more than 3–4 hours at a time. Keep away from drafts, children and pets.</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Usually 3–7 business days; the final delivery estimate is shared with your order confirmation.</t>
+        </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
+          <t>Shipping cost is separate and is calculated and shared with you at payment.</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>This product cannot be returned unless the wrong product or a defective product is received.</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>Dhoop &amp; Chandan Signature Ritual, Dhoop &amp; Chandan, Dhoop &amp; Chandan candle, handcrafted signature ritual, soy wax candle India, Indian fragrance candle, handmade candle India, Mysaa Rituals, gifting India</t>
+        </is>
+      </c>
+      <c r="Y7" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA7" t="b">
+        <v>1</v>
+      </c>
+      <c r="AB7" t="b">
+        <v>1</v>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
           <t>assets/catalogue/dhoop-chandan/hero-jar-candle/01-cover.jpg</t>
         </is>
       </c>
-      <c r="W7" t="inlineStr">
+      <c r="AD7" t="inlineStr">
         <is>
           <t>assets/catalogue/dhoop-chandan/hero-jar-candle/02-detail.jpg</t>
         </is>
       </c>
-      <c r="X7" t="inlineStr">
+      <c r="AE7" t="inlineStr">
         <is>
           <t>assets/catalogue/dhoop-chandan/hero-jar-candle/03-lifestyle.jpg</t>
         </is>
@@ -1318,11 +1591,13 @@
           <t>festivals-celebrations</t>
         </is>
       </c>
+      <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr">
         <is>
           <t>120 ml</t>
         </is>
       </c>
+      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr">
         <is>
           <t>Natural soy wax, cotton wick, phthalate-free fragrance oils</t>
@@ -1335,7 +1610,7 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Dhoop &amp; Chandan in our everyday ritual.</t>
+          <t>Dhoop &amp; Chandan · Everyday Ritual. A warm, grounding fragrance inspired by the familiar aroma of sandalwood and dhoop.</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
@@ -1343,29 +1618,64 @@
           <t>A Mysaa Rituals everyday ritual in the Dhoop &amp; Chandan fragrance. Made for gifting, rituals and everyday moments.</t>
         </is>
       </c>
-      <c r="R8" t="b">
-        <v>0</v>
-      </c>
-      <c r="S8" t="b">
-        <v>0</v>
-      </c>
-      <c r="T8" t="b">
-        <v>1</v>
-      </c>
-      <c r="U8" t="b">
-        <v>1</v>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>Dhoop &amp; Chandan Everyday Ritual is a handcrafted everyday ritual scented with Dhoop &amp; Chandan. A warm, grounding fragrance inspired by the familiar aroma of sandalwood and dhoop. Made with natural soy wax, cotton wick(s) and phthalate-free fragrance oils, it is designed for slow everyday rituals, meaningful gifting and fragrance-led spaces.</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>Approx. 20–25 hours</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Trim the wick to about 5 mm before each burn. On the first burn, allow the wax pool to reach the edge. Burn for no more than 3–4 hours at a time. Keep away from drafts, children and pets.</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Usually 3–7 business days; the final delivery estimate is shared with your order confirmation.</t>
+        </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
+          <t>Shipping cost is separate and is calculated and shared with you at payment.</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>This product cannot be returned unless the wrong product or a defective product is received.</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>Dhoop &amp; Chandan Everyday Ritual, Dhoop &amp; Chandan, Dhoop &amp; Chandan candle, handcrafted everyday ritual, soy wax candle India, Indian fragrance candle, handmade candle India, Mysaa Rituals, gifting India</t>
+        </is>
+      </c>
+      <c r="Y8" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA8" t="b">
+        <v>1</v>
+      </c>
+      <c r="AB8" t="b">
+        <v>1</v>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
           <t>assets/catalogue/dhoop-chandan/wide-jar-candle/01-cover.jpg</t>
         </is>
       </c>
-      <c r="W8" t="inlineStr">
+      <c r="AD8" t="inlineStr">
         <is>
           <t>assets/catalogue/dhoop-chandan/wide-jar-candle/02-detail.jpg</t>
         </is>
       </c>
-      <c r="X8" t="inlineStr">
+      <c r="AE8" t="inlineStr">
         <is>
           <t>assets/catalogue/dhoop-chandan/wide-jar-candle/03-lifestyle.jpg</t>
         </is>
@@ -1410,11 +1720,13 @@
           <t>festivals-celebrations</t>
         </is>
       </c>
+      <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr">
         <is>
           <t>60 ml</t>
         </is>
       </c>
+      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr">
         <is>
           <t>Natural soy wax, cotton wick, phthalate-free fragrance oils</t>
@@ -1427,7 +1739,7 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Dhoop &amp; Chandan in our mini ritual.</t>
+          <t>Dhoop &amp; Chandan · Mini Ritual. A warm, grounding fragrance inspired by the familiar aroma of sandalwood and dhoop.</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
@@ -1435,29 +1747,64 @@
           <t>A Mysaa Rituals mini ritual in the Dhoop &amp; Chandan fragrance. Made for gifting, rituals and everyday moments.</t>
         </is>
       </c>
-      <c r="R9" t="b">
-        <v>0</v>
-      </c>
-      <c r="S9" t="b">
-        <v>0</v>
-      </c>
-      <c r="T9" t="b">
-        <v>1</v>
-      </c>
-      <c r="U9" t="b">
-        <v>1</v>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>Dhoop &amp; Chandan Mini Ritual is a handcrafted mini ritual scented with Dhoop &amp; Chandan. A warm, grounding fragrance inspired by the familiar aroma of sandalwood and dhoop. Made with natural soy wax, cotton wick(s) and phthalate-free fragrance oils, it is designed for slow everyday rituals, meaningful gifting and fragrance-led spaces.</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>Approx. 10–15 hours</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Trim the wick to about 5 mm before each burn. On the first burn, allow the wax pool to reach the edge. Burn for no more than 3–4 hours at a time. Keep away from drafts, children and pets.</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Usually 3–7 business days; the final delivery estimate is shared with your order confirmation.</t>
+        </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
+          <t>Shipping cost is separate and is calculated and shared with you at payment.</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>This product cannot be returned unless the wrong product or a defective product is received.</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>Dhoop &amp; Chandan Mini Ritual, Dhoop &amp; Chandan, Dhoop &amp; Chandan candle, handcrafted mini ritual, soy wax candle India, Indian fragrance candle, handmade candle India, Mysaa Rituals, gifting India</t>
+        </is>
+      </c>
+      <c r="Y9" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA9" t="b">
+        <v>1</v>
+      </c>
+      <c r="AB9" t="b">
+        <v>1</v>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
           <t>assets/catalogue/dhoop-chandan/shot-glass-candle/01-cover.jpg</t>
         </is>
       </c>
-      <c r="W9" t="inlineStr">
+      <c r="AD9" t="inlineStr">
         <is>
           <t>assets/catalogue/dhoop-chandan/shot-glass-candle/02-detail.jpg</t>
         </is>
       </c>
-      <c r="X9" t="inlineStr">
+      <c r="AE9" t="inlineStr">
         <is>
           <t>assets/catalogue/dhoop-chandan/shot-glass-candle/03-lifestyle.jpg</t>
         </is>
@@ -1506,11 +1853,13 @@
           <t>festivals-celebrations</t>
         </is>
       </c>
+      <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr">
         <is>
           <t>Combo</t>
         </is>
       </c>
+      <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr">
         <is>
           <t>Natural soy wax, cotton wick, phthalate-free fragrance oils</t>
@@ -1523,7 +1872,7 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Dhoop &amp; Chandan in our wax sachet combo.</t>
+          <t>Dhoop &amp; Chandan · Wax Sachet Combo. A warm, grounding fragrance inspired by the familiar aroma of sandalwood and dhoop.</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
@@ -1531,29 +1880,64 @@
           <t>A Mysaa Rituals wax sachet combo in the Dhoop &amp; Chandan fragrance. Made for gifting, rituals and everyday moments.</t>
         </is>
       </c>
-      <c r="R10" t="b">
-        <v>0</v>
-      </c>
-      <c r="S10" t="b">
-        <v>0</v>
-      </c>
-      <c r="T10" t="b">
-        <v>1</v>
-      </c>
-      <c r="U10" t="b">
-        <v>1</v>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>Dhoop &amp; Chandan wax sachet combo from Mysaa Rituals, made with natural soy wax and fragrance oils. A warm, grounding fragrance inspired by the familiar aroma of sandalwood and dhoop. It is a flame-free way to bring the fragrance into your space and is suited to gifting, wardrobes, drawers or wax-warming rituals.</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>Not applicable — designed to be warmed, not burned</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Place a wax sachet in a suitable wax warmer and follow the warmer manufacturer's instructions. Never place wax melts directly on a flame.</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Usually 3–7 business days; the final delivery estimate is shared with your order confirmation.</t>
+        </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
+          <t>Shipping cost is separate and is calculated and shared with you at payment.</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>This product cannot be returned unless the wrong product or a defective product is received.</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>Dhoop &amp; Chandan Wax Sachet Combo, Dhoop &amp; Chandan, Dhoop &amp; Chandan candle, handcrafted wax sachet combo, soy wax candle India, Indian fragrance candle, handmade candle India, Mysaa Rituals, gifting India</t>
+        </is>
+      </c>
+      <c r="Y10" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA10" t="b">
+        <v>1</v>
+      </c>
+      <c r="AB10" t="b">
+        <v>1</v>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
           <t>assets/catalogue/dhoop-chandan/wax-melts/01-cover.jpg</t>
         </is>
       </c>
-      <c r="W10" t="inlineStr">
+      <c r="AD10" t="inlineStr">
         <is>
           <t>assets/catalogue/dhoop-chandan/wax-melts/02-detail.jpg</t>
         </is>
       </c>
-      <c r="X10" t="inlineStr">
+      <c r="AE10" t="inlineStr">
         <is>
           <t>assets/catalogue/dhoop-chandan/wax-melts/03-lifestyle.jpg</t>
         </is>
@@ -1598,11 +1982,13 @@
           <t>festivals-celebrations</t>
         </is>
       </c>
+      <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr">
         <is>
           <t>Curated set</t>
         </is>
       </c>
+      <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr">
         <is>
           <t>Curated Mysaa Rituals gifting selection</t>
@@ -1615,7 +2001,7 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Dhoop &amp; Chandan in our gift hamper.</t>
+          <t>Dhoop &amp; Chandan · Gift Hampers. A warm, grounding fragrance inspired by the familiar aroma of sandalwood and dhoop.</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
@@ -1623,29 +2009,64 @@
           <t>A Mysaa Rituals gift hamper in the Dhoop &amp; Chandan fragrance. Made for gifting, rituals and everyday moments.</t>
         </is>
       </c>
-      <c r="R11" t="b">
-        <v>0</v>
-      </c>
-      <c r="S11" t="b">
-        <v>0</v>
-      </c>
-      <c r="T11" t="b">
-        <v>1</v>
-      </c>
-      <c r="U11" t="b">
-        <v>1</v>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>Dhoop &amp; Chandan gift hamper from Mysaa Rituals — a curated gifting selection built around the Dhoop &amp; Chandan fragrance. A warm, grounding fragrance inspired by the familiar aroma of sandalwood and dhoop. Designed for birthdays, weddings, festivals, return gifts and thoughtful personal gifting.</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>Varies by candle included in the hamper</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Follow the care instructions for each candle included in your hamper.</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Usually 3–7 business days; the final delivery estimate is shared with your order confirmation.</t>
+        </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
+          <t>Shipping cost is separate and is calculated and shared with you at payment.</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>This product cannot be returned unless the wrong product or a defective product is received.</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>Dhoop &amp; Chandan Gift Hamper, Dhoop &amp; Chandan, Dhoop &amp; Chandan candle, handcrafted gift hampers, soy wax candle India, Indian fragrance candle, handmade candle India, Mysaa Rituals, gifting India, gift hamper India, wedding return gifts, festive gifts</t>
+        </is>
+      </c>
+      <c r="Y11" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA11" t="b">
+        <v>1</v>
+      </c>
+      <c r="AB11" t="b">
+        <v>1</v>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
           <t>assets/catalogue/dhoop-chandan/gift-hampers/01-cover.jpg</t>
         </is>
       </c>
-      <c r="W11" t="inlineStr">
+      <c r="AD11" t="inlineStr">
         <is>
           <t>assets/catalogue/dhoop-chandan/gift-hampers/02-detail.jpg</t>
         </is>
       </c>
-      <c r="X11" t="inlineStr">
+      <c r="AE11" t="inlineStr">
         <is>
           <t>assets/catalogue/dhoop-chandan/gift-hampers/03-lifestyle.jpg</t>
         </is>
@@ -1690,11 +2111,13 @@
           <t>weddings-return-gifts</t>
         </is>
       </c>
+      <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr">
         <is>
           <t>220 ml</t>
         </is>
       </c>
+      <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr">
         <is>
           <t>Natural soy wax, cotton wick, phthalate-free fragrance oils</t>
@@ -1707,7 +2130,7 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Gajre Ka Shringar in our signature ritual.</t>
+          <t>Gajre Ka Shringar · Signature Ritual. Inspired by the fragrance of fresh gajras and the timeless beauty of jasmine.</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
@@ -1715,29 +2138,64 @@
           <t>A Mysaa Rituals signature ritual in the Gajre Ka Shringar fragrance. Made for gifting, rituals and everyday moments.</t>
         </is>
       </c>
-      <c r="R12" t="b">
-        <v>0</v>
-      </c>
-      <c r="S12" t="b">
-        <v>0</v>
-      </c>
-      <c r="T12" t="b">
-        <v>1</v>
-      </c>
-      <c r="U12" t="b">
-        <v>1</v>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>Gajre Ka Shringar Signature Ritual is a handcrafted signature ritual scented with Gajre Ka Shringar. Inspired by the fragrance of fresh gajras and the timeless beauty of jasmine. Made with natural soy wax, cotton wick(s) and phthalate-free fragrance oils, it is designed for slow everyday rituals, meaningful gifting and fragrance-led spaces.</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>Approx. 35–45 hours</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Trim the wick to about 5 mm before each burn. On the first burn, allow the wax pool to reach the edge. Burn for no more than 3–4 hours at a time. Keep away from drafts, children and pets.</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Usually 3–7 business days; the final delivery estimate is shared with your order confirmation.</t>
+        </is>
       </c>
       <c r="V12" t="inlineStr">
         <is>
+          <t>Shipping cost is separate and is calculated and shared with you at payment.</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>This product cannot be returned unless the wrong product or a defective product is received.</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>Gajre Ka Shringar Signature Ritual, Gajre Ka Shringar, Gajre Ka Shringar candle, handcrafted signature ritual, soy wax candle India, Indian fragrance candle, handmade candle India, Mysaa Rituals, gifting India</t>
+        </is>
+      </c>
+      <c r="Y12" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA12" t="b">
+        <v>1</v>
+      </c>
+      <c r="AB12" t="b">
+        <v>1</v>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
           <t>assets/catalogue/gajre-ka-shringar/hero-jar-candle/01-cover.jpg</t>
         </is>
       </c>
-      <c r="W12" t="inlineStr">
+      <c r="AD12" t="inlineStr">
         <is>
           <t>assets/catalogue/gajre-ka-shringar/hero-jar-candle/02-detail.jpg</t>
         </is>
       </c>
-      <c r="X12" t="inlineStr">
+      <c r="AE12" t="inlineStr">
         <is>
           <t>assets/catalogue/gajre-ka-shringar/hero-jar-candle/03-lifestyle.jpg</t>
         </is>
@@ -1782,11 +2240,13 @@
           <t>weddings-return-gifts</t>
         </is>
       </c>
+      <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr">
         <is>
           <t>120 ml</t>
         </is>
       </c>
+      <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr">
         <is>
           <t>Natural soy wax, cotton wick, phthalate-free fragrance oils</t>
@@ -1799,7 +2259,7 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Gajre Ka Shringar in our everyday ritual.</t>
+          <t>Gajre Ka Shringar · Everyday Ritual. Inspired by the fragrance of fresh gajras and the timeless beauty of jasmine.</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
@@ -1807,29 +2267,64 @@
           <t>A Mysaa Rituals everyday ritual in the Gajre Ka Shringar fragrance. Made for gifting, rituals and everyday moments.</t>
         </is>
       </c>
-      <c r="R13" t="b">
-        <v>0</v>
-      </c>
-      <c r="S13" t="b">
-        <v>0</v>
-      </c>
-      <c r="T13" t="b">
-        <v>1</v>
-      </c>
-      <c r="U13" t="b">
-        <v>1</v>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>Gajre Ka Shringar Everyday Ritual is a handcrafted everyday ritual scented with Gajre Ka Shringar. Inspired by the fragrance of fresh gajras and the timeless beauty of jasmine. Made with natural soy wax, cotton wick(s) and phthalate-free fragrance oils, it is designed for slow everyday rituals, meaningful gifting and fragrance-led spaces.</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>Approx. 20–25 hours</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Trim the wick to about 5 mm before each burn. On the first burn, allow the wax pool to reach the edge. Burn for no more than 3–4 hours at a time. Keep away from drafts, children and pets.</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Usually 3–7 business days; the final delivery estimate is shared with your order confirmation.</t>
+        </is>
       </c>
       <c r="V13" t="inlineStr">
         <is>
+          <t>Shipping cost is separate and is calculated and shared with you at payment.</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>This product cannot be returned unless the wrong product or a defective product is received.</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>Gajre Ka Shringar Everyday Ritual, Gajre Ka Shringar, Gajre Ka Shringar candle, handcrafted everyday ritual, soy wax candle India, Indian fragrance candle, handmade candle India, Mysaa Rituals, gifting India</t>
+        </is>
+      </c>
+      <c r="Y13" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA13" t="b">
+        <v>1</v>
+      </c>
+      <c r="AB13" t="b">
+        <v>1</v>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
           <t>assets/catalogue/gajre-ka-shringar/wide-jar-candle/01-cover.jpg</t>
         </is>
       </c>
-      <c r="W13" t="inlineStr">
+      <c r="AD13" t="inlineStr">
         <is>
           <t>assets/catalogue/gajre-ka-shringar/wide-jar-candle/02-detail.jpg</t>
         </is>
       </c>
-      <c r="X13" t="inlineStr">
+      <c r="AE13" t="inlineStr">
         <is>
           <t>assets/catalogue/gajre-ka-shringar/wide-jar-candle/03-lifestyle.jpg</t>
         </is>
@@ -1874,11 +2369,13 @@
           <t>weddings-return-gifts</t>
         </is>
       </c>
+      <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr">
         <is>
           <t>60 ml</t>
         </is>
       </c>
+      <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr">
         <is>
           <t>Natural soy wax, cotton wick, phthalate-free fragrance oils</t>
@@ -1891,7 +2388,7 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Gajre Ka Shringar in our mini ritual.</t>
+          <t>Gajre Ka Shringar · Mini Ritual. Inspired by the fragrance of fresh gajras and the timeless beauty of jasmine.</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
@@ -1899,29 +2396,64 @@
           <t>A Mysaa Rituals mini ritual in the Gajre Ka Shringar fragrance. Made for gifting, rituals and everyday moments.</t>
         </is>
       </c>
-      <c r="R14" t="b">
-        <v>0</v>
-      </c>
-      <c r="S14" t="b">
-        <v>0</v>
-      </c>
-      <c r="T14" t="b">
-        <v>1</v>
-      </c>
-      <c r="U14" t="b">
-        <v>1</v>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>Gajre Ka Shringar Mini Ritual is a handcrafted mini ritual scented with Gajre Ka Shringar. Inspired by the fragrance of fresh gajras and the timeless beauty of jasmine. Made with natural soy wax, cotton wick(s) and phthalate-free fragrance oils, it is designed for slow everyday rituals, meaningful gifting and fragrance-led spaces.</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>Approx. 10–15 hours</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Trim the wick to about 5 mm before each burn. On the first burn, allow the wax pool to reach the edge. Burn for no more than 3–4 hours at a time. Keep away from drafts, children and pets.</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Usually 3–7 business days; the final delivery estimate is shared with your order confirmation.</t>
+        </is>
       </c>
       <c r="V14" t="inlineStr">
         <is>
+          <t>Shipping cost is separate and is calculated and shared with you at payment.</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>This product cannot be returned unless the wrong product or a defective product is received.</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>Gajre Ka Shringar Mini Ritual, Gajre Ka Shringar, Gajre Ka Shringar candle, handcrafted mini ritual, soy wax candle India, Indian fragrance candle, handmade candle India, Mysaa Rituals, gifting India</t>
+        </is>
+      </c>
+      <c r="Y14" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA14" t="b">
+        <v>1</v>
+      </c>
+      <c r="AB14" t="b">
+        <v>1</v>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
           <t>assets/catalogue/gajre-ka-shringar/shot-glass-candle/01-cover.jpg</t>
         </is>
       </c>
-      <c r="W14" t="inlineStr">
+      <c r="AD14" t="inlineStr">
         <is>
           <t>assets/catalogue/gajre-ka-shringar/shot-glass-candle/02-detail.jpg</t>
         </is>
       </c>
-      <c r="X14" t="inlineStr">
+      <c r="AE14" t="inlineStr">
         <is>
           <t>assets/catalogue/gajre-ka-shringar/shot-glass-candle/03-lifestyle.jpg</t>
         </is>
@@ -1970,11 +2502,13 @@
           <t>weddings-return-gifts</t>
         </is>
       </c>
+      <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr">
         <is>
           <t>Combo</t>
         </is>
       </c>
+      <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr">
         <is>
           <t>Natural soy wax, cotton wick, phthalate-free fragrance oils</t>
@@ -1987,7 +2521,7 @@
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Gajre Ka Shringar in our wax sachet combo.</t>
+          <t>Gajre Ka Shringar · Wax Sachet Combo. Inspired by the fragrance of fresh gajras and the timeless beauty of jasmine.</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
@@ -1995,29 +2529,64 @@
           <t>A Mysaa Rituals wax sachet combo in the Gajre Ka Shringar fragrance. Made for gifting, rituals and everyday moments.</t>
         </is>
       </c>
-      <c r="R15" t="b">
-        <v>0</v>
-      </c>
-      <c r="S15" t="b">
-        <v>0</v>
-      </c>
-      <c r="T15" t="b">
-        <v>1</v>
-      </c>
-      <c r="U15" t="b">
-        <v>1</v>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>Gajre Ka Shringar wax sachet combo from Mysaa Rituals, made with natural soy wax and fragrance oils. Inspired by the fragrance of fresh gajras and the timeless beauty of jasmine. It is a flame-free way to bring the fragrance into your space and is suited to gifting, wardrobes, drawers or wax-warming rituals.</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>Not applicable — designed to be warmed, not burned</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Place a wax sachet in a suitable wax warmer and follow the warmer manufacturer's instructions. Never place wax melts directly on a flame.</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Usually 3–7 business days; the final delivery estimate is shared with your order confirmation.</t>
+        </is>
       </c>
       <c r="V15" t="inlineStr">
         <is>
+          <t>Shipping cost is separate and is calculated and shared with you at payment.</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>This product cannot be returned unless the wrong product or a defective product is received.</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>Gajre Ka Shringar Wax Sachet Combo, Gajre Ka Shringar, Gajre Ka Shringar candle, handcrafted wax sachet combo, soy wax candle India, Indian fragrance candle, handmade candle India, Mysaa Rituals, gifting India</t>
+        </is>
+      </c>
+      <c r="Y15" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA15" t="b">
+        <v>1</v>
+      </c>
+      <c r="AB15" t="b">
+        <v>1</v>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
           <t>assets/catalogue/gajre-ka-shringar/wax-melts/01-cover.jpg</t>
         </is>
       </c>
-      <c r="W15" t="inlineStr">
+      <c r="AD15" t="inlineStr">
         <is>
           <t>assets/catalogue/gajre-ka-shringar/wax-melts/02-detail.jpg</t>
         </is>
       </c>
-      <c r="X15" t="inlineStr">
+      <c r="AE15" t="inlineStr">
         <is>
           <t>assets/catalogue/gajre-ka-shringar/wax-melts/03-lifestyle.jpg</t>
         </is>
@@ -2062,11 +2631,13 @@
           <t>weddings-return-gifts</t>
         </is>
       </c>
+      <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr">
         <is>
           <t>Curated set</t>
         </is>
       </c>
+      <c r="M16" t="inlineStr"/>
       <c r="N16" t="inlineStr">
         <is>
           <t>Curated Mysaa Rituals gifting selection</t>
@@ -2079,7 +2650,7 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Gajre Ka Shringar in our gift hamper.</t>
+          <t>Gajre Ka Shringar · Gift Hampers. Inspired by the fragrance of fresh gajras and the timeless beauty of jasmine.</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
@@ -2087,29 +2658,64 @@
           <t>A Mysaa Rituals gift hamper in the Gajre Ka Shringar fragrance. Made for gifting, rituals and everyday moments.</t>
         </is>
       </c>
-      <c r="R16" t="b">
-        <v>0</v>
-      </c>
-      <c r="S16" t="b">
-        <v>0</v>
-      </c>
-      <c r="T16" t="b">
-        <v>1</v>
-      </c>
-      <c r="U16" t="b">
-        <v>1</v>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>Gajre Ka Shringar gift hamper from Mysaa Rituals — a curated gifting selection built around the Gajre Ka Shringar fragrance. Inspired by the fragrance of fresh gajras and the timeless beauty of jasmine. Designed for birthdays, weddings, festivals, return gifts and thoughtful personal gifting.</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>Varies by candle included in the hamper</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Follow the care instructions for each candle included in your hamper.</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Usually 3–7 business days; the final delivery estimate is shared with your order confirmation.</t>
+        </is>
       </c>
       <c r="V16" t="inlineStr">
         <is>
+          <t>Shipping cost is separate and is calculated and shared with you at payment.</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>This product cannot be returned unless the wrong product or a defective product is received.</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>Gajre Ka Shringar Gift Hamper, Gajre Ka Shringar, Gajre Ka Shringar candle, handcrafted gift hampers, soy wax candle India, Indian fragrance candle, handmade candle India, Mysaa Rituals, gifting India, gift hamper India, wedding return gifts, festive gifts</t>
+        </is>
+      </c>
+      <c r="Y16" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA16" t="b">
+        <v>1</v>
+      </c>
+      <c r="AB16" t="b">
+        <v>1</v>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
           <t>assets/catalogue/gajre-ka-shringar/gift-hampers/01-cover.jpg</t>
         </is>
       </c>
-      <c r="W16" t="inlineStr">
+      <c r="AD16" t="inlineStr">
         <is>
           <t>assets/catalogue/gajre-ka-shringar/gift-hampers/02-detail.jpg</t>
         </is>
       </c>
-      <c r="X16" t="inlineStr">
+      <c r="AE16" t="inlineStr">
         <is>
           <t>assets/catalogue/gajre-ka-shringar/gift-hampers/03-lifestyle.jpg</t>
         </is>
@@ -2154,11 +2760,13 @@
           <t>festivals-celebrations</t>
         </is>
       </c>
+      <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr">
         <is>
           <t>220 ml</t>
         </is>
       </c>
+      <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr">
         <is>
           <t>Natural soy wax, cotton wick, phthalate-free fragrance oils</t>
@@ -2171,7 +2779,7 @@
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Madhuban in our signature ritual.</t>
+          <t>Madhuban · Signature Ritual. A deep floral fragrance inspired by flowers that come alive after sunset.</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
@@ -2179,29 +2787,64 @@
           <t>A Mysaa Rituals signature ritual in the Madhuban fragrance. Made for gifting, rituals and everyday moments.</t>
         </is>
       </c>
-      <c r="R17" t="b">
-        <v>0</v>
-      </c>
-      <c r="S17" t="b">
-        <v>0</v>
-      </c>
-      <c r="T17" t="b">
-        <v>1</v>
-      </c>
-      <c r="U17" t="b">
-        <v>1</v>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>Madhuban Signature Ritual is a handcrafted signature ritual scented with Madhuban. A deep floral fragrance inspired by flowers that come alive after sunset. Made with natural soy wax, cotton wick(s) and phthalate-free fragrance oils, it is designed for slow everyday rituals, meaningful gifting and fragrance-led spaces.</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>Approx. 35–45 hours</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Trim the wick to about 5 mm before each burn. On the first burn, allow the wax pool to reach the edge. Burn for no more than 3–4 hours at a time. Keep away from drafts, children and pets.</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Usually 3–7 business days; the final delivery estimate is shared with your order confirmation.</t>
+        </is>
       </c>
       <c r="V17" t="inlineStr">
         <is>
+          <t>Shipping cost is separate and is calculated and shared with you at payment.</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>This product cannot be returned unless the wrong product or a defective product is received.</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>Madhuban Signature Ritual, Madhuban, Madhuban candle, handcrafted signature ritual, soy wax candle India, Indian fragrance candle, handmade candle India, Mysaa Rituals, gifting India</t>
+        </is>
+      </c>
+      <c r="Y17" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA17" t="b">
+        <v>1</v>
+      </c>
+      <c r="AB17" t="b">
+        <v>1</v>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
           <t>assets/catalogue/madhuban/hero-jar-candle/01-cover.jpg</t>
         </is>
       </c>
-      <c r="W17" t="inlineStr">
+      <c r="AD17" t="inlineStr">
         <is>
           <t>assets/catalogue/madhuban/hero-jar-candle/02-detail.jpg</t>
         </is>
       </c>
-      <c r="X17" t="inlineStr">
+      <c r="AE17" t="inlineStr">
         <is>
           <t>assets/catalogue/madhuban/hero-jar-candle/03-lifestyle.jpg</t>
         </is>
@@ -2246,11 +2889,13 @@
           <t>festivals-celebrations</t>
         </is>
       </c>
+      <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr">
         <is>
           <t>120 ml</t>
         </is>
       </c>
+      <c r="M18" t="inlineStr"/>
       <c r="N18" t="inlineStr">
         <is>
           <t>Natural soy wax, cotton wick, phthalate-free fragrance oils</t>
@@ -2263,7 +2908,7 @@
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Madhuban in our everyday ritual.</t>
+          <t>Madhuban · Everyday Ritual. A deep floral fragrance inspired by flowers that come alive after sunset.</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
@@ -2271,29 +2916,64 @@
           <t>A Mysaa Rituals everyday ritual in the Madhuban fragrance. Made for gifting, rituals and everyday moments.</t>
         </is>
       </c>
-      <c r="R18" t="b">
-        <v>0</v>
-      </c>
-      <c r="S18" t="b">
-        <v>0</v>
-      </c>
-      <c r="T18" t="b">
-        <v>1</v>
-      </c>
-      <c r="U18" t="b">
-        <v>1</v>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>Madhuban Everyday Ritual is a handcrafted everyday ritual scented with Madhuban. A deep floral fragrance inspired by flowers that come alive after sunset. Made with natural soy wax, cotton wick(s) and phthalate-free fragrance oils, it is designed for slow everyday rituals, meaningful gifting and fragrance-led spaces.</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>Approx. 20–25 hours</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Trim the wick to about 5 mm before each burn. On the first burn, allow the wax pool to reach the edge. Burn for no more than 3–4 hours at a time. Keep away from drafts, children and pets.</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Usually 3–7 business days; the final delivery estimate is shared with your order confirmation.</t>
+        </is>
       </c>
       <c r="V18" t="inlineStr">
         <is>
+          <t>Shipping cost is separate and is calculated and shared with you at payment.</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>This product cannot be returned unless the wrong product or a defective product is received.</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>Madhuban Everyday Ritual, Madhuban, Madhuban candle, handcrafted everyday ritual, soy wax candle India, Indian fragrance candle, handmade candle India, Mysaa Rituals, gifting India</t>
+        </is>
+      </c>
+      <c r="Y18" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA18" t="b">
+        <v>1</v>
+      </c>
+      <c r="AB18" t="b">
+        <v>1</v>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
           <t>assets/catalogue/madhuban/wide-jar-candle/01-cover.jpg</t>
         </is>
       </c>
-      <c r="W18" t="inlineStr">
+      <c r="AD18" t="inlineStr">
         <is>
           <t>assets/catalogue/madhuban/wide-jar-candle/02-detail.jpg</t>
         </is>
       </c>
-      <c r="X18" t="inlineStr">
+      <c r="AE18" t="inlineStr">
         <is>
           <t>assets/catalogue/madhuban/wide-jar-candle/03-lifestyle.jpg</t>
         </is>
@@ -2338,11 +3018,13 @@
           <t>festivals-celebrations</t>
         </is>
       </c>
+      <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr">
         <is>
           <t>60 ml</t>
         </is>
       </c>
+      <c r="M19" t="inlineStr"/>
       <c r="N19" t="inlineStr">
         <is>
           <t>Natural soy wax, cotton wick, phthalate-free fragrance oils</t>
@@ -2355,7 +3037,7 @@
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Madhuban in our mini ritual.</t>
+          <t>Madhuban · Mini Ritual. A deep floral fragrance inspired by flowers that come alive after sunset.</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
@@ -2363,29 +3045,64 @@
           <t>A Mysaa Rituals mini ritual in the Madhuban fragrance. Made for gifting, rituals and everyday moments.</t>
         </is>
       </c>
-      <c r="R19" t="b">
-        <v>0</v>
-      </c>
-      <c r="S19" t="b">
-        <v>0</v>
-      </c>
-      <c r="T19" t="b">
-        <v>1</v>
-      </c>
-      <c r="U19" t="b">
-        <v>1</v>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>Madhuban Mini Ritual is a handcrafted mini ritual scented with Madhuban. A deep floral fragrance inspired by flowers that come alive after sunset. Made with natural soy wax, cotton wick(s) and phthalate-free fragrance oils, it is designed for slow everyday rituals, meaningful gifting and fragrance-led spaces.</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>Approx. 10–15 hours</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Trim the wick to about 5 mm before each burn. On the first burn, allow the wax pool to reach the edge. Burn for no more than 3–4 hours at a time. Keep away from drafts, children and pets.</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Usually 3–7 business days; the final delivery estimate is shared with your order confirmation.</t>
+        </is>
       </c>
       <c r="V19" t="inlineStr">
         <is>
+          <t>Shipping cost is separate and is calculated and shared with you at payment.</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>This product cannot be returned unless the wrong product or a defective product is received.</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>Madhuban Mini Ritual, Madhuban, Madhuban candle, handcrafted mini ritual, soy wax candle India, Indian fragrance candle, handmade candle India, Mysaa Rituals, gifting India</t>
+        </is>
+      </c>
+      <c r="Y19" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA19" t="b">
+        <v>1</v>
+      </c>
+      <c r="AB19" t="b">
+        <v>1</v>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
           <t>assets/catalogue/madhuban/shot-glass-candle/01-cover.jpg</t>
         </is>
       </c>
-      <c r="W19" t="inlineStr">
+      <c r="AD19" t="inlineStr">
         <is>
           <t>assets/catalogue/madhuban/shot-glass-candle/02-detail.jpg</t>
         </is>
       </c>
-      <c r="X19" t="inlineStr">
+      <c r="AE19" t="inlineStr">
         <is>
           <t>assets/catalogue/madhuban/shot-glass-candle/03-lifestyle.jpg</t>
         </is>
@@ -2434,11 +3151,13 @@
           <t>festivals-celebrations</t>
         </is>
       </c>
+      <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr">
         <is>
           <t>Combo</t>
         </is>
       </c>
+      <c r="M20" t="inlineStr"/>
       <c r="N20" t="inlineStr">
         <is>
           <t>Natural soy wax, cotton wick, phthalate-free fragrance oils</t>
@@ -2451,7 +3170,7 @@
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Madhuban in our wax sachet combo.</t>
+          <t>Madhuban · Wax Sachet Combo. A deep floral fragrance inspired by flowers that come alive after sunset.</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
@@ -2459,29 +3178,64 @@
           <t>A Mysaa Rituals wax sachet combo in the Madhuban fragrance. Made for gifting, rituals and everyday moments.</t>
         </is>
       </c>
-      <c r="R20" t="b">
-        <v>0</v>
-      </c>
-      <c r="S20" t="b">
-        <v>0</v>
-      </c>
-      <c r="T20" t="b">
-        <v>1</v>
-      </c>
-      <c r="U20" t="b">
-        <v>1</v>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>Madhuban wax sachet combo from Mysaa Rituals, made with natural soy wax and fragrance oils. A deep floral fragrance inspired by flowers that come alive after sunset. It is a flame-free way to bring the fragrance into your space and is suited to gifting, wardrobes, drawers or wax-warming rituals.</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>Not applicable — designed to be warmed, not burned</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Place a wax sachet in a suitable wax warmer and follow the warmer manufacturer's instructions. Never place wax melts directly on a flame.</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Usually 3–7 business days; the final delivery estimate is shared with your order confirmation.</t>
+        </is>
       </c>
       <c r="V20" t="inlineStr">
         <is>
+          <t>Shipping cost is separate and is calculated and shared with you at payment.</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>This product cannot be returned unless the wrong product or a defective product is received.</t>
+        </is>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>Madhuban Wax Sachet Combo, Madhuban, Madhuban candle, handcrafted wax sachet combo, soy wax candle India, Indian fragrance candle, handmade candle India, Mysaa Rituals, gifting India</t>
+        </is>
+      </c>
+      <c r="Y20" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA20" t="b">
+        <v>1</v>
+      </c>
+      <c r="AB20" t="b">
+        <v>1</v>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
           <t>assets/catalogue/madhuban/wax-melts/01-cover.jpg</t>
         </is>
       </c>
-      <c r="W20" t="inlineStr">
+      <c r="AD20" t="inlineStr">
         <is>
           <t>assets/catalogue/madhuban/wax-melts/02-detail.jpg</t>
         </is>
       </c>
-      <c r="X20" t="inlineStr">
+      <c r="AE20" t="inlineStr">
         <is>
           <t>assets/catalogue/madhuban/wax-melts/03-lifestyle.jpg</t>
         </is>
@@ -2526,11 +3280,13 @@
           <t>festivals-celebrations</t>
         </is>
       </c>
+      <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr">
         <is>
           <t>Curated set</t>
         </is>
       </c>
+      <c r="M21" t="inlineStr"/>
       <c r="N21" t="inlineStr">
         <is>
           <t>Curated Mysaa Rituals gifting selection</t>
@@ -2543,7 +3299,7 @@
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Madhuban in our gift hamper.</t>
+          <t>Madhuban · Gift Hampers. A deep floral fragrance inspired by flowers that come alive after sunset.</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
@@ -2551,29 +3307,64 @@
           <t>A Mysaa Rituals gift hamper in the Madhuban fragrance. Made for gifting, rituals and everyday moments.</t>
         </is>
       </c>
-      <c r="R21" t="b">
-        <v>0</v>
-      </c>
-      <c r="S21" t="b">
-        <v>0</v>
-      </c>
-      <c r="T21" t="b">
-        <v>1</v>
-      </c>
-      <c r="U21" t="b">
-        <v>1</v>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>Madhuban gift hamper from Mysaa Rituals — a curated gifting selection built around the Madhuban fragrance. A deep floral fragrance inspired by flowers that come alive after sunset. Designed for birthdays, weddings, festivals, return gifts and thoughtful personal gifting.</t>
+        </is>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>Varies by candle included in the hamper</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Follow the care instructions for each candle included in your hamper.</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Usually 3–7 business days; the final delivery estimate is shared with your order confirmation.</t>
+        </is>
       </c>
       <c r="V21" t="inlineStr">
         <is>
+          <t>Shipping cost is separate and is calculated and shared with you at payment.</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>This product cannot be returned unless the wrong product or a defective product is received.</t>
+        </is>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>Madhuban Gift Hamper, Madhuban, Madhuban candle, handcrafted gift hampers, soy wax candle India, Indian fragrance candle, handmade candle India, Mysaa Rituals, gifting India, gift hamper India, wedding return gifts, festive gifts</t>
+        </is>
+      </c>
+      <c r="Y21" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA21" t="b">
+        <v>1</v>
+      </c>
+      <c r="AB21" t="b">
+        <v>1</v>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
           <t>assets/catalogue/madhuban/gift-hampers/01-cover.jpg</t>
         </is>
       </c>
-      <c r="W21" t="inlineStr">
+      <c r="AD21" t="inlineStr">
         <is>
           <t>assets/catalogue/madhuban/gift-hampers/02-detail.jpg</t>
         </is>
       </c>
-      <c r="X21" t="inlineStr">
+      <c r="AE21" t="inlineStr">
         <is>
           <t>assets/catalogue/madhuban/gift-hampers/03-lifestyle.jpg</t>
         </is>
@@ -2618,11 +3409,13 @@
           <t>birthdays-just-because</t>
         </is>
       </c>
+      <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr">
         <is>
           <t>220 ml</t>
         </is>
       </c>
+      <c r="M22" t="inlineStr"/>
       <c r="N22" t="inlineStr">
         <is>
           <t>Natural soy wax, cotton wick, phthalate-free fragrance oils</t>
@@ -2635,7 +3428,7 @@
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Raat Ki Rani in our signature ritual.</t>
+          <t>Raat Ki Rani · Signature Ritual. An evocative night-blooming floral fragrance inspired by the queen of the night.</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
@@ -2643,29 +3436,64 @@
           <t>A Mysaa Rituals signature ritual in the Raat Ki Rani fragrance. Made for gifting, rituals and everyday moments.</t>
         </is>
       </c>
-      <c r="R22" t="b">
-        <v>0</v>
-      </c>
-      <c r="S22" t="b">
-        <v>0</v>
-      </c>
-      <c r="T22" t="b">
-        <v>1</v>
-      </c>
-      <c r="U22" t="b">
-        <v>1</v>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>Raat Ki Rani Signature Ritual is a handcrafted signature ritual scented with Raat Ki Rani. An evocative night-blooming floral fragrance inspired by the queen of the night. Made with natural soy wax, cotton wick(s) and phthalate-free fragrance oils, it is designed for slow everyday rituals, meaningful gifting and fragrance-led spaces.</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>Approx. 35–45 hours</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Trim the wick to about 5 mm before each burn. On the first burn, allow the wax pool to reach the edge. Burn for no more than 3–4 hours at a time. Keep away from drafts, children and pets.</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Usually 3–7 business days; the final delivery estimate is shared with your order confirmation.</t>
+        </is>
       </c>
       <c r="V22" t="inlineStr">
         <is>
+          <t>Shipping cost is separate and is calculated and shared with you at payment.</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>This product cannot be returned unless the wrong product or a defective product is received.</t>
+        </is>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>Raat Ki Rani Signature Ritual, Raat Ki Rani, Raat Ki Rani candle, handcrafted signature ritual, soy wax candle India, Indian fragrance candle, handmade candle India, Mysaa Rituals, gifting India</t>
+        </is>
+      </c>
+      <c r="Y22" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA22" t="b">
+        <v>1</v>
+      </c>
+      <c r="AB22" t="b">
+        <v>1</v>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
           <t>assets/catalogue/raat-ki-rani/hero-jar-candle/01-cover.jpg</t>
         </is>
       </c>
-      <c r="W22" t="inlineStr">
+      <c r="AD22" t="inlineStr">
         <is>
           <t>assets/catalogue/raat-ki-rani/hero-jar-candle/02-detail.jpg</t>
         </is>
       </c>
-      <c r="X22" t="inlineStr">
+      <c r="AE22" t="inlineStr">
         <is>
           <t>assets/catalogue/raat-ki-rani/hero-jar-candle/03-lifestyle.jpg</t>
         </is>
@@ -2710,11 +3538,13 @@
           <t>birthdays-just-because</t>
         </is>
       </c>
+      <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr">
         <is>
           <t>120 ml</t>
         </is>
       </c>
+      <c r="M23" t="inlineStr"/>
       <c r="N23" t="inlineStr">
         <is>
           <t>Natural soy wax, cotton wick, phthalate-free fragrance oils</t>
@@ -2727,7 +3557,7 @@
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Raat Ki Rani in our everyday ritual.</t>
+          <t>Raat Ki Rani · Everyday Ritual. An evocative night-blooming floral fragrance inspired by the queen of the night.</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
@@ -2735,29 +3565,64 @@
           <t>A Mysaa Rituals everyday ritual in the Raat Ki Rani fragrance. Made for gifting, rituals and everyday moments.</t>
         </is>
       </c>
-      <c r="R23" t="b">
-        <v>0</v>
-      </c>
-      <c r="S23" t="b">
-        <v>0</v>
-      </c>
-      <c r="T23" t="b">
-        <v>1</v>
-      </c>
-      <c r="U23" t="b">
-        <v>1</v>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>Raat Ki Rani Everyday Ritual is a handcrafted everyday ritual scented with Raat Ki Rani. An evocative night-blooming floral fragrance inspired by the queen of the night. Made with natural soy wax, cotton wick(s) and phthalate-free fragrance oils, it is designed for slow everyday rituals, meaningful gifting and fragrance-led spaces.</t>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>Approx. 20–25 hours</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Trim the wick to about 5 mm before each burn. On the first burn, allow the wax pool to reach the edge. Burn for no more than 3–4 hours at a time. Keep away from drafts, children and pets.</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Usually 3–7 business days; the final delivery estimate is shared with your order confirmation.</t>
+        </is>
       </c>
       <c r="V23" t="inlineStr">
         <is>
+          <t>Shipping cost is separate and is calculated and shared with you at payment.</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>This product cannot be returned unless the wrong product or a defective product is received.</t>
+        </is>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>Raat Ki Rani Everyday Ritual, Raat Ki Rani, Raat Ki Rani candle, handcrafted everyday ritual, soy wax candle India, Indian fragrance candle, handmade candle India, Mysaa Rituals, gifting India</t>
+        </is>
+      </c>
+      <c r="Y23" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA23" t="b">
+        <v>1</v>
+      </c>
+      <c r="AB23" t="b">
+        <v>1</v>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
           <t>assets/catalogue/raat-ki-rani/wide-jar-candle/01-cover.jpg</t>
         </is>
       </c>
-      <c r="W23" t="inlineStr">
+      <c r="AD23" t="inlineStr">
         <is>
           <t>assets/catalogue/raat-ki-rani/wide-jar-candle/02-detail.jpg</t>
         </is>
       </c>
-      <c r="X23" t="inlineStr">
+      <c r="AE23" t="inlineStr">
         <is>
           <t>assets/catalogue/raat-ki-rani/wide-jar-candle/03-lifestyle.jpg</t>
         </is>
@@ -2802,11 +3667,13 @@
           <t>birthdays-just-because</t>
         </is>
       </c>
+      <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr">
         <is>
           <t>60 ml</t>
         </is>
       </c>
+      <c r="M24" t="inlineStr"/>
       <c r="N24" t="inlineStr">
         <is>
           <t>Natural soy wax, cotton wick, phthalate-free fragrance oils</t>
@@ -2819,7 +3686,7 @@
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Raat Ki Rani in our mini ritual.</t>
+          <t>Raat Ki Rani · Mini Ritual. An evocative night-blooming floral fragrance inspired by the queen of the night.</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
@@ -2827,29 +3694,64 @@
           <t>A Mysaa Rituals mini ritual in the Raat Ki Rani fragrance. Made for gifting, rituals and everyday moments.</t>
         </is>
       </c>
-      <c r="R24" t="b">
-        <v>0</v>
-      </c>
-      <c r="S24" t="b">
-        <v>0</v>
-      </c>
-      <c r="T24" t="b">
-        <v>1</v>
-      </c>
-      <c r="U24" t="b">
-        <v>1</v>
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>Raat Ki Rani Mini Ritual is a handcrafted mini ritual scented with Raat Ki Rani. An evocative night-blooming floral fragrance inspired by the queen of the night. Made with natural soy wax, cotton wick(s) and phthalate-free fragrance oils, it is designed for slow everyday rituals, meaningful gifting and fragrance-led spaces.</t>
+        </is>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>Approx. 10–15 hours</t>
+        </is>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Trim the wick to about 5 mm before each burn. On the first burn, allow the wax pool to reach the edge. Burn for no more than 3–4 hours at a time. Keep away from drafts, children and pets.</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Usually 3–7 business days; the final delivery estimate is shared with your order confirmation.</t>
+        </is>
       </c>
       <c r="V24" t="inlineStr">
         <is>
+          <t>Shipping cost is separate and is calculated and shared with you at payment.</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>This product cannot be returned unless the wrong product or a defective product is received.</t>
+        </is>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>Raat Ki Rani Mini Ritual, Raat Ki Rani, Raat Ki Rani candle, handcrafted mini ritual, soy wax candle India, Indian fragrance candle, handmade candle India, Mysaa Rituals, gifting India</t>
+        </is>
+      </c>
+      <c r="Y24" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA24" t="b">
+        <v>1</v>
+      </c>
+      <c r="AB24" t="b">
+        <v>1</v>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
           <t>assets/catalogue/raat-ki-rani/shot-glass-candle/01-cover.jpg</t>
         </is>
       </c>
-      <c r="W24" t="inlineStr">
+      <c r="AD24" t="inlineStr">
         <is>
           <t>assets/catalogue/raat-ki-rani/shot-glass-candle/02-detail.jpg</t>
         </is>
       </c>
-      <c r="X24" t="inlineStr">
+      <c r="AE24" t="inlineStr">
         <is>
           <t>assets/catalogue/raat-ki-rani/shot-glass-candle/03-lifestyle.jpg</t>
         </is>
@@ -2898,11 +3800,13 @@
           <t>birthdays-just-because</t>
         </is>
       </c>
+      <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr">
         <is>
           <t>Combo</t>
         </is>
       </c>
+      <c r="M25" t="inlineStr"/>
       <c r="N25" t="inlineStr">
         <is>
           <t>Natural soy wax, cotton wick, phthalate-free fragrance oils</t>
@@ -2915,7 +3819,7 @@
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Raat Ki Rani in our wax sachet combo.</t>
+          <t>Raat Ki Rani · Wax Sachet Combo. An evocative night-blooming floral fragrance inspired by the queen of the night.</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
@@ -2923,29 +3827,64 @@
           <t>A Mysaa Rituals wax sachet combo in the Raat Ki Rani fragrance. Made for gifting, rituals and everyday moments.</t>
         </is>
       </c>
-      <c r="R25" t="b">
-        <v>0</v>
-      </c>
-      <c r="S25" t="b">
-        <v>0</v>
-      </c>
-      <c r="T25" t="b">
-        <v>1</v>
-      </c>
-      <c r="U25" t="b">
-        <v>1</v>
+      <c r="R25" t="inlineStr">
+        <is>
+          <t>Raat Ki Rani wax sachet combo from Mysaa Rituals, made with natural soy wax and fragrance oils. An evocative night-blooming floral fragrance inspired by the queen of the night. It is a flame-free way to bring the fragrance into your space and is suited to gifting, wardrobes, drawers or wax-warming rituals.</t>
+        </is>
+      </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>Not applicable — designed to be warmed, not burned</t>
+        </is>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Place a wax sachet in a suitable wax warmer and follow the warmer manufacturer's instructions. Never place wax melts directly on a flame.</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Usually 3–7 business days; the final delivery estimate is shared with your order confirmation.</t>
+        </is>
       </c>
       <c r="V25" t="inlineStr">
         <is>
+          <t>Shipping cost is separate and is calculated and shared with you at payment.</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>This product cannot be returned unless the wrong product or a defective product is received.</t>
+        </is>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>Raat Ki Rani Wax Sachet Combo, Raat Ki Rani, Raat Ki Rani candle, handcrafted wax sachet combo, soy wax candle India, Indian fragrance candle, handmade candle India, Mysaa Rituals, gifting India</t>
+        </is>
+      </c>
+      <c r="Y25" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA25" t="b">
+        <v>1</v>
+      </c>
+      <c r="AB25" t="b">
+        <v>1</v>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
           <t>assets/catalogue/raat-ki-rani/wax-melts/01-cover.jpg</t>
         </is>
       </c>
-      <c r="W25" t="inlineStr">
+      <c r="AD25" t="inlineStr">
         <is>
           <t>assets/catalogue/raat-ki-rani/wax-melts/02-detail.jpg</t>
         </is>
       </c>
-      <c r="X25" t="inlineStr">
+      <c r="AE25" t="inlineStr">
         <is>
           <t>assets/catalogue/raat-ki-rani/wax-melts/03-lifestyle.jpg</t>
         </is>
@@ -2990,11 +3929,13 @@
           <t>birthdays-just-because</t>
         </is>
       </c>
+      <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr">
         <is>
           <t>Curated set</t>
         </is>
       </c>
+      <c r="M26" t="inlineStr"/>
       <c r="N26" t="inlineStr">
         <is>
           <t>Curated Mysaa Rituals gifting selection</t>
@@ -3007,7 +3948,7 @@
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Raat Ki Rani in our gift hamper.</t>
+          <t>Raat Ki Rani · Gift Hampers. An evocative night-blooming floral fragrance inspired by the queen of the night.</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
@@ -3015,29 +3956,64 @@
           <t>A Mysaa Rituals gift hamper in the Raat Ki Rani fragrance. Made for gifting, rituals and everyday moments.</t>
         </is>
       </c>
-      <c r="R26" t="b">
-        <v>0</v>
-      </c>
-      <c r="S26" t="b">
-        <v>0</v>
-      </c>
-      <c r="T26" t="b">
-        <v>1</v>
-      </c>
-      <c r="U26" t="b">
-        <v>1</v>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>Raat Ki Rani gift hamper from Mysaa Rituals — a curated gifting selection built around the Raat Ki Rani fragrance. An evocative night-blooming floral fragrance inspired by the queen of the night. Designed for birthdays, weddings, festivals, return gifts and thoughtful personal gifting.</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>Varies by candle included in the hamper</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Follow the care instructions for each candle included in your hamper.</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Usually 3–7 business days; the final delivery estimate is shared with your order confirmation.</t>
+        </is>
       </c>
       <c r="V26" t="inlineStr">
         <is>
+          <t>Shipping cost is separate and is calculated and shared with you at payment.</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>This product cannot be returned unless the wrong product or a defective product is received.</t>
+        </is>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>Raat Ki Rani Gift Hamper, Raat Ki Rani, Raat Ki Rani candle, handcrafted gift hampers, soy wax candle India, Indian fragrance candle, handmade candle India, Mysaa Rituals, gifting India, gift hamper India, wedding return gifts, festive gifts</t>
+        </is>
+      </c>
+      <c r="Y26" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA26" t="b">
+        <v>1</v>
+      </c>
+      <c r="AB26" t="b">
+        <v>1</v>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
           <t>assets/catalogue/raat-ki-rani/gift-hampers/01-cover.jpg</t>
         </is>
       </c>
-      <c r="W26" t="inlineStr">
+      <c r="AD26" t="inlineStr">
         <is>
           <t>assets/catalogue/raat-ki-rani/gift-hampers/02-detail.jpg</t>
         </is>
       </c>
-      <c r="X26" t="inlineStr">
+      <c r="AE26" t="inlineStr">
         <is>
           <t>assets/catalogue/raat-ki-rani/gift-hampers/03-lifestyle.jpg</t>
         </is>
@@ -3082,11 +4058,13 @@
           <t>birthdays-just-because</t>
         </is>
       </c>
+      <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr">
         <is>
           <t>220 ml</t>
         </is>
       </c>
+      <c r="M27" t="inlineStr"/>
       <c r="N27" t="inlineStr">
         <is>
           <t>Natural soy wax, cotton wick, phthalate-free fragrance oils</t>
@@ -3099,7 +4077,7 @@
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Saanjh in our signature ritual.</t>
+          <t>Saanjh · Signature Ritual. The warmth of an evening that lingers — creamy vanilla softens deep sandalwood.</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
@@ -3107,29 +4085,64 @@
           <t>A Mysaa Rituals signature ritual in the Saanjh fragrance — creamy vanilla softened by deep sandalwood, made for gifting, rituals and everyday moments.</t>
         </is>
       </c>
-      <c r="R27" t="b">
-        <v>0</v>
-      </c>
-      <c r="S27" t="b">
-        <v>0</v>
-      </c>
-      <c r="T27" t="b">
-        <v>1</v>
-      </c>
-      <c r="U27" t="b">
-        <v>1</v>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>Saanjh Signature Ritual is a handcrafted signature ritual scented with Saanjh. The warmth of an evening that lingers — creamy vanilla softens deep sandalwood. Made with natural soy wax, cotton wick(s) and phthalate-free fragrance oils, it is designed for slow everyday rituals, meaningful gifting and fragrance-led spaces.</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>Approx. 35–45 hours</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Trim the wick to about 5 mm before each burn. On the first burn, allow the wax pool to reach the edge. Burn for no more than 3–4 hours at a time. Keep away from drafts, children and pets.</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Usually 3–7 business days; the final delivery estimate is shared with your order confirmation.</t>
+        </is>
       </c>
       <c r="V27" t="inlineStr">
         <is>
+          <t>Shipping cost is separate and is calculated and shared with you at payment.</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>This product cannot be returned unless the wrong product or a defective product is received.</t>
+        </is>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>Saanjh Signature Ritual, Saanjh, Saanjh candle, handcrafted signature ritual, soy wax candle India, Indian fragrance candle, handmade candle India, Mysaa Rituals, gifting India</t>
+        </is>
+      </c>
+      <c r="Y27" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA27" t="b">
+        <v>1</v>
+      </c>
+      <c r="AB27" t="b">
+        <v>1</v>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
           <t>assets/catalogue/saanjh/hero-jar-candle/01-cover.jpg</t>
         </is>
       </c>
-      <c r="W27" t="inlineStr">
+      <c r="AD27" t="inlineStr">
         <is>
           <t>assets/catalogue/saanjh/hero-jar-candle/02-detail.jpg</t>
         </is>
       </c>
-      <c r="X27" t="inlineStr">
+      <c r="AE27" t="inlineStr">
         <is>
           <t>assets/catalogue/saanjh/hero-jar-candle/03-lifestyle.jpg</t>
         </is>
@@ -3174,11 +4187,13 @@
           <t>birthdays-just-because</t>
         </is>
       </c>
+      <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr">
         <is>
           <t>120 ml</t>
         </is>
       </c>
+      <c r="M28" t="inlineStr"/>
       <c r="N28" t="inlineStr">
         <is>
           <t>Natural soy wax, cotton wick, phthalate-free fragrance oils</t>
@@ -3191,7 +4206,7 @@
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Saanjh in our everyday ritual.</t>
+          <t>Saanjh · Everyday Ritual. The warmth of an evening that lingers — creamy vanilla softens deep sandalwood.</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
@@ -3199,29 +4214,64 @@
           <t>A Mysaa Rituals everyday ritual in the Saanjh fragrance — creamy vanilla softened by deep sandalwood, made for gifting, rituals and everyday moments.</t>
         </is>
       </c>
-      <c r="R28" t="b">
-        <v>0</v>
-      </c>
-      <c r="S28" t="b">
-        <v>1</v>
-      </c>
-      <c r="T28" t="b">
-        <v>1</v>
-      </c>
-      <c r="U28" t="b">
-        <v>1</v>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>Saanjh Everyday Ritual is a handcrafted everyday ritual scented with Saanjh. The warmth of an evening that lingers — creamy vanilla softens deep sandalwood. Made with natural soy wax, cotton wick(s) and phthalate-free fragrance oils, it is designed for slow everyday rituals, meaningful gifting and fragrance-led spaces.</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>Approx. 20–25 hours</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Trim the wick to about 5 mm before each burn. On the first burn, allow the wax pool to reach the edge. Burn for no more than 3–4 hours at a time. Keep away from drafts, children and pets.</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Usually 3–7 business days; the final delivery estimate is shared with your order confirmation.</t>
+        </is>
       </c>
       <c r="V28" t="inlineStr">
         <is>
+          <t>Shipping cost is separate and is calculated and shared with you at payment.</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>This product cannot be returned unless the wrong product or a defective product is received.</t>
+        </is>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>Saanjh Everyday Ritual, Saanjh, Saanjh candle, handcrafted everyday ritual, soy wax candle India, Indian fragrance candle, handmade candle India, Mysaa Rituals, gifting India</t>
+        </is>
+      </c>
+      <c r="Y28" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z28" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA28" t="b">
+        <v>1</v>
+      </c>
+      <c r="AB28" t="b">
+        <v>1</v>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
           <t>assets/catalogue/saanjh/wide-jar-candle/01-cover.jpg</t>
         </is>
       </c>
-      <c r="W28" t="inlineStr">
+      <c r="AD28" t="inlineStr">
         <is>
           <t>assets/catalogue/saanjh/wide-jar-candle/02-detail.jpg</t>
         </is>
       </c>
-      <c r="X28" t="inlineStr">
+      <c r="AE28" t="inlineStr">
         <is>
           <t>assets/catalogue/saanjh/wide-jar-candle/03-lifestyle.jpg</t>
         </is>
@@ -3266,11 +4316,13 @@
           <t>birthdays-just-because</t>
         </is>
       </c>
+      <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr">
         <is>
           <t>60 ml</t>
         </is>
       </c>
+      <c r="M29" t="inlineStr"/>
       <c r="N29" t="inlineStr">
         <is>
           <t>Natural soy wax, cotton wick, phthalate-free fragrance oils</t>
@@ -3283,7 +4335,7 @@
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Saanjh in our mini ritual.</t>
+          <t>Saanjh · Mini Ritual. The warmth of an evening that lingers — creamy vanilla softens deep sandalwood.</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
@@ -3291,29 +4343,64 @@
           <t>A Mysaa Rituals mini ritual in the Saanjh fragrance — creamy vanilla softened by deep sandalwood, made for gifting, rituals and everyday moments.</t>
         </is>
       </c>
-      <c r="R29" t="b">
-        <v>0</v>
-      </c>
-      <c r="S29" t="b">
-        <v>0</v>
-      </c>
-      <c r="T29" t="b">
-        <v>1</v>
-      </c>
-      <c r="U29" t="b">
-        <v>1</v>
+      <c r="R29" t="inlineStr">
+        <is>
+          <t>Saanjh Mini Ritual is a handcrafted mini ritual scented with Saanjh. The warmth of an evening that lingers — creamy vanilla softens deep sandalwood. Made with natural soy wax, cotton wick(s) and phthalate-free fragrance oils, it is designed for slow everyday rituals, meaningful gifting and fragrance-led spaces.</t>
+        </is>
+      </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>Approx. 10–15 hours</t>
+        </is>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Trim the wick to about 5 mm before each burn. On the first burn, allow the wax pool to reach the edge. Burn for no more than 3–4 hours at a time. Keep away from drafts, children and pets.</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Usually 3–7 business days; the final delivery estimate is shared with your order confirmation.</t>
+        </is>
       </c>
       <c r="V29" t="inlineStr">
         <is>
+          <t>Shipping cost is separate and is calculated and shared with you at payment.</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>This product cannot be returned unless the wrong product or a defective product is received.</t>
+        </is>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>Saanjh Mini Ritual, Saanjh, Saanjh candle, handcrafted mini ritual, soy wax candle India, Indian fragrance candle, handmade candle India, Mysaa Rituals, gifting India</t>
+        </is>
+      </c>
+      <c r="Y29" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA29" t="b">
+        <v>1</v>
+      </c>
+      <c r="AB29" t="b">
+        <v>1</v>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
           <t>assets/catalogue/saanjh/shot-glass-candle/01-cover.jpg</t>
         </is>
       </c>
-      <c r="W29" t="inlineStr">
+      <c r="AD29" t="inlineStr">
         <is>
           <t>assets/catalogue/saanjh/shot-glass-candle/02-detail.jpg</t>
         </is>
       </c>
-      <c r="X29" t="inlineStr">
+      <c r="AE29" t="inlineStr">
         <is>
           <t>assets/catalogue/saanjh/shot-glass-candle/03-lifestyle.jpg</t>
         </is>
@@ -3362,6 +4449,9 @@
           <t>birthdays-just-because</t>
         </is>
       </c>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr"/>
       <c r="N30" t="inlineStr">
         <is>
           <t>Natural soy wax, cotton wick, phthalate-free fragrance oils</t>
@@ -3374,7 +4464,7 @@
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Saanjh in our wax sachet combo.</t>
+          <t>Saanjh · Wax Sachet Combo. The warmth of an evening that lingers — creamy vanilla softens deep sandalwood.</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
@@ -3382,29 +4472,64 @@
           <t>A Mysaa Rituals wax sachet combo in the Saanjh fragrance — creamy vanilla softened by deep sandalwood, made for gifting, rituals and everyday moments.</t>
         </is>
       </c>
-      <c r="R30" t="b">
-        <v>0</v>
-      </c>
-      <c r="S30" t="b">
-        <v>0</v>
-      </c>
-      <c r="T30" t="b">
-        <v>1</v>
-      </c>
-      <c r="U30" t="b">
-        <v>1</v>
+      <c r="R30" t="inlineStr">
+        <is>
+          <t>Saanjh wax sachet combo from Mysaa Rituals, made with natural soy wax and fragrance oils. The warmth of an evening that lingers — creamy vanilla softens deep sandalwood. It is a flame-free way to bring the fragrance into your space and is suited to gifting, wardrobes, drawers or wax-warming rituals.</t>
+        </is>
+      </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>Not applicable — designed to be warmed, not burned</t>
+        </is>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Place a wax sachet in a suitable wax warmer and follow the warmer manufacturer's instructions. Never place wax melts directly on a flame.</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Usually 3–7 business days; the final delivery estimate is shared with your order confirmation.</t>
+        </is>
       </c>
       <c r="V30" t="inlineStr">
         <is>
+          <t>Shipping cost is separate and is calculated and shared with you at payment.</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>This product cannot be returned unless the wrong product or a defective product is received.</t>
+        </is>
+      </c>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>Saanjh Wax Sachet Combo, Saanjh, Saanjh candle, handcrafted wax sachet combo, soy wax candle India, Indian fragrance candle, handmade candle India, Mysaa Rituals, gifting India</t>
+        </is>
+      </c>
+      <c r="Y30" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA30" t="b">
+        <v>1</v>
+      </c>
+      <c r="AB30" t="b">
+        <v>1</v>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
           <t>assets/catalogue/saanjh/wax-melts/01-cover.jpg</t>
         </is>
       </c>
-      <c r="W30" t="inlineStr">
+      <c r="AD30" t="inlineStr">
         <is>
           <t>assets/catalogue/saanjh/wax-melts/02-detail.jpg</t>
         </is>
       </c>
-      <c r="X30" t="inlineStr">
+      <c r="AE30" t="inlineStr">
         <is>
           <t>assets/catalogue/saanjh/wax-melts/03-lifestyle.jpg</t>
         </is>
@@ -3449,6 +4574,9 @@
           <t>birthdays-just-because</t>
         </is>
       </c>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr"/>
       <c r="N31" t="inlineStr">
         <is>
           <t>Natural soy wax, cotton wick, phthalate-free fragrance oils</t>
@@ -3461,7 +4589,7 @@
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Saanjh in our gift hamper.</t>
+          <t>Saanjh · Gift Hampers. The warmth of an evening that lingers — creamy vanilla softens deep sandalwood.</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
@@ -3469,29 +4597,64 @@
           <t>A Mysaa Rituals gift hamper in the Saanjh fragrance — creamy vanilla softened by deep sandalwood, made for gifting, rituals and everyday moments.</t>
         </is>
       </c>
-      <c r="R31" t="b">
-        <v>0</v>
-      </c>
-      <c r="S31" t="b">
-        <v>0</v>
-      </c>
-      <c r="T31" t="b">
-        <v>1</v>
-      </c>
-      <c r="U31" t="b">
-        <v>1</v>
+      <c r="R31" t="inlineStr">
+        <is>
+          <t>Saanjh gift hamper from Mysaa Rituals — a curated gifting selection built around the Saanjh fragrance. The warmth of an evening that lingers — creamy vanilla softens deep sandalwood. Designed for birthdays, weddings, festivals, return gifts and thoughtful personal gifting.</t>
+        </is>
+      </c>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>Varies by candle included in the hamper</t>
+        </is>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Follow the care instructions for each candle included in your hamper.</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Usually 3–7 business days; the final delivery estimate is shared with your order confirmation.</t>
+        </is>
       </c>
       <c r="V31" t="inlineStr">
         <is>
+          <t>Shipping cost is separate and is calculated and shared with you at payment.</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>This product cannot be returned unless the wrong product or a defective product is received.</t>
+        </is>
+      </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>Saanjh Gift Hampers, Saanjh, Saanjh candle, handcrafted gift hampers, soy wax candle India, Indian fragrance candle, handmade candle India, Mysaa Rituals, gifting India, gift hamper India, wedding return gifts, festive gifts</t>
+        </is>
+      </c>
+      <c r="Y31" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA31" t="b">
+        <v>1</v>
+      </c>
+      <c r="AB31" t="b">
+        <v>1</v>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
           <t>assets/catalogue/saanjh/gift-hampers/01-cover.jpg</t>
         </is>
       </c>
-      <c r="W31" t="inlineStr">
+      <c r="AD31" t="inlineStr">
         <is>
           <t>assets/catalogue/saanjh/gift-hampers/02-detail.jpg</t>
         </is>
       </c>
-      <c r="X31" t="inlineStr">
+      <c r="AE31" t="inlineStr">
         <is>
           <t>assets/catalogue/saanjh/gift-hampers/03-lifestyle.jpg</t>
         </is>
@@ -3536,11 +4699,13 @@
           <t>festivals-celebrations|weddings-return-gifts|birthdays-just-because</t>
         </is>
       </c>
+      <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr">
         <is>
           <t>6 × 60 ml</t>
         </is>
       </c>
+      <c r="M32" t="inlineStr"/>
       <c r="N32" t="inlineStr">
         <is>
           <t>Natural soy wax, cotton wick, phthalate-free fragrance oils</t>
@@ -3553,7 +4718,7 @@
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>All six Mysaa Rituals fragrances in six 60 ml Mini Ritual candles.</t>
+          <t>all-fragrances · Discovery Set.</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
@@ -3561,29 +4726,64 @@
           <t>A complete discovery of all six Mysaa Rituals fragrances, presented as six 60 ml Mini Ritual candles.</t>
         </is>
       </c>
-      <c r="R32" t="b">
-        <v>0</v>
-      </c>
-      <c r="S32" t="b">
-        <v>1</v>
-      </c>
-      <c r="T32" t="b">
-        <v>0</v>
-      </c>
-      <c r="U32" t="b">
-        <v>1</v>
+      <c r="R32" t="inlineStr">
+        <is>
+          <t>The Mysaa Rituals Discovery Set brings together all six signature fragrances in six 60 ml Mini Ritual candles. It is an easy way to explore the collection before choosing a larger candle, and makes a thoughtful fragrance-led gift.</t>
+        </is>
+      </c>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>Approx. 10–15 hours per Mini Ritual</t>
+        </is>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Trim the wick to about 5 mm before each burn. On the first burn, allow the wax pool to reach the edge. Burn for no more than 3–4 hours at a time. Keep away from drafts, children and pets.</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Usually 3–7 business days; the final delivery estimate is shared with your order confirmation.</t>
+        </is>
       </c>
       <c r="V32" t="inlineStr">
         <is>
+          <t>Shipping cost is separate and is calculated and shared with you at payment.</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>This product cannot be returned unless the wrong product or a defective product is received.</t>
+        </is>
+      </c>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>Mysaa Rituals Discovery Set, all-fragrances, all-fragrances candle, handcrafted discovery set, soy wax candle India, Indian fragrance candle, handmade candle India, Mysaa Rituals, gifting India</t>
+        </is>
+      </c>
+      <c r="Y32" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z32" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB32" t="b">
+        <v>1</v>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
           <t>assets/catalogue/all-fragrances/discovery-set/01-discover-set.jpg</t>
         </is>
       </c>
-      <c r="W32" t="inlineStr">
+      <c r="AD32" t="inlineStr">
         <is>
           <t>assets/catalogue/all-fragrances/discovery-set/02-gulab-ki-chitthi.jpg</t>
         </is>
       </c>
-      <c r="X32" t="inlineStr">
+      <c r="AE32" t="inlineStr">
         <is>
           <t>assets/catalogue/all-fragrances/discovery-set/03-dhoop-chandan.jpg</t>
         </is>
@@ -3628,11 +4828,13 @@
           <t>weddings-return-gifts</t>
         </is>
       </c>
+      <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr">
         <is>
           <t>450 ml · 3 wick</t>
         </is>
       </c>
+      <c r="M33" t="inlineStr"/>
       <c r="N33" t="inlineStr">
         <is>
           <t>Natural soy wax, cotton wicks, phthalate-free fragrance oils</t>
@@ -3645,7 +4847,7 @@
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Gulab Ki Chitthi in our Grand Ritual — a 450 ml, 3-wick luxury candle.</t>
+          <t>Gulab Ki Chitthi · Grand Ritual. A fragrance that feels like receiving an old handwritten letter carrying the scent of roses.</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
@@ -3653,18 +4855,56 @@
           <t>A luxurious 450 ml, 3-wick Mysaa Rituals Grand Ritual in the Gulab Ki Chitthi fragrance. Designed for statement gifting and elevated spaces.</t>
         </is>
       </c>
-      <c r="R33" t="b">
-        <v>0</v>
-      </c>
-      <c r="S33" t="b">
-        <v>1</v>
-      </c>
-      <c r="T33" t="b">
-        <v>1</v>
-      </c>
-      <c r="U33" t="b">
-        <v>1</v>
-      </c>
+      <c r="R33" t="inlineStr">
+        <is>
+          <t>Gulab Ki Chitthi Grand Ritual is a handcrafted grand ritual scented with Gulab Ki Chitthi. A fragrance that feels like receiving an old handwritten letter carrying the scent of roses. Made with natural soy wax, cotton wick(s) and phthalate-free fragrance oils, it is designed for slow everyday rituals, meaningful gifting and fragrance-led spaces.</t>
+        </is>
+      </c>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>Approx. 50–60 hours</t>
+        </is>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Trim the wick to about 5 mm before each burn. On the first burn, allow the wax pool to reach the edge. Burn for no more than 3–4 hours at a time. Keep away from drafts, children and pets.</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Usually 3–7 business days; the final delivery estimate is shared with your order confirmation.</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Shipping cost is separate and is calculated and shared with you at payment.</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>This product cannot be returned unless the wrong product or a defective product is received.</t>
+        </is>
+      </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>Gulab Ki Chitthi Grand Ritual, Gulab Ki Chitthi, Gulab Ki Chitthi candle, handcrafted grand ritual, soy wax candle India, Indian fragrance candle, handmade candle India, Mysaa Rituals, gifting India</t>
+        </is>
+      </c>
+      <c r="Y33" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z33" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA33" t="b">
+        <v>1</v>
+      </c>
+      <c r="AB33" t="b">
+        <v>1</v>
+      </c>
+      <c r="AC33" t="inlineStr"/>
+      <c r="AD33" t="inlineStr"/>
+      <c r="AE33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -3705,11 +4945,13 @@
           <t>festivals-celebrations</t>
         </is>
       </c>
+      <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr">
         <is>
           <t>450 ml · 3 wick</t>
         </is>
       </c>
+      <c r="M34" t="inlineStr"/>
       <c r="N34" t="inlineStr">
         <is>
           <t>Natural soy wax, cotton wicks, phthalate-free fragrance oils</t>
@@ -3722,7 +4964,7 @@
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Dhoop &amp; Chandan in our Grand Ritual — a 450 ml, 3-wick luxury candle.</t>
+          <t>Dhoop &amp; Chandan · Grand Ritual. A warm, grounding fragrance inspired by the familiar aroma of sandalwood and dhoop.</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
@@ -3730,18 +4972,56 @@
           <t>A luxurious 450 ml, 3-wick Mysaa Rituals Grand Ritual in the Dhoop &amp; Chandan fragrance. Designed for statement gifting and elevated spaces.</t>
         </is>
       </c>
-      <c r="R34" t="b">
-        <v>0</v>
-      </c>
-      <c r="S34" t="b">
-        <v>1</v>
-      </c>
-      <c r="T34" t="b">
-        <v>1</v>
-      </c>
-      <c r="U34" t="b">
-        <v>1</v>
-      </c>
+      <c r="R34" t="inlineStr">
+        <is>
+          <t>Dhoop &amp; Chandan Grand Ritual is a handcrafted grand ritual scented with Dhoop &amp; Chandan. A warm, grounding fragrance inspired by the familiar aroma of sandalwood and dhoop. Made with natural soy wax, cotton wick(s) and phthalate-free fragrance oils, it is designed for slow everyday rituals, meaningful gifting and fragrance-led spaces.</t>
+        </is>
+      </c>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>Approx. 50–60 hours</t>
+        </is>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Trim the wick to about 5 mm before each burn. On the first burn, allow the wax pool to reach the edge. Burn for no more than 3–4 hours at a time. Keep away from drafts, children and pets.</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Usually 3–7 business days; the final delivery estimate is shared with your order confirmation.</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Shipping cost is separate and is calculated and shared with you at payment.</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>This product cannot be returned unless the wrong product or a defective product is received.</t>
+        </is>
+      </c>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>Dhoop &amp; Chandan Grand Ritual, Dhoop &amp; Chandan, Dhoop &amp; Chandan candle, handcrafted grand ritual, soy wax candle India, Indian fragrance candle, handmade candle India, Mysaa Rituals, gifting India</t>
+        </is>
+      </c>
+      <c r="Y34" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z34" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA34" t="b">
+        <v>1</v>
+      </c>
+      <c r="AB34" t="b">
+        <v>1</v>
+      </c>
+      <c r="AC34" t="inlineStr"/>
+      <c r="AD34" t="inlineStr"/>
+      <c r="AE34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -3782,11 +5062,13 @@
           <t>weddings-return-gifts</t>
         </is>
       </c>
+      <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr">
         <is>
           <t>450 ml · 3 wick</t>
         </is>
       </c>
+      <c r="M35" t="inlineStr"/>
       <c r="N35" t="inlineStr">
         <is>
           <t>Natural soy wax, cotton wicks, phthalate-free fragrance oils</t>
@@ -3799,7 +5081,7 @@
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Gajre Ka Shringar in our Grand Ritual — a 450 ml, 3-wick luxury candle.</t>
+          <t>Gajre Ka Shringar · Grand Ritual. Inspired by the fragrance of fresh gajras and the timeless beauty of jasmine.</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
@@ -3807,18 +5089,56 @@
           <t>A luxurious 450 ml, 3-wick Mysaa Rituals Grand Ritual in the Gajre Ka Shringar fragrance. Designed for statement gifting and elevated spaces.</t>
         </is>
       </c>
-      <c r="R35" t="b">
-        <v>0</v>
-      </c>
-      <c r="S35" t="b">
-        <v>1</v>
-      </c>
-      <c r="T35" t="b">
-        <v>1</v>
-      </c>
-      <c r="U35" t="b">
-        <v>1</v>
-      </c>
+      <c r="R35" t="inlineStr">
+        <is>
+          <t>Gajre Ka Shringar Grand Ritual is a handcrafted grand ritual scented with Gajre Ka Shringar. Inspired by the fragrance of fresh gajras and the timeless beauty of jasmine. Made with natural soy wax, cotton wick(s) and phthalate-free fragrance oils, it is designed for slow everyday rituals, meaningful gifting and fragrance-led spaces.</t>
+        </is>
+      </c>
+      <c r="S35" t="inlineStr">
+        <is>
+          <t>Approx. 50–60 hours</t>
+        </is>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Trim the wick to about 5 mm before each burn. On the first burn, allow the wax pool to reach the edge. Burn for no more than 3–4 hours at a time. Keep away from drafts, children and pets.</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Usually 3–7 business days; the final delivery estimate is shared with your order confirmation.</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Shipping cost is separate and is calculated and shared with you at payment.</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>This product cannot be returned unless the wrong product or a defective product is received.</t>
+        </is>
+      </c>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>Gajre Ka Shringar Grand Ritual, Gajre Ka Shringar, Gajre Ka Shringar candle, handcrafted grand ritual, soy wax candle India, Indian fragrance candle, handmade candle India, Mysaa Rituals, gifting India</t>
+        </is>
+      </c>
+      <c r="Y35" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z35" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA35" t="b">
+        <v>1</v>
+      </c>
+      <c r="AB35" t="b">
+        <v>1</v>
+      </c>
+      <c r="AC35" t="inlineStr"/>
+      <c r="AD35" t="inlineStr"/>
+      <c r="AE35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -3859,11 +5179,13 @@
           <t>festivals-celebrations</t>
         </is>
       </c>
+      <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr">
         <is>
           <t>450 ml · 3 wick</t>
         </is>
       </c>
+      <c r="M36" t="inlineStr"/>
       <c r="N36" t="inlineStr">
         <is>
           <t>Natural soy wax, cotton wicks, phthalate-free fragrance oils</t>
@@ -3876,7 +5198,7 @@
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Madhuban in our Grand Ritual — a 450 ml, 3-wick luxury candle.</t>
+          <t>Madhuban · Grand Ritual. A deep floral fragrance inspired by flowers that come alive after sunset.</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
@@ -3884,18 +5206,56 @@
           <t>A luxurious 450 ml, 3-wick Mysaa Rituals Grand Ritual in the Madhuban fragrance. Designed for statement gifting and elevated spaces.</t>
         </is>
       </c>
-      <c r="R36" t="b">
-        <v>0</v>
-      </c>
-      <c r="S36" t="b">
-        <v>1</v>
-      </c>
-      <c r="T36" t="b">
-        <v>1</v>
-      </c>
-      <c r="U36" t="b">
-        <v>1</v>
-      </c>
+      <c r="R36" t="inlineStr">
+        <is>
+          <t>Madhuban Grand Ritual is a handcrafted grand ritual scented with Madhuban. A deep floral fragrance inspired by flowers that come alive after sunset. Made with natural soy wax, cotton wick(s) and phthalate-free fragrance oils, it is designed for slow everyday rituals, meaningful gifting and fragrance-led spaces.</t>
+        </is>
+      </c>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>Approx. 50–60 hours</t>
+        </is>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Trim the wick to about 5 mm before each burn. On the first burn, allow the wax pool to reach the edge. Burn for no more than 3–4 hours at a time. Keep away from drafts, children and pets.</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Usually 3–7 business days; the final delivery estimate is shared with your order confirmation.</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Shipping cost is separate and is calculated and shared with you at payment.</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>This product cannot be returned unless the wrong product or a defective product is received.</t>
+        </is>
+      </c>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>Madhuban Grand Ritual, Madhuban, Madhuban candle, handcrafted grand ritual, soy wax candle India, Indian fragrance candle, handmade candle India, Mysaa Rituals, gifting India</t>
+        </is>
+      </c>
+      <c r="Y36" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z36" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA36" t="b">
+        <v>1</v>
+      </c>
+      <c r="AB36" t="b">
+        <v>1</v>
+      </c>
+      <c r="AC36" t="inlineStr"/>
+      <c r="AD36" t="inlineStr"/>
+      <c r="AE36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -3936,11 +5296,13 @@
           <t>birthdays-just-because</t>
         </is>
       </c>
+      <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr">
         <is>
           <t>450 ml · 3 wick</t>
         </is>
       </c>
+      <c r="M37" t="inlineStr"/>
       <c r="N37" t="inlineStr">
         <is>
           <t>Natural soy wax, cotton wicks, phthalate-free fragrance oils</t>
@@ -3953,7 +5315,7 @@
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Raat Ki Rani in our Grand Ritual — a 450 ml, 3-wick luxury candle.</t>
+          <t>Raat Ki Rani · Grand Ritual. An evocative night-blooming floral fragrance inspired by the queen of the night.</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
@@ -3961,18 +5323,56 @@
           <t>A luxurious 450 ml, 3-wick Mysaa Rituals Grand Ritual in the Raat Ki Rani fragrance. Designed for statement gifting and elevated spaces.</t>
         </is>
       </c>
-      <c r="R37" t="b">
-        <v>0</v>
-      </c>
-      <c r="S37" t="b">
-        <v>1</v>
-      </c>
-      <c r="T37" t="b">
-        <v>1</v>
-      </c>
-      <c r="U37" t="b">
-        <v>1</v>
-      </c>
+      <c r="R37" t="inlineStr">
+        <is>
+          <t>Raat Ki Rani Grand Ritual is a handcrafted grand ritual scented with Raat Ki Rani. An evocative night-blooming floral fragrance inspired by the queen of the night. Made with natural soy wax, cotton wick(s) and phthalate-free fragrance oils, it is designed for slow everyday rituals, meaningful gifting and fragrance-led spaces.</t>
+        </is>
+      </c>
+      <c r="S37" t="inlineStr">
+        <is>
+          <t>Approx. 50–60 hours</t>
+        </is>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Trim the wick to about 5 mm before each burn. On the first burn, allow the wax pool to reach the edge. Burn for no more than 3–4 hours at a time. Keep away from drafts, children and pets.</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Usually 3–7 business days; the final delivery estimate is shared with your order confirmation.</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Shipping cost is separate and is calculated and shared with you at payment.</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>This product cannot be returned unless the wrong product or a defective product is received.</t>
+        </is>
+      </c>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>Raat Ki Rani Grand Ritual, Raat Ki Rani, Raat Ki Rani candle, handcrafted grand ritual, soy wax candle India, Indian fragrance candle, handmade candle India, Mysaa Rituals, gifting India</t>
+        </is>
+      </c>
+      <c r="Y37" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z37" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA37" t="b">
+        <v>1</v>
+      </c>
+      <c r="AB37" t="b">
+        <v>1</v>
+      </c>
+      <c r="AC37" t="inlineStr"/>
+      <c r="AD37" t="inlineStr"/>
+      <c r="AE37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -4013,11 +5413,13 @@
           <t>birthdays-just-because</t>
         </is>
       </c>
+      <c r="K38" t="inlineStr"/>
       <c r="L38" t="inlineStr">
         <is>
           <t>450 ml · 3 wick</t>
         </is>
       </c>
+      <c r="M38" t="inlineStr"/>
       <c r="N38" t="inlineStr">
         <is>
           <t>Natural soy wax, cotton wicks, phthalate-free fragrance oils</t>
@@ -4030,7 +5432,7 @@
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Saanjh in our Grand Ritual — a 450 ml, 3-wick luxury candle.</t>
+          <t>Saanjh · Grand Ritual. The warmth of an evening that lingers — creamy vanilla softens deep sandalwood.</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
@@ -4038,18 +5440,56 @@
           <t>A luxurious 450 ml, 3-wick Mysaa Rituals Grand Ritual in the Saanjh fragrance. Designed for statement gifting and elevated spaces.</t>
         </is>
       </c>
-      <c r="R38" t="b">
-        <v>0</v>
-      </c>
-      <c r="S38" t="b">
-        <v>1</v>
-      </c>
-      <c r="T38" t="b">
-        <v>1</v>
-      </c>
-      <c r="U38" t="b">
-        <v>1</v>
-      </c>
+      <c r="R38" t="inlineStr">
+        <is>
+          <t>Saanjh Grand Ritual is a handcrafted grand ritual scented with Saanjh. The warmth of an evening that lingers — creamy vanilla softens deep sandalwood. Made with natural soy wax, cotton wick(s) and phthalate-free fragrance oils, it is designed for slow everyday rituals, meaningful gifting and fragrance-led spaces.</t>
+        </is>
+      </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>Approx. 50–60 hours</t>
+        </is>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Trim the wick to about 5 mm before each burn. On the first burn, allow the wax pool to reach the edge. Burn for no more than 3–4 hours at a time. Keep away from drafts, children and pets.</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Usually 3–7 business days; the final delivery estimate is shared with your order confirmation.</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Shipping cost is separate and is calculated and shared with you at payment.</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>This product cannot be returned unless the wrong product or a defective product is received.</t>
+        </is>
+      </c>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>Saanjh Grand Ritual, Saanjh, Saanjh candle, handcrafted grand ritual, soy wax candle India, Indian fragrance candle, handmade candle India, Mysaa Rituals, gifting India</t>
+        </is>
+      </c>
+      <c r="Y38" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z38" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA38" t="b">
+        <v>1</v>
+      </c>
+      <c r="AB38" t="b">
+        <v>1</v>
+      </c>
+      <c r="AC38" t="inlineStr"/>
+      <c r="AD38" t="inlineStr"/>
+      <c r="AE38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -4099,6 +5539,7 @@
           <t>6 pieces minimum</t>
         </is>
       </c>
+      <c r="M39" t="inlineStr"/>
       <c r="N39" t="inlineStr">
         <is>
           <t>Hand-poured wax candle</t>
@@ -4111,7 +5552,7 @@
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Create a custom batch of mould candles with your choice of shape, fragrance and primary colour.</t>
+          <t>None · Mold Candles.</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
@@ -4119,18 +5560,56 @@
           <t>Choose one mould shape, one Mysaa Rituals fragrance and one primary colour for your batch. Minimum order is 6 pieces. The current batch price is ₹399 for 6 pieces.</t>
         </is>
       </c>
-      <c r="R39" t="b">
-        <v>0</v>
-      </c>
-      <c r="S39" t="b">
-        <v>1</v>
-      </c>
-      <c r="T39" t="b">
-        <v>1</v>
-      </c>
-      <c r="U39" t="b">
-        <v>1</v>
-      </c>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>Mysaa Rituals custom mould candles let you choose a candle shape, fragrance and primary colour for a personalised batch. Choose from Daisy, Rose, Carnation, Cactus, Tortoise, Laddu and Chakli shapes, with a minimum order quantity of 6 pieces.</t>
+        </is>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>Approx. 12–20 hours, depending on mould size</t>
+        </is>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Trim the wick to about 5 mm before each burn. On the first burn, allow the wax pool to reach the edge. Burn for no more than 3–4 hours at a time. Keep away from drafts, children and pets.</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Usually 3–7 business days; the final delivery estimate is shared with your order confirmation.</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Shipping cost is separate and is calculated and shared with you at payment.</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>This product cannot be returned unless the wrong product or a defective product is received.</t>
+        </is>
+      </c>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>Mold Candles, None candle, handcrafted mold candles, soy wax candle India, Indian fragrance candle, handmade candle India, Mysaa Rituals, gifting India, custom mould candles, personalised candles, wedding favour candles</t>
+        </is>
+      </c>
+      <c r="Y39" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z39" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA39" t="b">
+        <v>1</v>
+      </c>
+      <c r="AB39" t="b">
+        <v>1</v>
+      </c>
+      <c r="AC39" t="inlineStr"/>
+      <c r="AD39" t="inlineStr"/>
+      <c r="AE39" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4579,7 +6058,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B24"/>
+  <dimension ref="A1:B25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -4702,7 +6181,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Mysaa Rituals — Handcrafted Fragrance &amp; Gifting</t>
+          <t>Mysaa Rituals — Handcrafted Soy Wax Candles, Indian Fragrances &amp; Gifting</t>
         </is>
       </c>
     </row>
@@ -4714,7 +6193,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Handcrafted candles and gifts inspired by Indian fragrances, memories and everyday rituals.</t>
+          <t>Shop handcrafted soy wax candles, Indian fragrance candles, Grand Rituals, Mini Rituals, gift hampers, wedding return gifts and personalised candles from Mysaa Rituals.</t>
         </is>
       </c>
     </row>
@@ -4850,6 +6329,11 @@
           <t>festivalBannerImage</t>
         </is>
       </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>assets/festive-banner-bg.svg</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -4860,6 +6344,18 @@
       <c r="B24" t="inlineStr">
         <is>
           <t>mysaarituals@gmail.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>seoKeywords</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>handcrafted candles India, soy wax candles India, luxury candles India, Indian fragrance candles, handmade candles, gift hampers India, wedding return gifts, festive candles, personalised candles, custom candles, candle gifting, Mysaa Rituals</t>
         </is>
       </c>
     </row>

--- a/data/mysaa_products.xlsx
+++ b/data/mysaa_products.xlsx
@@ -5853,7 +5853,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Mysaa Rituals — Handcrafted Soy Wax Candles, Indian Fragrances &amp; Gifting</t>
+          <t>Mysaa Rituals | Handcrafted Soy Wax Candles &amp; Indian Fragrances</t>
         </is>
       </c>
     </row>
